--- a/results.xlsx
+++ b/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utilizador\Desktop\uni\MEI 1ano1sem\DAA\trabalho\DAA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4876DA2B-187A-4A47-B183-D8C5C690976F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54769D0E-843A-4EB0-85CC-EA843817E8F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="14020" xr2:uid="{744B1543-7C44-49C5-883E-AA14D96B6E1A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="254">
   <si>
     <t>DAA tests and results</t>
   </si>
@@ -584,9 +584,6 @@
     <t>feature_fraction=0.8, reg_alpha=0.1,reg_lambda=0.1,verbose=-1</t>
   </si>
   <si>
-    <t>Stacking type1</t>
-  </si>
-  <si>
     <t>(5 estimators)</t>
   </si>
   <si>
@@ -608,9 +605,6 @@
     <t>est=rfc2,xgb2,lgbm1</t>
   </si>
   <si>
-    <t>Voting type1</t>
-  </si>
-  <si>
     <t>est=rfc1,xgb1,svm1,lr1,lgbm1</t>
   </si>
   <si>
@@ -618,9 +612,6 @@
   </si>
   <si>
     <t>est=rfc2,xgb2,svm2,lr1,lgbm1</t>
-  </si>
-  <si>
-    <t>Voting type2</t>
   </si>
   <si>
     <t>(3 estimators)</t>
@@ -728,7 +719,85 @@
     <t>LightGBM1</t>
   </si>
   <si>
-    <t>Stacking type2</t>
+    <t>None of the models provide super stable results, but some are interesting</t>
+  </si>
+  <si>
+    <t>Next step is to perfom more agressive oversampling</t>
+  </si>
+  <si>
+    <t>Fifth batch of tests - Oversampling without Dimensionality</t>
+  </si>
+  <si>
+    <t>Considering the last batche's results weren't completely inconsistent,</t>
+  </si>
+  <si>
+    <t>It's probably worth it to test na agressive way of oversampling again.</t>
+  </si>
+  <si>
+    <t>In this batch, data treatment is the same as in the fourth besides for the oversampling.</t>
+  </si>
+  <si>
+    <t>Oversampling wise, the various ways to do it are described in the table</t>
+  </si>
+  <si>
+    <t>The models used are described in the table corresponding to the fourth batch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oversampling class 2 by </t>
+  </si>
+  <si>
+    <t>0.33 of majority class and</t>
+  </si>
+  <si>
+    <t>all other by 1.0 of</t>
+  </si>
+  <si>
+    <t>Stacking type1 - 1</t>
+  </si>
+  <si>
+    <t>Stacking type1 - 2</t>
+  </si>
+  <si>
+    <t>Stacking type2 - 1</t>
+  </si>
+  <si>
+    <t>Stacking type2 - 2</t>
+  </si>
+  <si>
+    <t>Voting type1 - 1</t>
+  </si>
+  <si>
+    <t>Voting type2 - 1</t>
+  </si>
+  <si>
+    <t>Voting type1 - 2</t>
+  </si>
+  <si>
+    <t>Voting type2 - 2</t>
+  </si>
+  <si>
+    <t>0.490</t>
+  </si>
+  <si>
+    <t>0.519</t>
+  </si>
+  <si>
+    <t>0.589</t>
+  </si>
+  <si>
+    <t>0.468</t>
+  </si>
+  <si>
+    <t>0.510</t>
+  </si>
+  <si>
+    <t>0.251</t>
+  </si>
+  <si>
+    <t>0.309</t>
+  </si>
+  <si>
+    <t>0.311</t>
   </si>
 </sst>
 </file>
@@ -1221,13 +1290,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1409,28 +1477,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1448,29 +1495,8 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1478,28 +1504,79 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1811,6 +1888,8 @@
     <col min="25" max="25" width="8.7265625" customWidth="1"/>
     <col min="26" max="26" width="16.90625" customWidth="1"/>
     <col min="27" max="27" width="73.7265625" customWidth="1"/>
+    <col min="33" max="33" width="23.453125" customWidth="1"/>
+    <col min="35" max="35" width="18.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:73" x14ac:dyDescent="0.35">
@@ -1987,27 +2066,29 @@
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
-      <c r="R3" s="74" t="s">
+      <c r="R3" s="89" t="s">
         <v>119</v>
       </c>
-      <c r="S3" s="74"/>
-      <c r="T3" s="74"/>
-      <c r="U3" s="74"/>
-      <c r="V3" s="74"/>
-      <c r="W3" s="74"/>
-      <c r="X3" s="74"/>
-      <c r="Y3" s="74"/>
-      <c r="Z3" s="74" t="s">
+      <c r="S3" s="89"/>
+      <c r="T3" s="89"/>
+      <c r="U3" s="89"/>
+      <c r="V3" s="89"/>
+      <c r="W3" s="89"/>
+      <c r="X3" s="89"/>
+      <c r="Y3" s="89"/>
+      <c r="Z3" s="73" t="s">
         <v>149</v>
       </c>
-      <c r="AA3" s="74"/>
-      <c r="AB3" s="74"/>
-      <c r="AC3" s="74"/>
-      <c r="AD3" s="74"/>
-      <c r="AE3" s="74"/>
-      <c r="AF3" s="74"/>
-      <c r="AG3" s="74"/>
-      <c r="AH3" s="1"/>
+      <c r="AA3" s="73"/>
+      <c r="AB3" s="73"/>
+      <c r="AC3" s="73"/>
+      <c r="AD3" s="73"/>
+      <c r="AE3" s="73"/>
+      <c r="AF3" s="73"/>
+      <c r="AG3" s="73" t="s">
+        <v>229</v>
+      </c>
+      <c r="AH3" s="73"/>
       <c r="AI3" s="1"/>
       <c r="AJ3" s="1"/>
       <c r="AK3" s="1"/>
@@ -2070,27 +2151,29 @@
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
-      <c r="R4" s="74" t="s">
+      <c r="R4" s="89" t="s">
         <v>120</v>
       </c>
-      <c r="S4" s="74"/>
-      <c r="T4" s="74"/>
-      <c r="U4" s="74"/>
-      <c r="V4" s="74"/>
-      <c r="W4" s="74"/>
-      <c r="X4" s="74"/>
-      <c r="Y4" s="74"/>
-      <c r="Z4" s="74" t="s">
+      <c r="S4" s="89"/>
+      <c r="T4" s="89"/>
+      <c r="U4" s="89"/>
+      <c r="V4" s="89"/>
+      <c r="W4" s="89"/>
+      <c r="X4" s="89"/>
+      <c r="Y4" s="89"/>
+      <c r="Z4" s="73" t="s">
         <v>150</v>
       </c>
-      <c r="AA4" s="74"/>
-      <c r="AB4" s="74"/>
-      <c r="AC4" s="74"/>
-      <c r="AD4" s="74"/>
-      <c r="AE4" s="74"/>
-      <c r="AF4" s="74"/>
-      <c r="AG4" s="74"/>
-      <c r="AH4" s="1"/>
+      <c r="AA4" s="73"/>
+      <c r="AB4" s="73"/>
+      <c r="AC4" s="73"/>
+      <c r="AD4" s="73"/>
+      <c r="AE4" s="73"/>
+      <c r="AF4" s="73"/>
+      <c r="AG4" s="73" t="s">
+        <v>150</v>
+      </c>
+      <c r="AH4" s="73"/>
       <c r="AI4" s="1"/>
       <c r="AJ4" s="1"/>
       <c r="AK4" s="1"/>
@@ -2170,7 +2253,9 @@
       <c r="AD5" s="1"/>
       <c r="AE5" s="1"/>
       <c r="AF5" s="1"/>
-      <c r="AG5" s="1"/>
+      <c r="AG5" s="4" t="s">
+        <v>230</v>
+      </c>
       <c r="AH5" s="1"/>
       <c r="AI5" s="1"/>
       <c r="AJ5" s="1"/>
@@ -2214,23 +2299,23 @@
     </row>
     <row r="6" spans="1:73" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1"/>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="F6" s="17" t="s">
         <v>3</v>
       </c>
       <c r="G6" s="1"/>
-      <c r="H6" s="14"/>
+      <c r="H6" s="13"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1" t="s">
         <v>82</v>
@@ -2261,7 +2346,9 @@
       <c r="AD6" s="1"/>
       <c r="AE6" s="1"/>
       <c r="AF6" s="1"/>
-      <c r="AG6" s="1"/>
+      <c r="AG6" s="1" t="s">
+        <v>231</v>
+      </c>
       <c r="AH6" s="1"/>
       <c r="AI6" s="1"/>
       <c r="AJ6" s="1"/>
@@ -2305,15 +2392,15 @@
     </row>
     <row r="7" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A7" s="1"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="27" t="s">
+      <c r="B7" s="18"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="27" t="s">
+      <c r="E7" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="39" t="s">
+      <c r="F7" s="38" t="s">
         <v>29</v>
       </c>
       <c r="G7" s="1"/>
@@ -2348,7 +2435,9 @@
       <c r="AD7" s="1"/>
       <c r="AE7" s="1"/>
       <c r="AF7" s="1"/>
-      <c r="AG7" s="1"/>
+      <c r="AG7" s="1" t="s">
+        <v>232</v>
+      </c>
       <c r="AH7" s="1"/>
       <c r="AI7" s="1"/>
       <c r="AJ7" s="1"/>
@@ -2392,19 +2481,19 @@
     </row>
     <row r="8" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A8" s="1"/>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="28" t="s">
+      <c r="C8" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="33" t="s">
+      <c r="D8" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="33" t="s">
+      <c r="E8" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="F8" s="40" t="s">
+      <c r="F8" s="39" t="s">
         <v>29</v>
       </c>
       <c r="G8" s="1"/>
@@ -2439,7 +2528,9 @@
       <c r="AD8" s="1"/>
       <c r="AE8" s="1"/>
       <c r="AF8" s="1"/>
-      <c r="AG8" s="1"/>
+      <c r="AG8" s="1" t="s">
+        <v>233</v>
+      </c>
       <c r="AH8" s="1"/>
       <c r="AI8" s="1"/>
       <c r="AJ8" s="1"/>
@@ -2483,15 +2574,15 @@
     </row>
     <row r="9" spans="1:73" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="1"/>
-      <c r="B9" s="25"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="34" t="s">
+      <c r="B9" s="24"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="38" t="s">
+      <c r="E9" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="13" t="s">
+      <c r="F9" s="12" t="s">
         <v>29</v>
       </c>
       <c r="G9" s="1"/>
@@ -2524,7 +2615,9 @@
       <c r="AD9" s="1"/>
       <c r="AE9" s="1"/>
       <c r="AF9" s="1"/>
-      <c r="AG9" s="1"/>
+      <c r="AG9" s="1" t="s">
+        <v>234</v>
+      </c>
       <c r="AH9" s="1"/>
       <c r="AI9" s="1"/>
       <c r="AJ9" s="1"/>
@@ -2568,35 +2661,35 @@
     </row>
     <row r="10" spans="1:73" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="1"/>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="C10" s="30"/>
-      <c r="D10" s="35" t="s">
+      <c r="C10" s="29"/>
+      <c r="D10" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="35" t="s">
+      <c r="E10" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="F10" s="41" t="s">
+      <c r="F10" s="40" t="s">
         <v>29</v>
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
-      <c r="J10" s="46" t="s">
+      <c r="J10" s="45" t="s">
         <v>49</v>
       </c>
-      <c r="K10" s="47" t="s">
+      <c r="K10" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="L10" s="47" t="s">
+      <c r="L10" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="M10" s="60" t="s">
+      <c r="M10" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="N10" s="48" t="s">
+      <c r="N10" s="47" t="s">
         <v>3</v>
       </c>
       <c r="O10" s="1"/>
@@ -2663,51 +2756,51 @@
     </row>
     <row r="11" spans="1:73" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="1"/>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="C11" s="30" t="s">
+      <c r="C11" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="35" t="s">
+      <c r="D11" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="E11" s="35" t="s">
+      <c r="E11" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="F11" s="41" t="s">
+      <c r="F11" s="40" t="s">
         <v>29</v>
       </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="70"/>
-      <c r="L11" s="51" t="s">
+      <c r="J11" s="7"/>
+      <c r="K11" s="69"/>
+      <c r="L11" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="M11" s="61" t="s">
+      <c r="M11" s="60" t="s">
         <v>100</v>
       </c>
-      <c r="N11" s="21" t="s">
+      <c r="N11" s="20" t="s">
         <v>101</v>
       </c>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
-      <c r="R11" s="46" t="s">
+      <c r="R11" s="45" t="s">
         <v>49</v>
       </c>
-      <c r="S11" s="47" t="s">
+      <c r="S11" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="T11" s="47" t="s">
+      <c r="T11" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="U11" s="60" t="s">
+      <c r="U11" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="V11" s="48" t="s">
+      <c r="V11" s="47" t="s">
         <v>3</v>
       </c>
       <c r="W11" s="1"/>
@@ -2722,11 +2815,21 @@
       <c r="AD11" s="1"/>
       <c r="AE11" s="1"/>
       <c r="AF11" s="1"/>
-      <c r="AG11" s="1"/>
-      <c r="AH11" s="1"/>
-      <c r="AI11" s="1"/>
-      <c r="AJ11" s="1"/>
-      <c r="AK11" s="1"/>
+      <c r="AG11" s="45" t="s">
+        <v>49</v>
+      </c>
+      <c r="AH11" s="46" t="s">
+        <v>48</v>
+      </c>
+      <c r="AI11" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ11" s="46" t="s">
+        <v>2</v>
+      </c>
+      <c r="AK11" s="47" t="s">
+        <v>3</v>
+      </c>
       <c r="AL11" s="1"/>
       <c r="AM11" s="1"/>
       <c r="AN11" s="1"/>
@@ -2766,47 +2869,47 @@
     </row>
     <row r="12" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A12" s="1"/>
-      <c r="B12" s="26" t="s">
+      <c r="B12" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="C12" s="31"/>
-      <c r="D12" s="36" t="s">
+      <c r="C12" s="30"/>
+      <c r="D12" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="E12" s="36" t="s">
+      <c r="E12" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="F12" s="16" t="s">
+      <c r="F12" s="15" t="s">
         <v>29</v>
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
-      <c r="J12" s="9" t="s">
+      <c r="J12" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="K12" s="52"/>
-      <c r="L12" s="58" t="s">
+      <c r="K12" s="51"/>
+      <c r="L12" s="57" t="s">
         <v>14</v>
       </c>
-      <c r="M12" s="61" t="s">
+      <c r="M12" s="60" t="s">
         <v>102</v>
       </c>
-      <c r="N12" s="21" t="s">
+      <c r="N12" s="20" t="s">
         <v>103</v>
       </c>
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
-      <c r="R12" s="8"/>
-      <c r="S12" s="70"/>
-      <c r="T12" s="51" t="s">
+      <c r="R12" s="7"/>
+      <c r="S12" s="69"/>
+      <c r="T12" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="U12" s="61" t="s">
+      <c r="U12" s="60" t="s">
         <v>98</v>
       </c>
-      <c r="V12" s="21" t="s">
+      <c r="V12" s="20" t="s">
         <v>99</v>
       </c>
       <c r="W12" s="1"/>
@@ -2821,11 +2924,17 @@
       <c r="AD12" s="1"/>
       <c r="AE12" s="1"/>
       <c r="AF12" s="1"/>
-      <c r="AG12" s="1"/>
-      <c r="AH12" s="1"/>
-      <c r="AI12" s="1"/>
-      <c r="AJ12" s="1"/>
-      <c r="AK12" s="1"/>
+      <c r="AG12" s="7"/>
+      <c r="AH12" s="69"/>
+      <c r="AI12" s="50" t="s">
+        <v>219</v>
+      </c>
+      <c r="AJ12" s="50" t="s">
+        <v>246</v>
+      </c>
+      <c r="AK12" s="20" t="s">
+        <v>251</v>
+      </c>
       <c r="AL12" s="1"/>
       <c r="AM12" s="1"/>
       <c r="AN12" s="1"/>
@@ -2865,47 +2974,47 @@
     </row>
     <row r="13" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A13" s="1"/>
-      <c r="B13" s="20" t="s">
+      <c r="B13" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="C13" s="28"/>
-      <c r="D13" s="33" t="s">
+      <c r="C13" s="27"/>
+      <c r="D13" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="E13" s="33" t="s">
+      <c r="E13" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="F13" s="40" t="s">
+      <c r="F13" s="39" t="s">
         <v>29</v>
       </c>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
-      <c r="J13" s="9" t="s">
+      <c r="J13" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="K13" s="52"/>
-      <c r="L13" s="58" t="s">
+      <c r="K13" s="51"/>
+      <c r="L13" s="57" t="s">
         <v>84</v>
       </c>
-      <c r="M13" s="62" t="s">
+      <c r="M13" s="61" t="s">
         <v>104</v>
       </c>
-      <c r="N13" s="21" t="s">
+      <c r="N13" s="20" t="s">
         <v>29</v>
       </c>
       <c r="O13" s="1"/>
       <c r="P13" s="1"/>
       <c r="Q13" s="1"/>
-      <c r="R13" s="9"/>
-      <c r="S13" s="52"/>
-      <c r="T13" s="58" t="s">
+      <c r="R13" s="8"/>
+      <c r="S13" s="51"/>
+      <c r="T13" s="57" t="s">
         <v>14</v>
       </c>
-      <c r="U13" s="61" t="s">
+      <c r="U13" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="V13" s="21" t="s">
+      <c r="V13" s="20" t="s">
         <v>29</v>
       </c>
       <c r="W13" s="1"/>
@@ -2920,11 +3029,19 @@
       <c r="AD13" s="1"/>
       <c r="AE13" s="1"/>
       <c r="AF13" s="1"/>
-      <c r="AG13" s="1"/>
-      <c r="AH13" s="1"/>
-      <c r="AI13" s="1"/>
-      <c r="AJ13" s="1"/>
-      <c r="AK13" s="1"/>
+      <c r="AG13" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="AH13" s="51"/>
+      <c r="AI13" s="57" t="s">
+        <v>222</v>
+      </c>
+      <c r="AJ13" s="57" t="s">
+        <v>247</v>
+      </c>
+      <c r="AK13" s="20" t="s">
+        <v>213</v>
+      </c>
       <c r="AL13" s="1"/>
       <c r="AM13" s="1"/>
       <c r="AN13" s="1"/>
@@ -2964,53 +3081,53 @@
     </row>
     <row r="14" spans="1:73" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="1"/>
-      <c r="B14" s="20" t="s">
+      <c r="B14" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="C14" s="28" t="s">
+      <c r="C14" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="33" t="s">
+      <c r="D14" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="E14" s="33" t="s">
+      <c r="E14" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="F14" s="40" t="s">
+      <c r="F14" s="39" t="s">
         <v>29</v>
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
-      <c r="J14" s="9" t="s">
+      <c r="J14" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="K14" s="52" t="s">
+      <c r="K14" s="51" t="s">
         <v>16</v>
       </c>
-      <c r="L14" s="53" t="s">
+      <c r="L14" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="M14" s="63" t="s">
+      <c r="M14" s="62" t="s">
         <v>105</v>
       </c>
-      <c r="N14" s="43" t="s">
+      <c r="N14" s="42" t="s">
         <v>29</v>
       </c>
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
       <c r="Q14" s="1"/>
-      <c r="R14" s="9" t="s">
+      <c r="R14" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="S14" s="52"/>
-      <c r="T14" s="58" t="s">
+      <c r="S14" s="51"/>
+      <c r="T14" s="57" t="s">
         <v>84</v>
       </c>
-      <c r="U14" s="62" t="s">
+      <c r="U14" s="61" t="s">
         <v>131</v>
       </c>
-      <c r="V14" s="21" t="s">
+      <c r="V14" s="20" t="s">
         <v>29</v>
       </c>
       <c r="W14" s="1"/>
@@ -3023,11 +3140,21 @@
       <c r="AD14" s="1"/>
       <c r="AE14" s="1"/>
       <c r="AF14" s="1"/>
-      <c r="AG14" s="1"/>
-      <c r="AH14" s="1"/>
-      <c r="AI14" s="1"/>
-      <c r="AJ14" s="1"/>
-      <c r="AK14" s="1"/>
+      <c r="AG14" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="AH14" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI14" s="57" t="s">
+        <v>224</v>
+      </c>
+      <c r="AJ14" s="88" t="s">
+        <v>248</v>
+      </c>
+      <c r="AK14" s="20" t="s">
+        <v>252</v>
+      </c>
       <c r="AL14" s="1"/>
       <c r="AM14" s="1"/>
       <c r="AN14" s="1"/>
@@ -3067,76 +3194,84 @@
     </row>
     <row r="15" spans="1:73" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="1"/>
-      <c r="B15" s="25" t="s">
+      <c r="B15" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="C15" s="29"/>
-      <c r="D15" s="34" t="s">
+      <c r="C15" s="28"/>
+      <c r="D15" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="34" t="s">
+      <c r="E15" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="F15" s="13" t="s">
+      <c r="F15" s="12" t="s">
         <v>29</v>
       </c>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
-      <c r="J15" s="9" t="s">
+      <c r="J15" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="K15" s="52"/>
-      <c r="L15" s="53" t="s">
+      <c r="K15" s="51"/>
+      <c r="L15" s="52" t="s">
         <v>87</v>
       </c>
-      <c r="M15" s="63" t="s">
+      <c r="M15" s="62" t="s">
         <v>106</v>
       </c>
-      <c r="N15" s="43" t="s">
+      <c r="N15" s="42" t="s">
         <v>29</v>
       </c>
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
       <c r="Q15" s="1"/>
-      <c r="R15" s="9" t="s">
+      <c r="R15" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="S15" s="52" t="s">
+      <c r="S15" s="51" t="s">
         <v>16</v>
       </c>
-      <c r="T15" s="53" t="s">
+      <c r="T15" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="U15" s="63" t="s">
+      <c r="U15" s="62" t="s">
         <v>45</v>
       </c>
-      <c r="V15" s="43" t="s">
+      <c r="V15" s="42" t="s">
         <v>29</v>
       </c>
       <c r="W15" s="1"/>
       <c r="X15" s="1"/>
       <c r="Y15" s="1"/>
-      <c r="Z15" s="46" t="s">
+      <c r="Z15" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="AA15" s="12" t="s">
+      <c r="AA15" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="AB15" s="12" t="s">
+      <c r="AB15" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="AC15" s="48" t="s">
+      <c r="AC15" s="47" t="s">
         <v>3</v>
       </c>
       <c r="AD15" s="1"/>
       <c r="AE15" s="1"/>
       <c r="AF15" s="1"/>
-      <c r="AG15" s="1"/>
-      <c r="AH15" s="1"/>
-      <c r="AI15" s="1"/>
-      <c r="AJ15" s="1"/>
-      <c r="AK15" s="1"/>
+      <c r="AG15" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="AH15" s="51"/>
+      <c r="AI15" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="AJ15" s="52" t="s">
+        <v>249</v>
+      </c>
+      <c r="AK15" s="42" t="s">
+        <v>253</v>
+      </c>
       <c r="AL15" s="1"/>
       <c r="AM15" s="1"/>
       <c r="AN15" s="1"/>
@@ -3174,76 +3309,82 @@
       <c r="BT15" s="1"/>
       <c r="BU15" s="1"/>
     </row>
-    <row r="16" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:73" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="1"/>
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="C16" s="30"/>
-      <c r="D16" s="35" t="s">
+      <c r="C16" s="29"/>
+      <c r="D16" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="E16" s="35" t="s">
+      <c r="E16" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="F16" s="41" t="s">
+      <c r="F16" s="40" t="s">
         <v>29</v>
       </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
-      <c r="J16" s="9" t="s">
+      <c r="J16" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="K16" s="52"/>
-      <c r="L16" s="53" t="s">
+      <c r="K16" s="51"/>
+      <c r="L16" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="M16" s="63" t="s">
+      <c r="M16" s="62" t="s">
         <v>29</v>
       </c>
-      <c r="N16" s="43" t="s">
+      <c r="N16" s="42" t="s">
         <v>29</v>
       </c>
       <c r="O16" s="1"/>
       <c r="P16" s="1"/>
       <c r="Q16" s="1"/>
-      <c r="R16" s="9" t="s">
+      <c r="R16" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="S16" s="52"/>
-      <c r="T16" s="53" t="s">
+      <c r="S16" s="51"/>
+      <c r="T16" s="52" t="s">
         <v>87</v>
       </c>
-      <c r="U16" s="63" t="s">
+      <c r="U16" s="62" t="s">
         <v>132</v>
       </c>
-      <c r="V16" s="43" t="s">
+      <c r="V16" s="42" t="s">
         <v>29</v>
       </c>
       <c r="W16" s="1"/>
       <c r="X16" s="1"/>
       <c r="Y16" s="1"/>
-      <c r="Z16" s="76" t="s">
-        <v>221</v>
-      </c>
-      <c r="AA16" s="86" t="s">
+      <c r="Z16" s="90" t="s">
+        <v>218</v>
+      </c>
+      <c r="AA16" s="78" t="s">
         <v>161</v>
       </c>
-      <c r="AB16" s="90" t="s">
+      <c r="AB16" s="92" t="s">
         <v>163</v>
       </c>
-      <c r="AC16" s="77" t="s">
+      <c r="AC16" s="94" t="s">
         <v>103</v>
       </c>
       <c r="AD16" s="1"/>
       <c r="AE16" s="1"/>
       <c r="AF16" s="1"/>
-      <c r="AG16" s="1"/>
-      <c r="AH16" s="1"/>
-      <c r="AI16" s="1"/>
-      <c r="AJ16" s="1"/>
-      <c r="AK16" s="1"/>
+      <c r="AG16" s="74"/>
+      <c r="AH16" s="72"/>
+      <c r="AI16" s="58" t="s">
+        <v>226</v>
+      </c>
+      <c r="AJ16" s="58" t="s">
+        <v>250</v>
+      </c>
+      <c r="AK16" s="44" t="s">
+        <v>29</v>
+      </c>
       <c r="AL16" s="1"/>
       <c r="AM16" s="1"/>
       <c r="AN16" s="1"/>
@@ -3283,63 +3424,63 @@
     </row>
     <row r="17" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A17" s="1"/>
-      <c r="B17" s="22" t="s">
+      <c r="B17" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="C17" s="30" t="s">
+      <c r="C17" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="D17" s="35" t="s">
+      <c r="D17" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="E17" s="35" t="s">
+      <c r="E17" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="F17" s="41" t="s">
+      <c r="F17" s="40" t="s">
         <v>29</v>
       </c>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="71"/>
-      <c r="L17" s="6" t="s">
+      <c r="J17" s="6"/>
+      <c r="K17" s="70"/>
+      <c r="L17" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="M17" s="64" t="s">
+      <c r="M17" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="N17" s="50" t="s">
+      <c r="N17" s="49" t="s">
         <v>29</v>
       </c>
       <c r="O17" s="1"/>
       <c r="P17" s="1"/>
       <c r="Q17" s="1"/>
-      <c r="R17" s="9"/>
-      <c r="S17" s="52"/>
-      <c r="T17" s="53" t="s">
+      <c r="R17" s="8"/>
+      <c r="S17" s="51"/>
+      <c r="T17" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="U17" s="63" t="s">
+      <c r="U17" s="62" t="s">
         <v>133</v>
       </c>
-      <c r="V17" s="43" t="s">
+      <c r="V17" s="42" t="s">
         <v>135</v>
       </c>
       <c r="W17" s="1"/>
       <c r="X17" s="1"/>
       <c r="Y17" s="1"/>
-      <c r="Z17" s="76"/>
-      <c r="AA17" s="86" t="s">
+      <c r="Z17" s="90"/>
+      <c r="AA17" s="78" t="s">
         <v>165</v>
       </c>
-      <c r="AB17" s="90"/>
-      <c r="AC17" s="77"/>
+      <c r="AB17" s="92"/>
+      <c r="AC17" s="94"/>
       <c r="AD17" s="1"/>
       <c r="AE17" s="1"/>
       <c r="AF17" s="1"/>
-      <c r="AG17" s="1"/>
-      <c r="AH17" s="1"/>
+      <c r="AG17" s="87"/>
+      <c r="AH17" s="87"/>
       <c r="AI17" s="1"/>
       <c r="AJ17" s="1"/>
       <c r="AK17" s="1"/>
@@ -3382,61 +3523,61 @@
     </row>
     <row r="18" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A18" s="1"/>
-      <c r="B18" s="26" t="s">
+      <c r="B18" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="C18" s="31"/>
-      <c r="D18" s="36" t="s">
+      <c r="C18" s="30"/>
+      <c r="D18" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="E18" s="36" t="s">
+      <c r="E18" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="F18" s="16" t="s">
+      <c r="F18" s="15" t="s">
         <v>29</v>
       </c>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="55"/>
-      <c r="L18" s="54" t="s">
+      <c r="J18" s="9"/>
+      <c r="K18" s="54"/>
+      <c r="L18" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="M18" s="65" t="s">
+      <c r="M18" s="64" t="s">
         <v>44</v>
       </c>
-      <c r="N18" s="23" t="s">
+      <c r="N18" s="22" t="s">
         <v>107</v>
       </c>
       <c r="O18" s="1"/>
       <c r="P18" s="1"/>
       <c r="Q18" s="1"/>
-      <c r="R18" s="7"/>
-      <c r="S18" s="71"/>
-      <c r="T18" s="6" t="s">
+      <c r="R18" s="6"/>
+      <c r="S18" s="70"/>
+      <c r="T18" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="U18" s="64" t="s">
+      <c r="U18" s="63" t="s">
         <v>134</v>
       </c>
-      <c r="V18" s="50" t="s">
+      <c r="V18" s="49" t="s">
         <v>136</v>
       </c>
       <c r="W18" s="1"/>
       <c r="X18" s="1"/>
       <c r="Y18" s="1"/>
-      <c r="Z18" s="81"/>
-      <c r="AA18" s="87" t="s">
+      <c r="Z18" s="91"/>
+      <c r="AA18" s="79" t="s">
         <v>162</v>
       </c>
-      <c r="AB18" s="91"/>
-      <c r="AC18" s="82"/>
+      <c r="AB18" s="93"/>
+      <c r="AC18" s="95"/>
       <c r="AD18" s="1"/>
       <c r="AE18" s="1"/>
       <c r="AF18" s="1"/>
-      <c r="AG18" s="1"/>
-      <c r="AH18" s="1"/>
+      <c r="AG18" s="87"/>
+      <c r="AH18" s="87"/>
       <c r="AI18" s="1"/>
       <c r="AJ18" s="1"/>
       <c r="AK18" s="1"/>
@@ -3479,62 +3620,62 @@
     </row>
     <row r="19" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A19" s="1"/>
-      <c r="B19" s="20" t="s">
+      <c r="B19" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="C19" s="28"/>
-      <c r="D19" s="33" t="s">
+      <c r="C19" s="27"/>
+      <c r="D19" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="E19" s="33" t="s">
+      <c r="E19" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="F19" s="40" t="s">
+      <c r="F19" s="39" t="s">
         <v>29</v>
       </c>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
-      <c r="J19" s="10" t="s">
+      <c r="J19" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="K19" s="55"/>
-      <c r="L19" s="54" t="s">
+      <c r="K19" s="54"/>
+      <c r="L19" s="53" t="s">
         <v>14</v>
       </c>
-      <c r="M19" s="65" t="s">
+      <c r="M19" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="N19" s="23" t="s">
+      <c r="N19" s="22" t="s">
         <v>29</v>
       </c>
       <c r="O19" s="1"/>
       <c r="P19" s="1"/>
       <c r="Q19" s="1"/>
-      <c r="R19" s="10"/>
-      <c r="S19" s="55"/>
-      <c r="T19" s="54" t="s">
+      <c r="R19" s="9"/>
+      <c r="S19" s="54"/>
+      <c r="T19" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="U19" s="65" t="s">
+      <c r="U19" s="64" t="s">
         <v>137</v>
       </c>
-      <c r="V19" s="23" t="s">
+      <c r="V19" s="22" t="s">
         <v>29</v>
       </c>
       <c r="W19" s="1"/>
       <c r="X19" s="1"/>
       <c r="Y19" s="1"/>
-      <c r="Z19" s="94" t="s">
-        <v>222</v>
-      </c>
-      <c r="AA19" s="95" t="s">
+      <c r="Z19" s="96" t="s">
+        <v>219</v>
+      </c>
+      <c r="AA19" s="82" t="s">
         <v>161</v>
       </c>
-      <c r="AB19" s="96" t="s">
+      <c r="AB19" s="99" t="s">
         <v>117</v>
       </c>
-      <c r="AC19" s="97" t="s">
+      <c r="AC19" s="102" t="s">
         <v>166</v>
       </c>
       <c r="AD19" s="1"/>
@@ -3584,62 +3725,62 @@
     </row>
     <row r="20" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A20" s="1"/>
-      <c r="B20" s="20" t="s">
+      <c r="B20" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="C20" s="28" t="s">
+      <c r="C20" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="33" t="s">
+      <c r="D20" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="E20" s="33" t="s">
+      <c r="E20" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="F20" s="40" t="s">
+      <c r="F20" s="39" t="s">
         <v>29</v>
       </c>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
-      <c r="J20" s="10" t="s">
+      <c r="J20" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="K20" s="55"/>
-      <c r="L20" s="54" t="s">
+      <c r="K20" s="54"/>
+      <c r="L20" s="53" t="s">
         <v>84</v>
       </c>
-      <c r="M20" s="66" t="s">
+      <c r="M20" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="N20" s="23" t="s">
+      <c r="N20" s="22" t="s">
         <v>29</v>
       </c>
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
       <c r="Q20" s="1"/>
-      <c r="R20" s="10" t="s">
+      <c r="R20" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="S20" s="55"/>
-      <c r="T20" s="54" t="s">
+      <c r="S20" s="54"/>
+      <c r="T20" s="53" t="s">
         <v>14</v>
       </c>
-      <c r="U20" s="65" t="s">
+      <c r="U20" s="64" t="s">
         <v>138</v>
       </c>
-      <c r="V20" s="23" t="s">
+      <c r="V20" s="22" t="s">
         <v>29</v>
       </c>
       <c r="W20" s="1"/>
       <c r="X20" s="1"/>
       <c r="Y20" s="1"/>
-      <c r="Z20" s="98"/>
-      <c r="AA20" s="99" t="s">
+      <c r="Z20" s="97"/>
+      <c r="AA20" s="84" t="s">
         <v>164</v>
       </c>
       <c r="AB20" s="100"/>
-      <c r="AC20" s="101"/>
+      <c r="AC20" s="103"/>
       <c r="AD20" s="1"/>
       <c r="AE20" s="1"/>
       <c r="AF20" s="1"/>
@@ -3687,62 +3828,62 @@
     </row>
     <row r="21" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A21" s="1"/>
-      <c r="B21" s="25" t="s">
+      <c r="B21" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="C21" s="29"/>
-      <c r="D21" s="34" t="s">
+      <c r="C21" s="28"/>
+      <c r="D21" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="E21" s="34" t="s">
+      <c r="E21" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="F21" s="13" t="s">
+      <c r="F21" s="12" t="s">
         <v>29</v>
       </c>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
-      <c r="J21" s="10" t="s">
+      <c r="J21" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="K21" s="55" t="s">
+      <c r="K21" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="L21" s="56" t="s">
+      <c r="L21" s="55" t="s">
         <v>86</v>
       </c>
-      <c r="M21" s="67" t="s">
+      <c r="M21" s="66" t="s">
         <v>29</v>
       </c>
-      <c r="N21" s="44" t="s">
+      <c r="N21" s="43" t="s">
         <v>29</v>
       </c>
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
       <c r="Q21" s="1"/>
-      <c r="R21" s="10" t="s">
+      <c r="R21" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="S21" s="55"/>
-      <c r="T21" s="54" t="s">
+      <c r="S21" s="54"/>
+      <c r="T21" s="53" t="s">
         <v>84</v>
       </c>
-      <c r="U21" s="66" t="s">
+      <c r="U21" s="65" t="s">
         <v>139</v>
       </c>
-      <c r="V21" s="23" t="s">
+      <c r="V21" s="22" t="s">
         <v>29</v>
       </c>
       <c r="W21" s="1"/>
       <c r="X21" s="1"/>
       <c r="Y21" s="1"/>
-      <c r="Z21" s="102"/>
-      <c r="AA21" s="103" t="s">
+      <c r="Z21" s="98"/>
+      <c r="AA21" s="86" t="s">
         <v>162</v>
       </c>
-      <c r="AB21" s="104"/>
-      <c r="AC21" s="105"/>
+      <c r="AB21" s="101"/>
+      <c r="AC21" s="104"/>
       <c r="AD21" s="1"/>
       <c r="AE21" s="1"/>
       <c r="AF21" s="1"/>
@@ -3790,67 +3931,67 @@
     </row>
     <row r="22" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A22" s="1"/>
-      <c r="B22" s="22" t="s">
+      <c r="B22" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="C22" s="30"/>
-      <c r="D22" s="35" t="s">
+      <c r="C22" s="29"/>
+      <c r="D22" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="E22" s="35" t="s">
+      <c r="E22" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="F22" s="41" t="s">
+      <c r="F22" s="40" t="s">
         <v>34</v>
       </c>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
-      <c r="J22" s="10" t="s">
+      <c r="J22" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="K22" s="55"/>
-      <c r="L22" s="56" t="s">
+      <c r="K22" s="54"/>
+      <c r="L22" s="55" t="s">
         <v>87</v>
       </c>
-      <c r="M22" s="67" t="s">
+      <c r="M22" s="66" t="s">
         <v>29</v>
       </c>
-      <c r="N22" s="44" t="s">
+      <c r="N22" s="43" t="s">
         <v>29</v>
       </c>
       <c r="O22" s="1"/>
       <c r="P22" s="1"/>
       <c r="Q22" s="1"/>
-      <c r="R22" s="10" t="s">
+      <c r="R22" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="S22" s="55" t="s">
+      <c r="S22" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="T22" s="56" t="s">
+      <c r="T22" s="55" t="s">
         <v>86</v>
       </c>
-      <c r="U22" s="67" t="s">
+      <c r="U22" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="V22" s="44" t="s">
+      <c r="V22" s="43" t="s">
         <v>143</v>
       </c>
       <c r="W22" s="1"/>
       <c r="X22" s="1"/>
       <c r="Y22" s="1"/>
-      <c r="Z22" s="83" t="s">
-        <v>223</v>
-      </c>
-      <c r="AA22" s="88" t="s">
-        <v>218</v>
-      </c>
-      <c r="AB22" s="92" t="s">
+      <c r="Z22" s="105" t="s">
+        <v>220</v>
+      </c>
+      <c r="AA22" s="80" t="s">
+        <v>215</v>
+      </c>
+      <c r="AB22" s="106" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC22" s="107" t="s">
         <v>217</v>
-      </c>
-      <c r="AC22" s="84" t="s">
-        <v>220</v>
       </c>
       <c r="AD22" s="1"/>
       <c r="AE22" s="1"/>
@@ -3899,62 +4040,62 @@
     </row>
     <row r="23" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A23" s="1"/>
-      <c r="B23" s="22" t="s">
+      <c r="B23" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="C23" s="30" t="s">
+      <c r="C23" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="D23" s="35" t="s">
+      <c r="D23" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="E23" s="35" t="s">
+      <c r="E23" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="F23" s="41" t="s">
+      <c r="F23" s="40" t="s">
         <v>36</v>
       </c>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
-      <c r="J23" s="10" t="s">
+      <c r="J23" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="K23" s="55"/>
-      <c r="L23" s="56" t="s">
+      <c r="K23" s="54"/>
+      <c r="L23" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="M23" s="67" t="s">
+      <c r="M23" s="66" t="s">
         <v>29</v>
       </c>
-      <c r="N23" s="44" t="s">
+      <c r="N23" s="43" t="s">
         <v>29</v>
       </c>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
       <c r="Q23" s="1"/>
-      <c r="R23" s="10" t="s">
+      <c r="R23" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="S23" s="55"/>
-      <c r="T23" s="56" t="s">
+      <c r="S23" s="54"/>
+      <c r="T23" s="55" t="s">
         <v>87</v>
       </c>
-      <c r="U23" s="67" t="s">
+      <c r="U23" s="66" t="s">
         <v>140</v>
       </c>
-      <c r="V23" s="44" t="s">
+      <c r="V23" s="43" t="s">
         <v>29</v>
       </c>
       <c r="W23" s="1"/>
       <c r="X23" s="1"/>
       <c r="Y23" s="1"/>
-      <c r="Z23" s="76"/>
-      <c r="AA23" s="86" t="s">
-        <v>219</v>
-      </c>
-      <c r="AB23" s="90"/>
-      <c r="AC23" s="77"/>
+      <c r="Z23" s="90"/>
+      <c r="AA23" s="78" t="s">
+        <v>216</v>
+      </c>
+      <c r="AB23" s="92"/>
+      <c r="AC23" s="94"/>
       <c r="AD23" s="1"/>
       <c r="AE23" s="1"/>
       <c r="AF23" s="1"/>
@@ -4002,56 +4143,56 @@
     </row>
     <row r="24" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A24" s="1"/>
-      <c r="B24" s="26"/>
-      <c r="C24" s="31"/>
-      <c r="D24" s="36" t="s">
+      <c r="B24" s="25"/>
+      <c r="C24" s="30"/>
+      <c r="D24" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="E24" s="36" t="s">
+      <c r="E24" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="F24" s="16" t="s">
+      <c r="F24" s="15" t="s">
         <v>36</v>
       </c>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
-      <c r="J24" s="11"/>
-      <c r="K24" s="72"/>
-      <c r="L24" s="57" t="s">
+      <c r="J24" s="10"/>
+      <c r="K24" s="71"/>
+      <c r="L24" s="56" t="s">
         <v>88</v>
       </c>
-      <c r="M24" s="68" t="s">
+      <c r="M24" s="67" t="s">
         <v>29</v>
       </c>
-      <c r="N24" s="49" t="s">
+      <c r="N24" s="48" t="s">
         <v>29</v>
       </c>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
       <c r="Q24" s="1"/>
-      <c r="R24" s="10" t="s">
+      <c r="R24" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="S24" s="55"/>
-      <c r="T24" s="56" t="s">
+      <c r="S24" s="54"/>
+      <c r="T24" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="U24" s="67" t="s">
+      <c r="U24" s="66" t="s">
         <v>141</v>
       </c>
-      <c r="V24" s="44" t="s">
+      <c r="V24" s="43" t="s">
         <v>144</v>
       </c>
       <c r="W24" s="1"/>
       <c r="X24" s="1"/>
       <c r="Y24" s="1"/>
-      <c r="Z24" s="81"/>
-      <c r="AA24" s="87" t="s">
+      <c r="Z24" s="91"/>
+      <c r="AA24" s="79" t="s">
         <v>162</v>
       </c>
-      <c r="AB24" s="91"/>
-      <c r="AC24" s="82"/>
+      <c r="AB24" s="93"/>
+      <c r="AC24" s="95"/>
       <c r="AD24" s="1"/>
       <c r="AE24" s="1"/>
       <c r="AF24" s="1"/>
@@ -4099,59 +4240,59 @@
     </row>
     <row r="25" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A25" s="1"/>
-      <c r="B25" s="20"/>
-      <c r="C25" s="28"/>
-      <c r="D25" s="33" t="s">
+      <c r="B25" s="19"/>
+      <c r="C25" s="27"/>
+      <c r="D25" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="E25" s="33" t="s">
+      <c r="E25" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="F25" s="40" t="s">
+      <c r="F25" s="39" t="s">
         <v>29</v>
       </c>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
-      <c r="J25" s="9"/>
-      <c r="K25" s="52"/>
-      <c r="L25" s="58" t="s">
+      <c r="J25" s="8"/>
+      <c r="K25" s="51"/>
+      <c r="L25" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="M25" s="61" t="s">
+      <c r="M25" s="60" t="s">
         <v>33</v>
       </c>
-      <c r="N25" s="21" t="s">
+      <c r="N25" s="20" t="s">
         <v>113</v>
       </c>
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
       <c r="Q25" s="1"/>
-      <c r="R25" s="11"/>
-      <c r="S25" s="72"/>
-      <c r="T25" s="57" t="s">
+      <c r="R25" s="10"/>
+      <c r="S25" s="71"/>
+      <c r="T25" s="56" t="s">
         <v>88</v>
       </c>
-      <c r="U25" s="68" t="s">
+      <c r="U25" s="67" t="s">
         <v>142</v>
       </c>
-      <c r="V25" s="49" t="s">
+      <c r="V25" s="48" t="s">
         <v>145</v>
       </c>
       <c r="W25" s="1"/>
       <c r="X25" s="1"/>
       <c r="Y25" s="1"/>
-      <c r="Z25" s="94" t="s">
-        <v>224</v>
-      </c>
-      <c r="AA25" s="95" t="s">
+      <c r="Z25" s="96" t="s">
+        <v>221</v>
+      </c>
+      <c r="AA25" s="82" t="s">
         <v>169</v>
       </c>
-      <c r="AB25" s="96" t="s">
-        <v>196</v>
-      </c>
-      <c r="AC25" s="97" t="s">
-        <v>207</v>
+      <c r="AB25" s="99" t="s">
+        <v>193</v>
+      </c>
+      <c r="AC25" s="102" t="s">
+        <v>204</v>
       </c>
       <c r="AD25" s="1"/>
       <c r="AE25" s="1"/>
@@ -4200,35 +4341,35 @@
     </row>
     <row r="26" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A26" s="1"/>
-      <c r="B26" s="20" t="s">
+      <c r="B26" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="C26" s="28" t="s">
+      <c r="C26" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="D26" s="33" t="s">
+      <c r="D26" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="E26" s="33" t="s">
+      <c r="E26" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="F26" s="40" t="s">
+      <c r="F26" s="39" t="s">
         <v>29</v>
       </c>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
-      <c r="J26" s="9" t="s">
+      <c r="J26" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="K26" s="52"/>
-      <c r="L26" s="58" t="s">
+      <c r="K26" s="51"/>
+      <c r="L26" s="57" t="s">
         <v>14</v>
       </c>
-      <c r="M26" s="61" t="s">
+      <c r="M26" s="60" t="s">
         <v>108</v>
       </c>
-      <c r="N26" s="21" t="s">
+      <c r="N26" s="20" t="s">
         <v>29</v>
       </c>
       <c r="O26" s="1"/>
@@ -4242,12 +4383,12 @@
       <c r="W26" s="1"/>
       <c r="X26" s="1"/>
       <c r="Y26" s="1"/>
-      <c r="Z26" s="98"/>
-      <c r="AA26" s="99" t="s">
+      <c r="Z26" s="97"/>
+      <c r="AA26" s="84" t="s">
         <v>167</v>
       </c>
       <c r="AB26" s="100"/>
-      <c r="AC26" s="101"/>
+      <c r="AC26" s="103"/>
       <c r="AD26" s="1"/>
       <c r="AE26" s="1"/>
       <c r="AF26" s="1"/>
@@ -4295,37 +4436,37 @@
     </row>
     <row r="27" spans="1:73" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A27" s="1"/>
-      <c r="B27" s="25"/>
-      <c r="C27" s="29"/>
-      <c r="D27" s="34" t="s">
+      <c r="B27" s="24"/>
+      <c r="C27" s="28"/>
+      <c r="D27" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="E27" s="34" t="s">
+      <c r="E27" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="F27" s="13" t="s">
+      <c r="F27" s="12" t="s">
         <v>29</v>
       </c>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
-      <c r="J27" s="9" t="s">
+      <c r="J27" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="K27" s="52"/>
-      <c r="L27" s="58" t="s">
+      <c r="K27" s="51"/>
+      <c r="L27" s="57" t="s">
         <v>84</v>
       </c>
-      <c r="M27" s="62" t="s">
+      <c r="M27" s="61" t="s">
         <v>105</v>
       </c>
-      <c r="N27" s="21" t="s">
+      <c r="N27" s="20" t="s">
         <v>114</v>
       </c>
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
       <c r="Q27" s="1"/>
-      <c r="R27" s="14" t="s">
+      <c r="R27" s="13" t="s">
         <v>73</v>
       </c>
       <c r="S27" s="1"/>
@@ -4335,12 +4476,12 @@
       <c r="W27" s="1"/>
       <c r="X27" s="1"/>
       <c r="Y27" s="1"/>
-      <c r="Z27" s="102"/>
-      <c r="AA27" s="103" t="s">
+      <c r="Z27" s="98"/>
+      <c r="AA27" s="86" t="s">
         <v>168</v>
       </c>
-      <c r="AB27" s="104"/>
-      <c r="AC27" s="105"/>
+      <c r="AB27" s="101"/>
+      <c r="AC27" s="104"/>
       <c r="AD27" s="1"/>
       <c r="AE27" s="1"/>
       <c r="AF27" s="1"/>
@@ -4388,33 +4529,33 @@
     </row>
     <row r="28" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A28" s="1"/>
-      <c r="B28" s="22"/>
-      <c r="C28" s="30"/>
-      <c r="D28" s="35" t="s">
+      <c r="B28" s="21"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="E28" s="35" t="s">
+      <c r="E28" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="F28" s="41" t="s">
+      <c r="F28" s="40" t="s">
         <v>29</v>
       </c>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
-      <c r="J28" s="9" t="s">
+      <c r="J28" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="K28" s="52" t="s">
+      <c r="K28" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="L28" s="53" t="s">
+      <c r="L28" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="M28" s="63" t="s">
+      <c r="M28" s="62" t="s">
         <v>109</v>
       </c>
-      <c r="N28" s="43" t="s">
+      <c r="N28" s="42" t="s">
         <v>115</v>
       </c>
       <c r="O28" s="1"/>
@@ -4430,17 +4571,17 @@
       <c r="W28" s="1"/>
       <c r="X28" s="1"/>
       <c r="Y28" s="1"/>
-      <c r="Z28" s="83" t="s">
-        <v>225</v>
-      </c>
-      <c r="AA28" s="88" t="s">
+      <c r="Z28" s="105" t="s">
+        <v>222</v>
+      </c>
+      <c r="AA28" s="80" t="s">
         <v>169</v>
       </c>
-      <c r="AB28" s="92" t="s">
-        <v>197</v>
-      </c>
-      <c r="AC28" s="84" t="s">
-        <v>208</v>
+      <c r="AB28" s="106" t="s">
+        <v>194</v>
+      </c>
+      <c r="AC28" s="107" t="s">
+        <v>205</v>
       </c>
       <c r="AD28" s="1"/>
       <c r="AE28" s="1"/>
@@ -4489,35 +4630,35 @@
     </row>
     <row r="29" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A29" s="1"/>
-      <c r="B29" s="22" t="s">
+      <c r="B29" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="C29" s="30" t="s">
+      <c r="C29" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="D29" s="35" t="s">
+      <c r="D29" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="E29" s="35" t="s">
+      <c r="E29" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="F29" s="41" t="s">
+      <c r="F29" s="40" t="s">
         <v>29</v>
       </c>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
-      <c r="J29" s="9" t="s">
+      <c r="J29" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="K29" s="52"/>
-      <c r="L29" s="53" t="s">
+      <c r="K29" s="51"/>
+      <c r="L29" s="52" t="s">
         <v>87</v>
       </c>
-      <c r="M29" s="63" t="s">
+      <c r="M29" s="62" t="s">
         <v>110</v>
       </c>
-      <c r="N29" s="43" t="s">
+      <c r="N29" s="42" t="s">
         <v>29</v>
       </c>
       <c r="O29" s="1"/>
@@ -4533,12 +4674,12 @@
       <c r="W29" s="1"/>
       <c r="X29" s="1"/>
       <c r="Y29" s="1"/>
-      <c r="Z29" s="76"/>
-      <c r="AA29" s="86" t="s">
+      <c r="Z29" s="90"/>
+      <c r="AA29" s="78" t="s">
         <v>170</v>
       </c>
-      <c r="AB29" s="90"/>
-      <c r="AC29" s="77"/>
+      <c r="AB29" s="92"/>
+      <c r="AC29" s="94"/>
       <c r="AD29" s="1"/>
       <c r="AE29" s="1"/>
       <c r="AF29" s="1"/>
@@ -4586,31 +4727,31 @@
     </row>
     <row r="30" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A30" s="1"/>
-      <c r="B30" s="26"/>
-      <c r="C30" s="31"/>
-      <c r="D30" s="36" t="s">
+      <c r="B30" s="25"/>
+      <c r="C30" s="30"/>
+      <c r="D30" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="E30" s="36" t="s">
+      <c r="E30" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="F30" s="16" t="s">
+      <c r="F30" s="15" t="s">
         <v>29</v>
       </c>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
-      <c r="J30" s="9" t="s">
+      <c r="J30" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="K30" s="52"/>
-      <c r="L30" s="53" t="s">
+      <c r="K30" s="51"/>
+      <c r="L30" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="M30" s="63" t="s">
+      <c r="M30" s="62" t="s">
         <v>111</v>
       </c>
-      <c r="N30" s="43" t="s">
+      <c r="N30" s="42" t="s">
         <v>116</v>
       </c>
       <c r="O30" s="1"/>
@@ -4626,12 +4767,12 @@
       <c r="W30" s="1"/>
       <c r="X30" s="1"/>
       <c r="Y30" s="1"/>
-      <c r="Z30" s="81"/>
-      <c r="AA30" s="87" t="s">
+      <c r="Z30" s="91"/>
+      <c r="AA30" s="79" t="s">
         <v>168</v>
       </c>
-      <c r="AB30" s="91"/>
-      <c r="AC30" s="82"/>
+      <c r="AB30" s="93"/>
+      <c r="AC30" s="95"/>
       <c r="AD30" s="1"/>
       <c r="AE30" s="1"/>
       <c r="AF30" s="1"/>
@@ -4679,31 +4820,31 @@
     </row>
     <row r="31" spans="1:73" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A31" s="1"/>
-      <c r="B31" s="20" t="s">
+      <c r="B31" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="C31" s="28"/>
-      <c r="D31" s="33" t="s">
+      <c r="C31" s="27"/>
+      <c r="D31" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="E31" s="33" t="s">
+      <c r="E31" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="F31" s="40" t="s">
+      <c r="F31" s="39" t="s">
         <v>29</v>
       </c>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
-      <c r="J31" s="75"/>
-      <c r="K31" s="73"/>
-      <c r="L31" s="59" t="s">
+      <c r="J31" s="74"/>
+      <c r="K31" s="72"/>
+      <c r="L31" s="58" t="s">
         <v>88</v>
       </c>
-      <c r="M31" s="69" t="s">
+      <c r="M31" s="68" t="s">
         <v>112</v>
       </c>
-      <c r="N31" s="45" t="s">
+      <c r="N31" s="44" t="s">
         <v>117</v>
       </c>
       <c r="O31" s="1"/>
@@ -4717,16 +4858,16 @@
       <c r="W31" s="1"/>
       <c r="X31" s="1"/>
       <c r="Y31" s="1"/>
-      <c r="Z31" s="94" t="s">
-        <v>226</v>
-      </c>
-      <c r="AA31" s="95" t="s">
+      <c r="Z31" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="AA31" s="82" t="s">
         <v>174</v>
       </c>
-      <c r="AB31" s="96" t="s">
+      <c r="AB31" s="99" t="s">
         <v>45</v>
       </c>
-      <c r="AC31" s="97" t="s">
+      <c r="AC31" s="102" t="s">
         <v>10</v>
       </c>
       <c r="AD31" s="1"/>
@@ -4776,29 +4917,29 @@
     </row>
     <row r="32" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A32" s="1"/>
-      <c r="B32" s="20" t="s">
+      <c r="B32" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="C32" s="28" t="s">
+      <c r="C32" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="D32" s="33" t="s">
+      <c r="D32" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="E32" s="33" t="s">
+      <c r="E32" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="F32" s="40" t="s">
+      <c r="F32" s="39" t="s">
         <v>29</v>
       </c>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
-      <c r="J32" s="5"/>
-      <c r="K32" s="5"/>
-      <c r="L32" s="5"/>
-      <c r="M32" s="5"/>
-      <c r="N32" s="5"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
       <c r="O32" s="1"/>
       <c r="P32" s="1"/>
       <c r="Q32" s="1"/>
@@ -4810,12 +4951,12 @@
       <c r="W32" s="1"/>
       <c r="X32" s="1"/>
       <c r="Y32" s="1"/>
-      <c r="Z32" s="98"/>
-      <c r="AA32" s="99" t="s">
+      <c r="Z32" s="97"/>
+      <c r="AA32" s="84" t="s">
         <v>175</v>
       </c>
       <c r="AB32" s="100"/>
-      <c r="AC32" s="101"/>
+      <c r="AC32" s="103"/>
       <c r="AD32" s="1"/>
       <c r="AE32" s="1"/>
       <c r="AF32" s="1"/>
@@ -4863,23 +5004,23 @@
     </row>
     <row r="33" spans="1:73" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A33" s="1"/>
-      <c r="B33" s="25" t="s">
+      <c r="B33" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="C33" s="29"/>
-      <c r="D33" s="34" t="s">
+      <c r="C33" s="28"/>
+      <c r="D33" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="E33" s="34" t="s">
+      <c r="E33" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="F33" s="13" t="s">
+      <c r="F33" s="12" t="s">
         <v>29</v>
       </c>
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
-      <c r="J33" s="14" t="s">
+      <c r="J33" s="13" t="s">
         <v>73</v>
       </c>
       <c r="K33" s="1"/>
@@ -4897,12 +5038,12 @@
       <c r="W33" s="1"/>
       <c r="X33" s="1"/>
       <c r="Y33" s="1"/>
-      <c r="Z33" s="102"/>
-      <c r="AA33" s="103" t="s">
+      <c r="Z33" s="98"/>
+      <c r="AA33" s="86" t="s">
         <v>173</v>
       </c>
-      <c r="AB33" s="104"/>
-      <c r="AC33" s="105"/>
+      <c r="AB33" s="101"/>
+      <c r="AC33" s="104"/>
       <c r="AD33" s="1"/>
       <c r="AE33" s="1"/>
       <c r="AF33" s="1"/>
@@ -4950,15 +5091,15 @@
     </row>
     <row r="34" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A34" s="1"/>
-      <c r="B34" s="22"/>
-      <c r="C34" s="30"/>
-      <c r="D34" s="35" t="s">
+      <c r="B34" s="21"/>
+      <c r="C34" s="29"/>
+      <c r="D34" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="E34" s="35" t="s">
+      <c r="E34" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="F34" s="41" t="s">
+      <c r="F34" s="40" t="s">
         <v>29</v>
       </c>
       <c r="G34" s="1"/>
@@ -4982,16 +5123,16 @@
       <c r="W34" s="1"/>
       <c r="X34" s="1"/>
       <c r="Y34" s="1"/>
-      <c r="Z34" s="83" t="s">
-        <v>227</v>
-      </c>
-      <c r="AA34" s="88" t="s">
+      <c r="Z34" s="105" t="s">
+        <v>224</v>
+      </c>
+      <c r="AA34" s="80" t="s">
         <v>171</v>
       </c>
-      <c r="AB34" s="92" t="s">
-        <v>198</v>
-      </c>
-      <c r="AC34" s="84" t="s">
+      <c r="AB34" s="106" t="s">
+        <v>195</v>
+      </c>
+      <c r="AC34" s="107" t="s">
         <v>102</v>
       </c>
       <c r="AD34" s="1"/>
@@ -5041,19 +5182,19 @@
     </row>
     <row r="35" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A35" s="1"/>
-      <c r="B35" s="22" t="s">
+      <c r="B35" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="C35" s="30" t="s">
+      <c r="C35" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="D35" s="35" t="s">
+      <c r="D35" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="E35" s="35" t="s">
+      <c r="E35" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="F35" s="41" t="s">
+      <c r="F35" s="40" t="s">
         <v>29</v>
       </c>
       <c r="G35" s="1"/>
@@ -5075,12 +5216,12 @@
       <c r="W35" s="1"/>
       <c r="X35" s="1"/>
       <c r="Y35" s="1"/>
-      <c r="Z35" s="76"/>
-      <c r="AA35" s="86" t="s">
+      <c r="Z35" s="90"/>
+      <c r="AA35" s="78" t="s">
         <v>172</v>
       </c>
-      <c r="AB35" s="90"/>
-      <c r="AC35" s="77"/>
+      <c r="AB35" s="92"/>
+      <c r="AC35" s="94"/>
       <c r="AD35" s="1"/>
       <c r="AE35" s="1"/>
       <c r="AF35" s="1"/>
@@ -5128,15 +5269,15 @@
     </row>
     <row r="36" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A36" s="1"/>
-      <c r="B36" s="26"/>
-      <c r="C36" s="31"/>
-      <c r="D36" s="36" t="s">
+      <c r="B36" s="25"/>
+      <c r="C36" s="30"/>
+      <c r="D36" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="E36" s="36" t="s">
+      <c r="E36" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="F36" s="16" t="s">
+      <c r="F36" s="15" t="s">
         <v>29</v>
       </c>
       <c r="G36" s="1"/>
@@ -5158,12 +5299,12 @@
       <c r="W36" s="1"/>
       <c r="X36" s="1"/>
       <c r="Y36" s="1"/>
-      <c r="Z36" s="81"/>
-      <c r="AA36" s="87" t="s">
+      <c r="Z36" s="91"/>
+      <c r="AA36" s="79" t="s">
         <v>173</v>
       </c>
-      <c r="AB36" s="91"/>
-      <c r="AC36" s="82"/>
+      <c r="AB36" s="93"/>
+      <c r="AC36" s="95"/>
       <c r="AD36" s="1"/>
       <c r="AE36" s="1"/>
       <c r="AF36" s="1"/>
@@ -5211,17 +5352,17 @@
     </row>
     <row r="37" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A37" s="1"/>
-      <c r="B37" s="20" t="s">
+      <c r="B37" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="C37" s="28"/>
-      <c r="D37" s="33" t="s">
+      <c r="C37" s="27"/>
+      <c r="D37" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="E37" s="33" t="s">
+      <c r="E37" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="F37" s="40" t="s">
+      <c r="F37" s="39" t="s">
         <v>40</v>
       </c>
       <c r="G37" s="1"/>
@@ -5243,17 +5384,17 @@
       <c r="W37" s="1"/>
       <c r="X37" s="1"/>
       <c r="Y37" s="1"/>
-      <c r="Z37" s="94" t="s">
-        <v>228</v>
-      </c>
-      <c r="AA37" s="95" t="s">
+      <c r="Z37" s="96" t="s">
+        <v>225</v>
+      </c>
+      <c r="AA37" s="82" t="s">
         <v>176</v>
       </c>
-      <c r="AB37" s="96" t="s">
-        <v>199</v>
-      </c>
-      <c r="AC37" s="97" t="s">
-        <v>209</v>
+      <c r="AB37" s="99" t="s">
+        <v>196</v>
+      </c>
+      <c r="AC37" s="102" t="s">
+        <v>206</v>
       </c>
       <c r="AD37" s="1"/>
       <c r="AE37" s="1"/>
@@ -5302,19 +5443,19 @@
     </row>
     <row r="38" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A38" s="1"/>
-      <c r="B38" s="20" t="s">
+      <c r="B38" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="C38" s="28" t="s">
+      <c r="C38" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="D38" s="33" t="s">
+      <c r="D38" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="E38" s="33" t="s">
+      <c r="E38" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="F38" s="40" t="s">
+      <c r="F38" s="39" t="s">
         <v>10</v>
       </c>
       <c r="G38" s="1"/>
@@ -5336,12 +5477,12 @@
       <c r="W38" s="1"/>
       <c r="X38" s="1"/>
       <c r="Y38" s="1"/>
-      <c r="Z38" s="98"/>
-      <c r="AA38" s="99" t="s">
+      <c r="Z38" s="97"/>
+      <c r="AA38" s="84" t="s">
         <v>177</v>
       </c>
       <c r="AB38" s="100"/>
-      <c r="AC38" s="101"/>
+      <c r="AC38" s="103"/>
       <c r="AD38" s="1"/>
       <c r="AE38" s="1"/>
       <c r="AF38" s="1"/>
@@ -5389,17 +5530,17 @@
     </row>
     <row r="39" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A39" s="1"/>
-      <c r="B39" s="25" t="s">
+      <c r="B39" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="C39" s="29"/>
-      <c r="D39" s="34" t="s">
+      <c r="C39" s="28"/>
+      <c r="D39" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="E39" s="34" t="s">
+      <c r="E39" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="F39" s="13" t="s">
+      <c r="F39" s="12" t="s">
         <v>43</v>
       </c>
       <c r="G39" s="1"/>
@@ -5421,12 +5562,12 @@
       <c r="W39" s="1"/>
       <c r="X39" s="1"/>
       <c r="Y39" s="1"/>
-      <c r="Z39" s="102"/>
-      <c r="AA39" s="103" t="s">
+      <c r="Z39" s="98"/>
+      <c r="AA39" s="86" t="s">
         <v>178</v>
       </c>
-      <c r="AB39" s="104"/>
-      <c r="AC39" s="105"/>
+      <c r="AB39" s="101"/>
+      <c r="AC39" s="104"/>
       <c r="AD39" s="1"/>
       <c r="AE39" s="1"/>
       <c r="AF39" s="1"/>
@@ -5474,17 +5615,17 @@
     </row>
     <row r="40" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A40" s="1"/>
-      <c r="B40" s="22" t="s">
+      <c r="B40" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="C40" s="30"/>
-      <c r="D40" s="35" t="s">
+      <c r="C40" s="29"/>
+      <c r="D40" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="E40" s="35" t="s">
+      <c r="E40" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="F40" s="41" t="s">
+      <c r="F40" s="40" t="s">
         <v>29</v>
       </c>
       <c r="G40" s="1"/>
@@ -5506,17 +5647,17 @@
       <c r="W40" s="1"/>
       <c r="X40" s="1"/>
       <c r="Y40" s="1"/>
-      <c r="Z40" s="83" t="s">
-        <v>229</v>
-      </c>
-      <c r="AA40" s="88" t="s">
+      <c r="Z40" s="105" t="s">
+        <v>226</v>
+      </c>
+      <c r="AA40" s="80" t="s">
         <v>179</v>
       </c>
-      <c r="AB40" s="92" t="s">
-        <v>200</v>
-      </c>
-      <c r="AC40" s="84" t="s">
-        <v>210</v>
+      <c r="AB40" s="106" t="s">
+        <v>197</v>
+      </c>
+      <c r="AC40" s="107" t="s">
+        <v>207</v>
       </c>
       <c r="AD40" s="1"/>
       <c r="AE40" s="1"/>
@@ -5565,19 +5706,19 @@
     </row>
     <row r="41" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A41" s="1"/>
-      <c r="B41" s="22" t="s">
+      <c r="B41" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="C41" s="30" t="s">
+      <c r="C41" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="D41" s="35" t="s">
+      <c r="D41" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="E41" s="35" t="s">
+      <c r="E41" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="F41" s="41" t="s">
+      <c r="F41" s="40" t="s">
         <v>29</v>
       </c>
       <c r="G41" s="1"/>
@@ -5599,12 +5740,12 @@
       <c r="W41" s="1"/>
       <c r="X41" s="1"/>
       <c r="Y41" s="1"/>
-      <c r="Z41" s="76"/>
-      <c r="AA41" s="86" t="s">
+      <c r="Z41" s="90"/>
+      <c r="AA41" s="78" t="s">
         <v>180</v>
       </c>
-      <c r="AB41" s="90"/>
-      <c r="AC41" s="77"/>
+      <c r="AB41" s="92"/>
+      <c r="AC41" s="94"/>
       <c r="AD41" s="1"/>
       <c r="AE41" s="1"/>
       <c r="AF41" s="1"/>
@@ -5652,17 +5793,17 @@
     </row>
     <row r="42" spans="1:73" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A42" s="1"/>
-      <c r="B42" s="24" t="s">
+      <c r="B42" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="C42" s="32"/>
-      <c r="D42" s="37" t="s">
+      <c r="C42" s="31"/>
+      <c r="D42" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="E42" s="37" t="s">
+      <c r="E42" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="F42" s="42" t="s">
+      <c r="F42" s="41" t="s">
         <v>29</v>
       </c>
       <c r="G42" s="1"/>
@@ -5684,12 +5825,12 @@
       <c r="W42" s="1"/>
       <c r="X42" s="1"/>
       <c r="Y42" s="1"/>
-      <c r="Z42" s="81"/>
-      <c r="AA42" s="87" t="s">
+      <c r="Z42" s="91"/>
+      <c r="AA42" s="79" t="s">
         <v>181</v>
       </c>
-      <c r="AB42" s="91"/>
-      <c r="AC42" s="82"/>
+      <c r="AB42" s="93"/>
+      <c r="AC42" s="95"/>
       <c r="AD42" s="1"/>
       <c r="AE42" s="1"/>
       <c r="AF42" s="1"/>
@@ -5761,17 +5902,17 @@
       <c r="W43" s="1"/>
       <c r="X43" s="1"/>
       <c r="Y43" s="1"/>
-      <c r="Z43" s="106" t="s">
-        <v>182</v>
-      </c>
-      <c r="AA43" s="95" t="s">
-        <v>184</v>
-      </c>
-      <c r="AB43" s="96" t="s">
-        <v>201</v>
-      </c>
-      <c r="AC43" s="97" t="s">
-        <v>211</v>
+      <c r="Z43" s="83" t="s">
+        <v>238</v>
+      </c>
+      <c r="AA43" s="82" t="s">
+        <v>183</v>
+      </c>
+      <c r="AB43" s="99" t="s">
+        <v>198</v>
+      </c>
+      <c r="AC43" s="102" t="s">
+        <v>208</v>
       </c>
       <c r="AD43" s="1"/>
       <c r="AE43" s="1"/>
@@ -5820,7 +5961,7 @@
     </row>
     <row r="44" spans="1:73" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A44" s="1"/>
-      <c r="B44" s="14" t="s">
+      <c r="B44" s="13" t="s">
         <v>73</v>
       </c>
       <c r="C44" s="1"/>
@@ -5846,14 +5987,14 @@
       <c r="W44" s="1"/>
       <c r="X44" s="1"/>
       <c r="Y44" s="1"/>
-      <c r="Z44" s="106" t="s">
-        <v>183</v>
-      </c>
-      <c r="AA44" s="99" t="s">
-        <v>185</v>
+      <c r="Z44" s="83" t="s">
+        <v>182</v>
+      </c>
+      <c r="AA44" s="84" t="s">
+        <v>184</v>
       </c>
       <c r="AB44" s="100"/>
-      <c r="AC44" s="101"/>
+      <c r="AC44" s="103"/>
       <c r="AD44" s="1"/>
       <c r="AE44" s="1"/>
       <c r="AF44" s="1"/>
@@ -5927,12 +6068,12 @@
       <c r="W45" s="1"/>
       <c r="X45" s="1"/>
       <c r="Y45" s="1"/>
-      <c r="Z45" s="107"/>
-      <c r="AA45" s="103" t="s">
-        <v>186</v>
-      </c>
-      <c r="AB45" s="104"/>
-      <c r="AC45" s="105"/>
+      <c r="Z45" s="85"/>
+      <c r="AA45" s="86" t="s">
+        <v>185</v>
+      </c>
+      <c r="AB45" s="101"/>
+      <c r="AC45" s="104"/>
       <c r="AD45" s="1"/>
       <c r="AE45" s="1"/>
       <c r="AF45" s="1"/>
@@ -6006,17 +6147,17 @@
       <c r="W46" s="1"/>
       <c r="X46" s="1"/>
       <c r="Y46" s="1"/>
-      <c r="Z46" s="78" t="s">
-        <v>182</v>
-      </c>
-      <c r="AA46" s="88" t="s">
-        <v>187</v>
-      </c>
-      <c r="AB46" s="92" t="s">
+      <c r="Z46" s="75" t="s">
+        <v>239</v>
+      </c>
+      <c r="AA46" s="80" t="s">
+        <v>186</v>
+      </c>
+      <c r="AB46" s="106" t="s">
         <v>134</v>
       </c>
-      <c r="AC46" s="84" t="s">
-        <v>212</v>
+      <c r="AC46" s="107" t="s">
+        <v>209</v>
       </c>
       <c r="AD46" s="1"/>
       <c r="AE46" s="1"/>
@@ -6091,14 +6232,14 @@
       <c r="W47" s="1"/>
       <c r="X47" s="1"/>
       <c r="Y47" s="1"/>
-      <c r="Z47" s="78" t="s">
-        <v>183</v>
-      </c>
-      <c r="AA47" s="86" t="s">
-        <v>185</v>
-      </c>
-      <c r="AB47" s="90"/>
-      <c r="AC47" s="77"/>
+      <c r="Z47" s="75" t="s">
+        <v>182</v>
+      </c>
+      <c r="AA47" s="78" t="s">
+        <v>184</v>
+      </c>
+      <c r="AB47" s="92"/>
+      <c r="AC47" s="94"/>
       <c r="AD47" s="1"/>
       <c r="AE47" s="1"/>
       <c r="AF47" s="1"/>
@@ -6172,12 +6313,12 @@
       <c r="W48" s="1"/>
       <c r="X48" s="1"/>
       <c r="Y48" s="1"/>
-      <c r="Z48" s="85"/>
-      <c r="AA48" s="87" t="s">
-        <v>186</v>
-      </c>
-      <c r="AB48" s="91"/>
-      <c r="AC48" s="82"/>
+      <c r="Z48" s="77"/>
+      <c r="AA48" s="79" t="s">
+        <v>185</v>
+      </c>
+      <c r="AB48" s="93"/>
+      <c r="AC48" s="95"/>
       <c r="AD48" s="1"/>
       <c r="AE48" s="1"/>
       <c r="AF48" s="1"/>
@@ -6249,17 +6390,17 @@
       <c r="W49" s="1"/>
       <c r="X49" s="1"/>
       <c r="Y49" s="1"/>
-      <c r="Z49" s="106" t="s">
-        <v>230</v>
-      </c>
-      <c r="AA49" s="95" t="s">
-        <v>188</v>
-      </c>
-      <c r="AB49" s="96" t="s">
+      <c r="Z49" s="83" t="s">
+        <v>240</v>
+      </c>
+      <c r="AA49" s="82" t="s">
+        <v>187</v>
+      </c>
+      <c r="AB49" s="99" t="s">
         <v>28</v>
       </c>
-      <c r="AC49" s="97" t="s">
-        <v>213</v>
+      <c r="AC49" s="102" t="s">
+        <v>210</v>
       </c>
       <c r="AD49" s="1"/>
       <c r="AE49" s="1"/>
@@ -6332,14 +6473,14 @@
       <c r="W50" s="1"/>
       <c r="X50" s="1"/>
       <c r="Y50" s="1"/>
-      <c r="Z50" s="106" t="s">
-        <v>195</v>
-      </c>
-      <c r="AA50" s="99" t="s">
-        <v>185</v>
+      <c r="Z50" s="83" t="s">
+        <v>192</v>
+      </c>
+      <c r="AA50" s="84" t="s">
+        <v>184</v>
       </c>
       <c r="AB50" s="100"/>
-      <c r="AC50" s="101"/>
+      <c r="AC50" s="103"/>
       <c r="AD50" s="1"/>
       <c r="AE50" s="1"/>
       <c r="AF50" s="1"/>
@@ -6411,12 +6552,12 @@
       <c r="W51" s="1"/>
       <c r="X51" s="1"/>
       <c r="Y51" s="1"/>
-      <c r="Z51" s="107"/>
-      <c r="AA51" s="103" t="s">
-        <v>186</v>
-      </c>
-      <c r="AB51" s="104"/>
-      <c r="AC51" s="105"/>
+      <c r="Z51" s="85"/>
+      <c r="AA51" s="86" t="s">
+        <v>185</v>
+      </c>
+      <c r="AB51" s="101"/>
+      <c r="AC51" s="104"/>
       <c r="AD51" s="1"/>
       <c r="AE51" s="1"/>
       <c r="AF51" s="1"/>
@@ -6488,17 +6629,17 @@
       <c r="W52" s="1"/>
       <c r="X52" s="1"/>
       <c r="Y52" s="1"/>
-      <c r="Z52" s="78" t="s">
-        <v>230</v>
-      </c>
-      <c r="AA52" s="88" t="s">
-        <v>189</v>
-      </c>
-      <c r="AB52" s="92" t="s">
-        <v>202</v>
-      </c>
-      <c r="AC52" s="84" t="s">
-        <v>214</v>
+      <c r="Z52" s="75" t="s">
+        <v>241</v>
+      </c>
+      <c r="AA52" s="80" t="s">
+        <v>188</v>
+      </c>
+      <c r="AB52" s="106" t="s">
+        <v>199</v>
+      </c>
+      <c r="AC52" s="107" t="s">
+        <v>211</v>
       </c>
       <c r="AD52" s="1"/>
       <c r="AE52" s="1"/>
@@ -6571,14 +6712,14 @@
       <c r="W53" s="1"/>
       <c r="X53" s="1"/>
       <c r="Y53" s="1"/>
-      <c r="Z53" s="78" t="s">
-        <v>195</v>
-      </c>
-      <c r="AA53" s="86" t="s">
-        <v>185</v>
-      </c>
-      <c r="AB53" s="90"/>
-      <c r="AC53" s="77"/>
+      <c r="Z53" s="75" t="s">
+        <v>192</v>
+      </c>
+      <c r="AA53" s="78" t="s">
+        <v>184</v>
+      </c>
+      <c r="AB53" s="92"/>
+      <c r="AC53" s="94"/>
       <c r="AD53" s="1"/>
       <c r="AE53" s="1"/>
       <c r="AF53" s="1"/>
@@ -6650,12 +6791,12 @@
       <c r="W54" s="1"/>
       <c r="X54" s="1"/>
       <c r="Y54" s="1"/>
-      <c r="Z54" s="85"/>
-      <c r="AA54" s="87" t="s">
-        <v>186</v>
-      </c>
-      <c r="AB54" s="91"/>
-      <c r="AC54" s="82"/>
+      <c r="Z54" s="77"/>
+      <c r="AA54" s="79" t="s">
+        <v>185</v>
+      </c>
+      <c r="AB54" s="93"/>
+      <c r="AC54" s="95"/>
       <c r="AD54" s="1"/>
       <c r="AE54" s="1"/>
       <c r="AF54" s="1"/>
@@ -6727,17 +6868,17 @@
       <c r="W55" s="1"/>
       <c r="X55" s="1"/>
       <c r="Y55" s="1"/>
-      <c r="Z55" s="106" t="s">
-        <v>190</v>
-      </c>
-      <c r="AA55" s="95" t="s">
-        <v>191</v>
-      </c>
-      <c r="AB55" s="96" t="s">
-        <v>203</v>
-      </c>
-      <c r="AC55" s="97" t="s">
-        <v>215</v>
+      <c r="Z55" s="83" t="s">
+        <v>242</v>
+      </c>
+      <c r="AA55" s="82" t="s">
+        <v>189</v>
+      </c>
+      <c r="AB55" s="99" t="s">
+        <v>200</v>
+      </c>
+      <c r="AC55" s="102" t="s">
+        <v>212</v>
       </c>
       <c r="AD55" s="1"/>
       <c r="AE55" s="1"/>
@@ -6810,14 +6951,14 @@
       <c r="W56" s="1"/>
       <c r="X56" s="1"/>
       <c r="Y56" s="1"/>
-      <c r="Z56" s="106" t="s">
-        <v>183</v>
-      </c>
-      <c r="AA56" s="99" t="s">
-        <v>192</v>
+      <c r="Z56" s="83" t="s">
+        <v>182</v>
+      </c>
+      <c r="AA56" s="84" t="s">
+        <v>190</v>
       </c>
       <c r="AB56" s="100"/>
-      <c r="AC56" s="101"/>
+      <c r="AC56" s="103"/>
       <c r="AD56" s="1"/>
       <c r="AE56" s="1"/>
       <c r="AF56" s="1"/>
@@ -6889,10 +7030,10 @@
       <c r="W57" s="1"/>
       <c r="X57" s="1"/>
       <c r="Y57" s="1"/>
-      <c r="Z57" s="107"/>
-      <c r="AA57" s="103"/>
-      <c r="AB57" s="104"/>
-      <c r="AC57" s="105"/>
+      <c r="Z57" s="85"/>
+      <c r="AA57" s="86"/>
+      <c r="AB57" s="101"/>
+      <c r="AC57" s="104"/>
       <c r="AD57" s="1"/>
       <c r="AE57" s="1"/>
       <c r="AF57" s="1"/>
@@ -6964,17 +7105,17 @@
       <c r="W58" s="1"/>
       <c r="X58" s="1"/>
       <c r="Y58" s="1"/>
-      <c r="Z58" s="78" t="s">
-        <v>190</v>
-      </c>
-      <c r="AA58" s="88" t="s">
-        <v>193</v>
-      </c>
-      <c r="AB58" s="92" t="s">
-        <v>204</v>
-      </c>
-      <c r="AC58" s="84" t="s">
-        <v>216</v>
+      <c r="Z58" s="75" t="s">
+        <v>244</v>
+      </c>
+      <c r="AA58" s="80" t="s">
+        <v>191</v>
+      </c>
+      <c r="AB58" s="106" t="s">
+        <v>201</v>
+      </c>
+      <c r="AC58" s="107" t="s">
+        <v>213</v>
       </c>
       <c r="AD58" s="1"/>
       <c r="AE58" s="1"/>
@@ -7047,14 +7188,14 @@
       <c r="W59" s="1"/>
       <c r="X59" s="1"/>
       <c r="Y59" s="1"/>
-      <c r="Z59" s="78" t="s">
-        <v>183</v>
-      </c>
-      <c r="AA59" s="86" t="s">
-        <v>192</v>
-      </c>
-      <c r="AB59" s="90"/>
-      <c r="AC59" s="77"/>
+      <c r="Z59" s="75" t="s">
+        <v>182</v>
+      </c>
+      <c r="AA59" s="78" t="s">
+        <v>190</v>
+      </c>
+      <c r="AB59" s="92"/>
+      <c r="AC59" s="94"/>
       <c r="AD59" s="1"/>
       <c r="AE59" s="1"/>
       <c r="AF59" s="1"/>
@@ -7126,10 +7267,10 @@
       <c r="W60" s="1"/>
       <c r="X60" s="1"/>
       <c r="Y60" s="1"/>
-      <c r="Z60" s="85"/>
-      <c r="AA60" s="87"/>
-      <c r="AB60" s="91"/>
-      <c r="AC60" s="82"/>
+      <c r="Z60" s="77"/>
+      <c r="AA60" s="79"/>
+      <c r="AB60" s="93"/>
+      <c r="AC60" s="95"/>
       <c r="AD60" s="1"/>
       <c r="AE60" s="1"/>
       <c r="AF60" s="1"/>
@@ -7201,17 +7342,17 @@
       <c r="W61" s="1"/>
       <c r="X61" s="1"/>
       <c r="Y61" s="1"/>
-      <c r="Z61" s="106" t="s">
-        <v>194</v>
-      </c>
-      <c r="AA61" s="95" t="s">
-        <v>188</v>
-      </c>
-      <c r="AB61" s="96" t="s">
-        <v>205</v>
-      </c>
-      <c r="AC61" s="97" t="s">
-        <v>215</v>
+      <c r="Z61" s="83" t="s">
+        <v>243</v>
+      </c>
+      <c r="AA61" s="82" t="s">
+        <v>187</v>
+      </c>
+      <c r="AB61" s="99" t="s">
+        <v>202</v>
+      </c>
+      <c r="AC61" s="102" t="s">
+        <v>212</v>
       </c>
       <c r="AD61" s="1"/>
       <c r="AE61" s="1"/>
@@ -7284,14 +7425,14 @@
       <c r="W62" s="1"/>
       <c r="X62" s="1"/>
       <c r="Y62" s="1"/>
-      <c r="Z62" s="106" t="s">
-        <v>195</v>
-      </c>
-      <c r="AA62" s="99" t="s">
+      <c r="Z62" s="83" t="s">
         <v>192</v>
       </c>
+      <c r="AA62" s="84" t="s">
+        <v>190</v>
+      </c>
       <c r="AB62" s="100"/>
-      <c r="AC62" s="101"/>
+      <c r="AC62" s="103"/>
       <c r="AD62" s="1"/>
       <c r="AE62" s="1"/>
       <c r="AF62" s="1"/>
@@ -7363,10 +7504,10 @@
       <c r="W63" s="1"/>
       <c r="X63" s="1"/>
       <c r="Y63" s="1"/>
-      <c r="Z63" s="107"/>
-      <c r="AA63" s="103"/>
-      <c r="AB63" s="104"/>
-      <c r="AC63" s="105"/>
+      <c r="Z63" s="85"/>
+      <c r="AA63" s="86"/>
+      <c r="AB63" s="101"/>
+      <c r="AC63" s="104"/>
       <c r="AD63" s="1"/>
       <c r="AE63" s="1"/>
       <c r="AF63" s="1"/>
@@ -7438,17 +7579,17 @@
       <c r="W64" s="1"/>
       <c r="X64" s="1"/>
       <c r="Y64" s="1"/>
-      <c r="Z64" s="78" t="s">
-        <v>194</v>
-      </c>
-      <c r="AA64" s="86" t="s">
-        <v>189</v>
-      </c>
-      <c r="AB64" s="90" t="s">
-        <v>206</v>
-      </c>
-      <c r="AC64" s="77" t="s">
-        <v>216</v>
+      <c r="Z64" s="75" t="s">
+        <v>245</v>
+      </c>
+      <c r="AA64" s="78" t="s">
+        <v>188</v>
+      </c>
+      <c r="AB64" s="92" t="s">
+        <v>203</v>
+      </c>
+      <c r="AC64" s="94" t="s">
+        <v>213</v>
       </c>
       <c r="AD64" s="1"/>
       <c r="AE64" s="1"/>
@@ -7521,14 +7662,14 @@
       <c r="W65" s="1"/>
       <c r="X65" s="1"/>
       <c r="Y65" s="1"/>
-      <c r="Z65" s="78" t="s">
-        <v>195</v>
-      </c>
-      <c r="AA65" s="86" t="s">
+      <c r="Z65" s="75" t="s">
         <v>192</v>
       </c>
-      <c r="AB65" s="90"/>
-      <c r="AC65" s="77"/>
+      <c r="AA65" s="78" t="s">
+        <v>190</v>
+      </c>
+      <c r="AB65" s="92"/>
+      <c r="AC65" s="94"/>
       <c r="AD65" s="1"/>
       <c r="AE65" s="1"/>
       <c r="AF65" s="1"/>
@@ -7600,10 +7741,10 @@
       <c r="W66" s="1"/>
       <c r="X66" s="1"/>
       <c r="Y66" s="1"/>
-      <c r="Z66" s="79"/>
-      <c r="AA66" s="89"/>
-      <c r="AB66" s="93"/>
-      <c r="AC66" s="80"/>
+      <c r="Z66" s="76"/>
+      <c r="AA66" s="81"/>
+      <c r="AB66" s="108"/>
+      <c r="AC66" s="109"/>
       <c r="AD66" s="1"/>
       <c r="AE66" s="1"/>
       <c r="AF66" s="1"/>
@@ -7750,7 +7891,7 @@
       <c r="W68" s="1"/>
       <c r="X68" s="1"/>
       <c r="Y68" s="1"/>
-      <c r="Z68" s="14" t="s">
+      <c r="Z68" s="13" t="s">
         <v>73</v>
       </c>
       <c r="AA68" s="1"/>
@@ -7827,7 +7968,9 @@
       <c r="W69" s="1"/>
       <c r="X69" s="1"/>
       <c r="Y69" s="1"/>
-      <c r="Z69" s="1"/>
+      <c r="Z69" s="1" t="s">
+        <v>227</v>
+      </c>
       <c r="AA69" s="1"/>
       <c r="AB69" s="1"/>
       <c r="AC69" s="1"/>
@@ -7902,7 +8045,9 @@
       <c r="W70" s="1"/>
       <c r="X70" s="1"/>
       <c r="Y70" s="1"/>
-      <c r="Z70" s="1"/>
+      <c r="Z70" s="1" t="s">
+        <v>228</v>
+      </c>
       <c r="AA70" s="1"/>
       <c r="AB70" s="1"/>
       <c r="AC70" s="1"/>
@@ -38357,7 +38502,7 @@
       <c r="BU476" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="47">
+  <mergeCells count="45">
     <mergeCell ref="AB64:AB66"/>
     <mergeCell ref="AC64:AC66"/>
     <mergeCell ref="Z22:Z24"/>
@@ -38398,13 +38543,11 @@
     <mergeCell ref="Z25:Z27"/>
     <mergeCell ref="AB25:AB27"/>
     <mergeCell ref="AC25:AC27"/>
-    <mergeCell ref="Z3:AG3"/>
-    <mergeCell ref="Z4:AG4"/>
+    <mergeCell ref="R3:Y3"/>
+    <mergeCell ref="R4:Y4"/>
     <mergeCell ref="Z16:Z18"/>
     <mergeCell ref="AB16:AB18"/>
     <mergeCell ref="AC16:AC18"/>
-    <mergeCell ref="R3:Y3"/>
-    <mergeCell ref="R4:Y4"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/results.xlsx
+++ b/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utilizador\Desktop\uni\MEI 1ano1sem\DAA\trabalho\DAA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54769D0E-843A-4EB0-85CC-EA843817E8F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22213A50-5106-428B-8CA5-533593317BCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="14020" xr2:uid="{744B1543-7C44-49C5-883E-AA14D96B6E1A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="281">
   <si>
     <t>DAA tests and results</t>
   </si>
@@ -719,21 +719,6 @@
     <t>LightGBM1</t>
   </si>
   <si>
-    <t>None of the models provide super stable results, but some are interesting</t>
-  </si>
-  <si>
-    <t>Next step is to perfom more agressive oversampling</t>
-  </si>
-  <si>
-    <t>Fifth batch of tests - Oversampling without Dimensionality</t>
-  </si>
-  <si>
-    <t>Considering the last batche's results weren't completely inconsistent,</t>
-  </si>
-  <si>
-    <t>It's probably worth it to test na agressive way of oversampling again.</t>
-  </si>
-  <si>
     <t>In this batch, data treatment is the same as in the fourth besides for the oversampling.</t>
   </si>
   <si>
@@ -798,6 +783,102 @@
   </si>
   <si>
     <t>0.311</t>
+  </si>
+  <si>
+    <t>0.351</t>
+  </si>
+  <si>
+    <t>Considering the last batch's results weren't completely inconsistent,</t>
+  </si>
+  <si>
+    <t>It's probably worth it to test an agressive way of oversampling again.</t>
+  </si>
+  <si>
+    <t>majority class</t>
+  </si>
+  <si>
+    <t>Fifth batch of tests - Agressive oversampling without Dimensionality</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reduction and feature selection. We did this because the results obtained at batch 3 are </t>
+  </si>
+  <si>
+    <t>too inconsistent. We want to confirm if it is normal or there was any error while measuring</t>
+  </si>
+  <si>
+    <t>them</t>
+  </si>
+  <si>
+    <t>&gt;&gt;&gt;None of the models provide super stable results, but some are interesting</t>
+  </si>
+  <si>
+    <t>&gt;&gt;&gt;Next step is to perfom more agressive oversampling</t>
+  </si>
+  <si>
+    <t>&gt;&gt;&gt;These models don't provide stable results either</t>
+  </si>
+  <si>
+    <t>&gt;&gt;&gt;While it might seem counter-productive, the next step is to test this with dimensionality</t>
+  </si>
+  <si>
+    <t>Sixth batch of tests - Agressive oversampling with Dimensionality</t>
+  </si>
+  <si>
+    <t>As explained in the fifth batch's conclusions part, we want to double check the</t>
+  </si>
+  <si>
+    <t>results obtained on the third batch.</t>
+  </si>
+  <si>
+    <t>We are using last batch's oversampling paramethers (class2 by 0.33 of majority class</t>
+  </si>
+  <si>
+    <t>and all others by 1.0 of majority class). Nothing changed on the data treatment part,</t>
+  </si>
+  <si>
+    <t>besides for adding dimensionality reduction and feature selection.</t>
+  </si>
+  <si>
+    <t>ANOVA (200)</t>
+  </si>
+  <si>
+    <t>+</t>
+  </si>
+  <si>
+    <t>PCA (100)</t>
+  </si>
+  <si>
+    <t>0.474</t>
+  </si>
+  <si>
+    <t>0.604</t>
+  </si>
+  <si>
+    <t>0.368</t>
+  </si>
+  <si>
+    <t>0.450</t>
+  </si>
+  <si>
+    <t>0.574</t>
+  </si>
+  <si>
+    <t>0.572</t>
+  </si>
+  <si>
+    <t>0.545</t>
+  </si>
+  <si>
+    <t>0.569</t>
+  </si>
+  <si>
+    <t>dimensionality reduction and feature selection description</t>
+  </si>
+  <si>
+    <t>0.28</t>
+  </si>
+  <si>
+    <t>0.380</t>
   </si>
 </sst>
 </file>
@@ -882,7 +963,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="35">
+  <borders count="36">
     <border>
       <left/>
       <right/>
@@ -1286,11 +1367,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="110">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1516,8 +1612,20 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1525,25 +1633,16 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1564,21 +1663,23 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1882,14 +1983,16 @@
   <dimension ref="A1:BU476"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="19.90625" customWidth="1"/>
-    <col min="10" max="10" width="17.08984375" customWidth="1"/>
+    <col min="2" max="2" width="19.81640625" customWidth="1"/>
+    <col min="10" max="10" width="17.1796875" customWidth="1"/>
     <col min="18" max="18" width="19.1796875" customWidth="1"/>
     <col min="25" max="25" width="8.7265625" customWidth="1"/>
-    <col min="26" max="26" width="16.90625" customWidth="1"/>
+    <col min="26" max="26" width="16.81640625" customWidth="1"/>
     <col min="27" max="27" width="73.7265625" customWidth="1"/>
     <col min="33" max="33" width="23.453125" customWidth="1"/>
     <col min="35" max="35" width="18.1796875" customWidth="1"/>
+    <col min="41" max="41" width="49.54296875" customWidth="1"/>
+    <col min="43" max="43" width="15.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:73" x14ac:dyDescent="0.35">
@@ -2066,16 +2169,16 @@
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
-      <c r="R3" s="89" t="s">
+      <c r="R3" s="109" t="s">
         <v>119</v>
       </c>
-      <c r="S3" s="89"/>
-      <c r="T3" s="89"/>
-      <c r="U3" s="89"/>
-      <c r="V3" s="89"/>
-      <c r="W3" s="89"/>
-      <c r="X3" s="89"/>
-      <c r="Y3" s="89"/>
+      <c r="S3" s="109"/>
+      <c r="T3" s="109"/>
+      <c r="U3" s="109"/>
+      <c r="V3" s="109"/>
+      <c r="W3" s="109"/>
+      <c r="X3" s="109"/>
+      <c r="Y3" s="109"/>
       <c r="Z3" s="73" t="s">
         <v>149</v>
       </c>
@@ -2086,7 +2189,7 @@
       <c r="AE3" s="73"/>
       <c r="AF3" s="73"/>
       <c r="AG3" s="73" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="AH3" s="73"/>
       <c r="AI3" s="1"/>
@@ -2095,8 +2198,10 @@
       <c r="AL3" s="1"/>
       <c r="AM3" s="1"/>
       <c r="AN3" s="1"/>
-      <c r="AO3" s="1"/>
-      <c r="AP3" s="1"/>
+      <c r="AO3" s="73" t="s">
+        <v>261</v>
+      </c>
+      <c r="AP3" s="73"/>
       <c r="AQ3" s="1"/>
       <c r="AR3" s="1"/>
       <c r="AS3" s="1"/>
@@ -2129,7 +2234,7 @@
       <c r="BT3" s="1"/>
       <c r="BU3" s="1"/>
     </row>
-    <row r="4" spans="1:73" ht="15.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:73" ht="15.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="1"/>
       <c r="B4" s="4" t="s">
         <v>47</v>
@@ -2151,16 +2256,16 @@
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
-      <c r="R4" s="89" t="s">
+      <c r="R4" s="109" t="s">
         <v>120</v>
       </c>
-      <c r="S4" s="89"/>
-      <c r="T4" s="89"/>
-      <c r="U4" s="89"/>
-      <c r="V4" s="89"/>
-      <c r="W4" s="89"/>
-      <c r="X4" s="89"/>
-      <c r="Y4" s="89"/>
+      <c r="S4" s="109"/>
+      <c r="T4" s="109"/>
+      <c r="U4" s="109"/>
+      <c r="V4" s="109"/>
+      <c r="W4" s="109"/>
+      <c r="X4" s="109"/>
+      <c r="Y4" s="109"/>
       <c r="Z4" s="73" t="s">
         <v>150</v>
       </c>
@@ -2180,8 +2285,10 @@
       <c r="AL4" s="1"/>
       <c r="AM4" s="1"/>
       <c r="AN4" s="1"/>
-      <c r="AO4" s="1"/>
-      <c r="AP4" s="1"/>
+      <c r="AO4" s="73" t="s">
+        <v>150</v>
+      </c>
+      <c r="AP4" s="73"/>
       <c r="AQ4" s="1"/>
       <c r="AR4" s="1"/>
       <c r="AS4" s="1"/>
@@ -2254,7 +2361,7 @@
       <c r="AE5" s="1"/>
       <c r="AF5" s="1"/>
       <c r="AG5" s="4" t="s">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="AH5" s="1"/>
       <c r="AI5" s="1"/>
@@ -2263,7 +2370,9 @@
       <c r="AL5" s="1"/>
       <c r="AM5" s="1"/>
       <c r="AN5" s="1"/>
-      <c r="AO5" s="1"/>
+      <c r="AO5" s="4" t="s">
+        <v>262</v>
+      </c>
       <c r="AP5" s="1"/>
       <c r="AQ5" s="1"/>
       <c r="AR5" s="1"/>
@@ -2347,7 +2456,7 @@
       <c r="AE6" s="1"/>
       <c r="AF6" s="1"/>
       <c r="AG6" s="1" t="s">
-        <v>231</v>
+        <v>251</v>
       </c>
       <c r="AH6" s="1"/>
       <c r="AI6" s="1"/>
@@ -2356,7 +2465,9 @@
       <c r="AL6" s="1"/>
       <c r="AM6" s="1"/>
       <c r="AN6" s="1"/>
-      <c r="AO6" s="1"/>
+      <c r="AO6" s="1" t="s">
+        <v>263</v>
+      </c>
       <c r="AP6" s="1"/>
       <c r="AQ6" s="1"/>
       <c r="AR6" s="1"/>
@@ -2436,7 +2547,7 @@
       <c r="AE7" s="1"/>
       <c r="AF7" s="1"/>
       <c r="AG7" s="1" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="AH7" s="1"/>
       <c r="AI7" s="1"/>
@@ -2445,7 +2556,9 @@
       <c r="AL7" s="1"/>
       <c r="AM7" s="1"/>
       <c r="AN7" s="1"/>
-      <c r="AO7" s="1"/>
+      <c r="AO7" s="1" t="s">
+        <v>264</v>
+      </c>
       <c r="AP7" s="1"/>
       <c r="AQ7" s="1"/>
       <c r="AR7" s="1"/>
@@ -2529,7 +2642,7 @@
       <c r="AE8" s="1"/>
       <c r="AF8" s="1"/>
       <c r="AG8" s="1" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="AH8" s="1"/>
       <c r="AI8" s="1"/>
@@ -2538,7 +2651,9 @@
       <c r="AL8" s="1"/>
       <c r="AM8" s="1"/>
       <c r="AN8" s="1"/>
-      <c r="AO8" s="1"/>
+      <c r="AO8" s="1" t="s">
+        <v>265</v>
+      </c>
       <c r="AP8" s="1"/>
       <c r="AQ8" s="1"/>
       <c r="AR8" s="1"/>
@@ -2616,7 +2731,7 @@
       <c r="AE9" s="1"/>
       <c r="AF9" s="1"/>
       <c r="AG9" s="1" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="AH9" s="1"/>
       <c r="AI9" s="1"/>
@@ -2625,7 +2740,9 @@
       <c r="AL9" s="1"/>
       <c r="AM9" s="1"/>
       <c r="AN9" s="1"/>
-      <c r="AO9" s="1"/>
+      <c r="AO9" s="1" t="s">
+        <v>266</v>
+      </c>
       <c r="AP9" s="1"/>
       <c r="AQ9" s="1"/>
       <c r="AR9" s="1"/>
@@ -2833,11 +2950,21 @@
       <c r="AL11" s="1"/>
       <c r="AM11" s="1"/>
       <c r="AN11" s="1"/>
-      <c r="AO11" s="1"/>
-      <c r="AP11" s="1"/>
-      <c r="AQ11" s="1"/>
-      <c r="AR11" s="1"/>
-      <c r="AS11" s="1"/>
+      <c r="AO11" s="110" t="s">
+        <v>278</v>
+      </c>
+      <c r="AP11" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="AQ11" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="AR11" s="59" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS11" s="47" t="s">
+        <v>3</v>
+      </c>
       <c r="AT11" s="1"/>
       <c r="AU11" s="1"/>
       <c r="AV11" s="1"/>
@@ -2927,22 +3054,28 @@
       <c r="AG12" s="7"/>
       <c r="AH12" s="69"/>
       <c r="AI12" s="50" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AJ12" s="50" t="s">
+        <v>241</v>
+      </c>
+      <c r="AK12" s="20" t="s">
         <v>246</v>
-      </c>
-      <c r="AK12" s="20" t="s">
-        <v>251</v>
       </c>
       <c r="AL12" s="1"/>
       <c r="AM12" s="1"/>
       <c r="AN12" s="1"/>
-      <c r="AO12" s="1"/>
-      <c r="AP12" s="1"/>
-      <c r="AQ12" s="1"/>
-      <c r="AR12" s="1"/>
-      <c r="AS12" s="1"/>
+      <c r="AO12" s="8"/>
+      <c r="AP12" s="51"/>
+      <c r="AQ12" s="57" t="s">
+        <v>220</v>
+      </c>
+      <c r="AR12" s="60" t="s">
+        <v>270</v>
+      </c>
+      <c r="AS12" s="20" t="s">
+        <v>279</v>
+      </c>
       <c r="AT12" s="1"/>
       <c r="AU12" s="1"/>
       <c r="AV12" s="1"/>
@@ -3030,14 +3163,14 @@
       <c r="AE13" s="1"/>
       <c r="AF13" s="1"/>
       <c r="AG13" s="8" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="AH13" s="51"/>
       <c r="AI13" s="57" t="s">
         <v>222</v>
       </c>
       <c r="AJ13" s="57" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="AK13" s="20" t="s">
         <v>213</v>
@@ -3045,11 +3178,17 @@
       <c r="AL13" s="1"/>
       <c r="AM13" s="1"/>
       <c r="AN13" s="1"/>
-      <c r="AO13" s="1"/>
-      <c r="AP13" s="1"/>
-      <c r="AQ13" s="1"/>
-      <c r="AR13" s="1"/>
-      <c r="AS13" s="1"/>
+      <c r="AO13" s="8"/>
+      <c r="AP13" s="51"/>
+      <c r="AQ13" s="57" t="s">
+        <v>222</v>
+      </c>
+      <c r="AR13" s="60" t="s">
+        <v>28</v>
+      </c>
+      <c r="AS13" s="20" t="s">
+        <v>280</v>
+      </c>
       <c r="AT13" s="1"/>
       <c r="AU13" s="1"/>
       <c r="AV13" s="1"/>
@@ -3141,7 +3280,7 @@
       <c r="AE14" s="1"/>
       <c r="AF14" s="1"/>
       <c r="AG14" s="8" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="AH14" s="51" t="s">
         <v>16</v>
@@ -3150,19 +3289,23 @@
         <v>224</v>
       </c>
       <c r="AJ14" s="88" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="AK14" s="20" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="AL14" s="1"/>
       <c r="AM14" s="1"/>
       <c r="AN14" s="1"/>
-      <c r="AO14" s="1"/>
-      <c r="AP14" s="1"/>
-      <c r="AQ14" s="1"/>
-      <c r="AR14" s="1"/>
-      <c r="AS14" s="1"/>
+      <c r="AO14" s="8"/>
+      <c r="AP14" s="51"/>
+      <c r="AQ14" s="57" t="s">
+        <v>224</v>
+      </c>
+      <c r="AR14" s="61" t="s">
+        <v>271</v>
+      </c>
+      <c r="AS14" s="20"/>
       <c r="AT14" s="1"/>
       <c r="AU14" s="1"/>
       <c r="AV14" s="1"/>
@@ -3260,26 +3403,32 @@
       <c r="AE15" s="1"/>
       <c r="AF15" s="1"/>
       <c r="AG15" s="8" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AH15" s="51"/>
       <c r="AI15" s="52" t="s">
         <v>225</v>
       </c>
       <c r="AJ15" s="52" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="AK15" s="42" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="AL15" s="1"/>
       <c r="AM15" s="1"/>
       <c r="AN15" s="1"/>
-      <c r="AO15" s="1"/>
-      <c r="AP15" s="1"/>
-      <c r="AQ15" s="1"/>
-      <c r="AR15" s="1"/>
-      <c r="AS15" s="1"/>
+      <c r="AO15" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="AP15" s="51"/>
+      <c r="AQ15" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="AR15" s="62" t="s">
+        <v>272</v>
+      </c>
+      <c r="AS15" s="42"/>
       <c r="AT15" s="1"/>
       <c r="AU15" s="1"/>
       <c r="AV15" s="1"/>
@@ -3359,40 +3508,50 @@
       <c r="W16" s="1"/>
       <c r="X16" s="1"/>
       <c r="Y16" s="1"/>
-      <c r="Z16" s="90" t="s">
+      <c r="Z16" s="94" t="s">
         <v>218</v>
       </c>
       <c r="AA16" s="78" t="s">
         <v>161</v>
       </c>
-      <c r="AB16" s="92" t="s">
+      <c r="AB16" s="89" t="s">
         <v>163</v>
       </c>
-      <c r="AC16" s="94" t="s">
+      <c r="AC16" s="91" t="s">
         <v>103</v>
       </c>
       <c r="AD16" s="1"/>
       <c r="AE16" s="1"/>
       <c r="AF16" s="1"/>
-      <c r="AG16" s="74"/>
+      <c r="AG16" s="74" t="s">
+        <v>252</v>
+      </c>
       <c r="AH16" s="72"/>
       <c r="AI16" s="58" t="s">
         <v>226</v>
       </c>
       <c r="AJ16" s="58" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="AK16" s="44" t="s">
-        <v>29</v>
+        <v>249</v>
       </c>
       <c r="AL16" s="1"/>
       <c r="AM16" s="1"/>
       <c r="AN16" s="1"/>
-      <c r="AO16" s="1"/>
-      <c r="AP16" s="1"/>
-      <c r="AQ16" s="1"/>
-      <c r="AR16" s="1"/>
-      <c r="AS16" s="1"/>
+      <c r="AO16" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="AP16" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="AQ16" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="AR16" s="62" t="s">
+        <v>273</v>
+      </c>
+      <c r="AS16" s="42"/>
       <c r="AT16" s="1"/>
       <c r="AU16" s="1"/>
       <c r="AV16" s="1"/>
@@ -3470,12 +3629,12 @@
       <c r="W17" s="1"/>
       <c r="X17" s="1"/>
       <c r="Y17" s="1"/>
-      <c r="Z17" s="90"/>
+      <c r="Z17" s="94"/>
       <c r="AA17" s="78" t="s">
         <v>165</v>
       </c>
-      <c r="AB17" s="92"/>
-      <c r="AC17" s="94"/>
+      <c r="AB17" s="89"/>
+      <c r="AC17" s="91"/>
       <c r="AD17" s="1"/>
       <c r="AE17" s="1"/>
       <c r="AF17" s="1"/>
@@ -3487,11 +3646,17 @@
       <c r="AL17" s="1"/>
       <c r="AM17" s="1"/>
       <c r="AN17" s="1"/>
-      <c r="AO17" s="1"/>
-      <c r="AP17" s="1"/>
-      <c r="AQ17" s="1"/>
-      <c r="AR17" s="1"/>
-      <c r="AS17" s="1"/>
+      <c r="AO17" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="AP17" s="52"/>
+      <c r="AQ17" s="52" t="s">
+        <v>234</v>
+      </c>
+      <c r="AR17" s="62" t="s">
+        <v>274</v>
+      </c>
+      <c r="AS17" s="42"/>
       <c r="AT17" s="1"/>
       <c r="AU17" s="1"/>
       <c r="AV17" s="1"/>
@@ -3521,7 +3686,7 @@
       <c r="BT17" s="1"/>
       <c r="BU17" s="1"/>
     </row>
-    <row r="18" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:73" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A18" s="1"/>
       <c r="B18" s="25" t="s">
         <v>57</v>
@@ -3567,16 +3732,18 @@
       <c r="W18" s="1"/>
       <c r="X18" s="1"/>
       <c r="Y18" s="1"/>
-      <c r="Z18" s="91"/>
+      <c r="Z18" s="95"/>
       <c r="AA18" s="79" t="s">
         <v>162</v>
       </c>
-      <c r="AB18" s="93"/>
-      <c r="AC18" s="95"/>
+      <c r="AB18" s="97"/>
+      <c r="AC18" s="99"/>
       <c r="AD18" s="1"/>
       <c r="AE18" s="1"/>
       <c r="AF18" s="1"/>
-      <c r="AG18" s="87"/>
+      <c r="AG18" s="13" t="s">
+        <v>73</v>
+      </c>
       <c r="AH18" s="87"/>
       <c r="AI18" s="1"/>
       <c r="AJ18" s="1"/>
@@ -3584,11 +3751,15 @@
       <c r="AL18" s="1"/>
       <c r="AM18" s="1"/>
       <c r="AN18" s="1"/>
-      <c r="AO18" s="1"/>
-      <c r="AP18" s="1"/>
-      <c r="AQ18" s="1"/>
-      <c r="AR18" s="1"/>
-      <c r="AS18" s="1"/>
+      <c r="AO18" s="111"/>
+      <c r="AP18" s="52"/>
+      <c r="AQ18" s="52" t="s">
+        <v>236</v>
+      </c>
+      <c r="AR18" s="62" t="s">
+        <v>275</v>
+      </c>
+      <c r="AS18" s="42"/>
       <c r="AT18" s="1"/>
       <c r="AU18" s="1"/>
       <c r="AV18" s="1"/>
@@ -3666,22 +3837,24 @@
       <c r="W19" s="1"/>
       <c r="X19" s="1"/>
       <c r="Y19" s="1"/>
-      <c r="Z19" s="96" t="s">
+      <c r="Z19" s="106" t="s">
         <v>219</v>
       </c>
       <c r="AA19" s="82" t="s">
         <v>161</v>
       </c>
-      <c r="AB19" s="99" t="s">
+      <c r="AB19" s="100" t="s">
         <v>117</v>
       </c>
-      <c r="AC19" s="102" t="s">
+      <c r="AC19" s="103" t="s">
         <v>166</v>
       </c>
       <c r="AD19" s="1"/>
       <c r="AE19" s="1"/>
       <c r="AF19" s="1"/>
-      <c r="AG19" s="1"/>
+      <c r="AG19" s="1" t="s">
+        <v>259</v>
+      </c>
       <c r="AH19" s="1"/>
       <c r="AI19" s="1"/>
       <c r="AJ19" s="1"/>
@@ -3689,11 +3862,15 @@
       <c r="AL19" s="1"/>
       <c r="AM19" s="1"/>
       <c r="AN19" s="1"/>
-      <c r="AO19" s="1"/>
-      <c r="AP19" s="1"/>
-      <c r="AQ19" s="1"/>
-      <c r="AR19" s="1"/>
-      <c r="AS19" s="1"/>
+      <c r="AO19" s="111"/>
+      <c r="AP19" s="52"/>
+      <c r="AQ19" s="52" t="s">
+        <v>239</v>
+      </c>
+      <c r="AR19" s="62" t="s">
+        <v>276</v>
+      </c>
+      <c r="AS19" s="42"/>
       <c r="AT19" s="1"/>
       <c r="AU19" s="1"/>
       <c r="AV19" s="1"/>
@@ -3723,7 +3900,7 @@
       <c r="BT19" s="1"/>
       <c r="BU19" s="1"/>
     </row>
-    <row r="20" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:73" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="1"/>
       <c r="B20" s="19" t="s">
         <v>56</v>
@@ -3775,16 +3952,18 @@
       <c r="W20" s="1"/>
       <c r="X20" s="1"/>
       <c r="Y20" s="1"/>
-      <c r="Z20" s="97"/>
+      <c r="Z20" s="107"/>
       <c r="AA20" s="84" t="s">
         <v>164</v>
       </c>
-      <c r="AB20" s="100"/>
-      <c r="AC20" s="103"/>
+      <c r="AB20" s="101"/>
+      <c r="AC20" s="104"/>
       <c r="AD20" s="1"/>
       <c r="AE20" s="1"/>
       <c r="AF20" s="1"/>
-      <c r="AG20" s="1"/>
+      <c r="AG20" s="1" t="s">
+        <v>260</v>
+      </c>
       <c r="AH20" s="1"/>
       <c r="AI20" s="1"/>
       <c r="AJ20" s="1"/>
@@ -3792,11 +3971,15 @@
       <c r="AL20" s="1"/>
       <c r="AM20" s="1"/>
       <c r="AN20" s="1"/>
-      <c r="AO20" s="1"/>
-      <c r="AP20" s="1"/>
-      <c r="AQ20" s="1"/>
-      <c r="AR20" s="1"/>
-      <c r="AS20" s="1"/>
+      <c r="AO20" s="112"/>
+      <c r="AP20" s="58"/>
+      <c r="AQ20" s="58" t="s">
+        <v>240</v>
+      </c>
+      <c r="AR20" s="68" t="s">
+        <v>277</v>
+      </c>
+      <c r="AS20" s="44"/>
       <c r="AT20" s="1"/>
       <c r="AU20" s="1"/>
       <c r="AV20" s="1"/>
@@ -3878,16 +4061,18 @@
       <c r="W21" s="1"/>
       <c r="X21" s="1"/>
       <c r="Y21" s="1"/>
-      <c r="Z21" s="98"/>
+      <c r="Z21" s="108"/>
       <c r="AA21" s="86" t="s">
         <v>162</v>
       </c>
-      <c r="AB21" s="101"/>
-      <c r="AC21" s="104"/>
+      <c r="AB21" s="102"/>
+      <c r="AC21" s="105"/>
       <c r="AD21" s="1"/>
       <c r="AE21" s="1"/>
       <c r="AF21" s="1"/>
-      <c r="AG21" s="1"/>
+      <c r="AG21" s="1" t="s">
+        <v>254</v>
+      </c>
       <c r="AH21" s="1"/>
       <c r="AI21" s="1"/>
       <c r="AJ21" s="1"/>
@@ -3981,22 +4166,24 @@
       <c r="W22" s="1"/>
       <c r="X22" s="1"/>
       <c r="Y22" s="1"/>
-      <c r="Z22" s="105" t="s">
+      <c r="Z22" s="93" t="s">
         <v>220</v>
       </c>
       <c r="AA22" s="80" t="s">
         <v>215</v>
       </c>
-      <c r="AB22" s="106" t="s">
+      <c r="AB22" s="96" t="s">
         <v>214</v>
       </c>
-      <c r="AC22" s="107" t="s">
+      <c r="AC22" s="98" t="s">
         <v>217</v>
       </c>
       <c r="AD22" s="1"/>
       <c r="AE22" s="1"/>
       <c r="AF22" s="1"/>
-      <c r="AG22" s="1"/>
+      <c r="AG22" s="1" t="s">
+        <v>255</v>
+      </c>
       <c r="AH22" s="1"/>
       <c r="AI22" s="1"/>
       <c r="AJ22" s="1"/>
@@ -4090,16 +4277,18 @@
       <c r="W23" s="1"/>
       <c r="X23" s="1"/>
       <c r="Y23" s="1"/>
-      <c r="Z23" s="90"/>
+      <c r="Z23" s="94"/>
       <c r="AA23" s="78" t="s">
         <v>216</v>
       </c>
-      <c r="AB23" s="92"/>
-      <c r="AC23" s="94"/>
+      <c r="AB23" s="89"/>
+      <c r="AC23" s="91"/>
       <c r="AD23" s="1"/>
       <c r="AE23" s="1"/>
       <c r="AF23" s="1"/>
-      <c r="AG23" s="1"/>
+      <c r="AG23" s="1" t="s">
+        <v>256</v>
+      </c>
       <c r="AH23" s="1"/>
       <c r="AI23" s="1"/>
       <c r="AJ23" s="1"/>
@@ -4187,12 +4376,12 @@
       <c r="W24" s="1"/>
       <c r="X24" s="1"/>
       <c r="Y24" s="1"/>
-      <c r="Z24" s="91"/>
+      <c r="Z24" s="95"/>
       <c r="AA24" s="79" t="s">
         <v>162</v>
       </c>
-      <c r="AB24" s="93"/>
-      <c r="AC24" s="95"/>
+      <c r="AB24" s="97"/>
+      <c r="AC24" s="99"/>
       <c r="AD24" s="1"/>
       <c r="AE24" s="1"/>
       <c r="AF24" s="1"/>
@@ -4282,16 +4471,16 @@
       <c r="W25" s="1"/>
       <c r="X25" s="1"/>
       <c r="Y25" s="1"/>
-      <c r="Z25" s="96" t="s">
+      <c r="Z25" s="106" t="s">
         <v>221</v>
       </c>
       <c r="AA25" s="82" t="s">
         <v>169</v>
       </c>
-      <c r="AB25" s="99" t="s">
+      <c r="AB25" s="100" t="s">
         <v>193</v>
       </c>
-      <c r="AC25" s="102" t="s">
+      <c r="AC25" s="103" t="s">
         <v>204</v>
       </c>
       <c r="AD25" s="1"/>
@@ -4383,12 +4572,12 @@
       <c r="W26" s="1"/>
       <c r="X26" s="1"/>
       <c r="Y26" s="1"/>
-      <c r="Z26" s="97"/>
+      <c r="Z26" s="107"/>
       <c r="AA26" s="84" t="s">
         <v>167</v>
       </c>
-      <c r="AB26" s="100"/>
-      <c r="AC26" s="103"/>
+      <c r="AB26" s="101"/>
+      <c r="AC26" s="104"/>
       <c r="AD26" s="1"/>
       <c r="AE26" s="1"/>
       <c r="AF26" s="1"/>
@@ -4476,12 +4665,12 @@
       <c r="W27" s="1"/>
       <c r="X27" s="1"/>
       <c r="Y27" s="1"/>
-      <c r="Z27" s="98"/>
+      <c r="Z27" s="108"/>
       <c r="AA27" s="86" t="s">
         <v>168</v>
       </c>
-      <c r="AB27" s="101"/>
-      <c r="AC27" s="104"/>
+      <c r="AB27" s="102"/>
+      <c r="AC27" s="105"/>
       <c r="AD27" s="1"/>
       <c r="AE27" s="1"/>
       <c r="AF27" s="1"/>
@@ -4571,16 +4760,16 @@
       <c r="W28" s="1"/>
       <c r="X28" s="1"/>
       <c r="Y28" s="1"/>
-      <c r="Z28" s="105" t="s">
+      <c r="Z28" s="93" t="s">
         <v>222</v>
       </c>
       <c r="AA28" s="80" t="s">
         <v>169</v>
       </c>
-      <c r="AB28" s="106" t="s">
+      <c r="AB28" s="96" t="s">
         <v>194</v>
       </c>
-      <c r="AC28" s="107" t="s">
+      <c r="AC28" s="98" t="s">
         <v>205</v>
       </c>
       <c r="AD28" s="1"/>
@@ -4674,12 +4863,12 @@
       <c r="W29" s="1"/>
       <c r="X29" s="1"/>
       <c r="Y29" s="1"/>
-      <c r="Z29" s="90"/>
+      <c r="Z29" s="94"/>
       <c r="AA29" s="78" t="s">
         <v>170</v>
       </c>
-      <c r="AB29" s="92"/>
-      <c r="AC29" s="94"/>
+      <c r="AB29" s="89"/>
+      <c r="AC29" s="91"/>
       <c r="AD29" s="1"/>
       <c r="AE29" s="1"/>
       <c r="AF29" s="1"/>
@@ -4767,12 +4956,12 @@
       <c r="W30" s="1"/>
       <c r="X30" s="1"/>
       <c r="Y30" s="1"/>
-      <c r="Z30" s="91"/>
+      <c r="Z30" s="95"/>
       <c r="AA30" s="79" t="s">
         <v>168</v>
       </c>
-      <c r="AB30" s="93"/>
-      <c r="AC30" s="95"/>
+      <c r="AB30" s="97"/>
+      <c r="AC30" s="99"/>
       <c r="AD30" s="1"/>
       <c r="AE30" s="1"/>
       <c r="AF30" s="1"/>
@@ -4858,16 +5047,16 @@
       <c r="W31" s="1"/>
       <c r="X31" s="1"/>
       <c r="Y31" s="1"/>
-      <c r="Z31" s="96" t="s">
+      <c r="Z31" s="106" t="s">
         <v>223</v>
       </c>
       <c r="AA31" s="82" t="s">
         <v>174</v>
       </c>
-      <c r="AB31" s="99" t="s">
+      <c r="AB31" s="100" t="s">
         <v>45</v>
       </c>
-      <c r="AC31" s="102" t="s">
+      <c r="AC31" s="103" t="s">
         <v>10</v>
       </c>
       <c r="AD31" s="1"/>
@@ -4951,12 +5140,12 @@
       <c r="W32" s="1"/>
       <c r="X32" s="1"/>
       <c r="Y32" s="1"/>
-      <c r="Z32" s="97"/>
+      <c r="Z32" s="107"/>
       <c r="AA32" s="84" t="s">
         <v>175</v>
       </c>
-      <c r="AB32" s="100"/>
-      <c r="AC32" s="103"/>
+      <c r="AB32" s="101"/>
+      <c r="AC32" s="104"/>
       <c r="AD32" s="1"/>
       <c r="AE32" s="1"/>
       <c r="AF32" s="1"/>
@@ -5038,12 +5227,12 @@
       <c r="W33" s="1"/>
       <c r="X33" s="1"/>
       <c r="Y33" s="1"/>
-      <c r="Z33" s="98"/>
+      <c r="Z33" s="108"/>
       <c r="AA33" s="86" t="s">
         <v>173</v>
       </c>
-      <c r="AB33" s="101"/>
-      <c r="AC33" s="104"/>
+      <c r="AB33" s="102"/>
+      <c r="AC33" s="105"/>
       <c r="AD33" s="1"/>
       <c r="AE33" s="1"/>
       <c r="AF33" s="1"/>
@@ -5123,16 +5312,16 @@
       <c r="W34" s="1"/>
       <c r="X34" s="1"/>
       <c r="Y34" s="1"/>
-      <c r="Z34" s="105" t="s">
+      <c r="Z34" s="93" t="s">
         <v>224</v>
       </c>
       <c r="AA34" s="80" t="s">
         <v>171</v>
       </c>
-      <c r="AB34" s="106" t="s">
+      <c r="AB34" s="96" t="s">
         <v>195</v>
       </c>
-      <c r="AC34" s="107" t="s">
+      <c r="AC34" s="98" t="s">
         <v>102</v>
       </c>
       <c r="AD34" s="1"/>
@@ -5216,12 +5405,12 @@
       <c r="W35" s="1"/>
       <c r="X35" s="1"/>
       <c r="Y35" s="1"/>
-      <c r="Z35" s="90"/>
+      <c r="Z35" s="94"/>
       <c r="AA35" s="78" t="s">
         <v>172</v>
       </c>
-      <c r="AB35" s="92"/>
-      <c r="AC35" s="94"/>
+      <c r="AB35" s="89"/>
+      <c r="AC35" s="91"/>
       <c r="AD35" s="1"/>
       <c r="AE35" s="1"/>
       <c r="AF35" s="1"/>
@@ -5299,12 +5488,12 @@
       <c r="W36" s="1"/>
       <c r="X36" s="1"/>
       <c r="Y36" s="1"/>
-      <c r="Z36" s="91"/>
+      <c r="Z36" s="95"/>
       <c r="AA36" s="79" t="s">
         <v>173</v>
       </c>
-      <c r="AB36" s="93"/>
-      <c r="AC36" s="95"/>
+      <c r="AB36" s="97"/>
+      <c r="AC36" s="99"/>
       <c r="AD36" s="1"/>
       <c r="AE36" s="1"/>
       <c r="AF36" s="1"/>
@@ -5384,16 +5573,16 @@
       <c r="W37" s="1"/>
       <c r="X37" s="1"/>
       <c r="Y37" s="1"/>
-      <c r="Z37" s="96" t="s">
+      <c r="Z37" s="106" t="s">
         <v>225</v>
       </c>
       <c r="AA37" s="82" t="s">
         <v>176</v>
       </c>
-      <c r="AB37" s="99" t="s">
+      <c r="AB37" s="100" t="s">
         <v>196</v>
       </c>
-      <c r="AC37" s="102" t="s">
+      <c r="AC37" s="103" t="s">
         <v>206</v>
       </c>
       <c r="AD37" s="1"/>
@@ -5477,12 +5666,12 @@
       <c r="W38" s="1"/>
       <c r="X38" s="1"/>
       <c r="Y38" s="1"/>
-      <c r="Z38" s="97"/>
+      <c r="Z38" s="107"/>
       <c r="AA38" s="84" t="s">
         <v>177</v>
       </c>
-      <c r="AB38" s="100"/>
-      <c r="AC38" s="103"/>
+      <c r="AB38" s="101"/>
+      <c r="AC38" s="104"/>
       <c r="AD38" s="1"/>
       <c r="AE38" s="1"/>
       <c r="AF38" s="1"/>
@@ -5562,12 +5751,12 @@
       <c r="W39" s="1"/>
       <c r="X39" s="1"/>
       <c r="Y39" s="1"/>
-      <c r="Z39" s="98"/>
+      <c r="Z39" s="108"/>
       <c r="AA39" s="86" t="s">
         <v>178</v>
       </c>
-      <c r="AB39" s="101"/>
-      <c r="AC39" s="104"/>
+      <c r="AB39" s="102"/>
+      <c r="AC39" s="105"/>
       <c r="AD39" s="1"/>
       <c r="AE39" s="1"/>
       <c r="AF39" s="1"/>
@@ -5647,16 +5836,16 @@
       <c r="W40" s="1"/>
       <c r="X40" s="1"/>
       <c r="Y40" s="1"/>
-      <c r="Z40" s="105" t="s">
+      <c r="Z40" s="93" t="s">
         <v>226</v>
       </c>
       <c r="AA40" s="80" t="s">
         <v>179</v>
       </c>
-      <c r="AB40" s="106" t="s">
+      <c r="AB40" s="96" t="s">
         <v>197</v>
       </c>
-      <c r="AC40" s="107" t="s">
+      <c r="AC40" s="98" t="s">
         <v>207</v>
       </c>
       <c r="AD40" s="1"/>
@@ -5740,12 +5929,12 @@
       <c r="W41" s="1"/>
       <c r="X41" s="1"/>
       <c r="Y41" s="1"/>
-      <c r="Z41" s="90"/>
+      <c r="Z41" s="94"/>
       <c r="AA41" s="78" t="s">
         <v>180</v>
       </c>
-      <c r="AB41" s="92"/>
-      <c r="AC41" s="94"/>
+      <c r="AB41" s="89"/>
+      <c r="AC41" s="91"/>
       <c r="AD41" s="1"/>
       <c r="AE41" s="1"/>
       <c r="AF41" s="1"/>
@@ -5825,12 +6014,12 @@
       <c r="W42" s="1"/>
       <c r="X42" s="1"/>
       <c r="Y42" s="1"/>
-      <c r="Z42" s="91"/>
+      <c r="Z42" s="95"/>
       <c r="AA42" s="79" t="s">
         <v>181</v>
       </c>
-      <c r="AB42" s="93"/>
-      <c r="AC42" s="95"/>
+      <c r="AB42" s="97"/>
+      <c r="AC42" s="99"/>
       <c r="AD42" s="1"/>
       <c r="AE42" s="1"/>
       <c r="AF42" s="1"/>
@@ -5903,15 +6092,15 @@
       <c r="X43" s="1"/>
       <c r="Y43" s="1"/>
       <c r="Z43" s="83" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="AA43" s="82" t="s">
         <v>183</v>
       </c>
-      <c r="AB43" s="99" t="s">
+      <c r="AB43" s="100" t="s">
         <v>198</v>
       </c>
-      <c r="AC43" s="102" t="s">
+      <c r="AC43" s="103" t="s">
         <v>208</v>
       </c>
       <c r="AD43" s="1"/>
@@ -5993,8 +6182,8 @@
       <c r="AA44" s="84" t="s">
         <v>184</v>
       </c>
-      <c r="AB44" s="100"/>
-      <c r="AC44" s="103"/>
+      <c r="AB44" s="101"/>
+      <c r="AC44" s="104"/>
       <c r="AD44" s="1"/>
       <c r="AE44" s="1"/>
       <c r="AF44" s="1"/>
@@ -6072,8 +6261,8 @@
       <c r="AA45" s="86" t="s">
         <v>185</v>
       </c>
-      <c r="AB45" s="101"/>
-      <c r="AC45" s="104"/>
+      <c r="AB45" s="102"/>
+      <c r="AC45" s="105"/>
       <c r="AD45" s="1"/>
       <c r="AE45" s="1"/>
       <c r="AF45" s="1"/>
@@ -6148,15 +6337,15 @@
       <c r="X46" s="1"/>
       <c r="Y46" s="1"/>
       <c r="Z46" s="75" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="AA46" s="80" t="s">
         <v>186</v>
       </c>
-      <c r="AB46" s="106" t="s">
+      <c r="AB46" s="96" t="s">
         <v>134</v>
       </c>
-      <c r="AC46" s="107" t="s">
+      <c r="AC46" s="98" t="s">
         <v>209</v>
       </c>
       <c r="AD46" s="1"/>
@@ -6238,8 +6427,8 @@
       <c r="AA47" s="78" t="s">
         <v>184</v>
       </c>
-      <c r="AB47" s="92"/>
-      <c r="AC47" s="94"/>
+      <c r="AB47" s="89"/>
+      <c r="AC47" s="91"/>
       <c r="AD47" s="1"/>
       <c r="AE47" s="1"/>
       <c r="AF47" s="1"/>
@@ -6317,8 +6506,8 @@
       <c r="AA48" s="79" t="s">
         <v>185</v>
       </c>
-      <c r="AB48" s="93"/>
-      <c r="AC48" s="95"/>
+      <c r="AB48" s="97"/>
+      <c r="AC48" s="99"/>
       <c r="AD48" s="1"/>
       <c r="AE48" s="1"/>
       <c r="AF48" s="1"/>
@@ -6391,15 +6580,15 @@
       <c r="X49" s="1"/>
       <c r="Y49" s="1"/>
       <c r="Z49" s="83" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="AA49" s="82" t="s">
         <v>187</v>
       </c>
-      <c r="AB49" s="99" t="s">
+      <c r="AB49" s="100" t="s">
         <v>28</v>
       </c>
-      <c r="AC49" s="102" t="s">
+      <c r="AC49" s="103" t="s">
         <v>210</v>
       </c>
       <c r="AD49" s="1"/>
@@ -6479,8 +6668,8 @@
       <c r="AA50" s="84" t="s">
         <v>184</v>
       </c>
-      <c r="AB50" s="100"/>
-      <c r="AC50" s="103"/>
+      <c r="AB50" s="101"/>
+      <c r="AC50" s="104"/>
       <c r="AD50" s="1"/>
       <c r="AE50" s="1"/>
       <c r="AF50" s="1"/>
@@ -6556,8 +6745,8 @@
       <c r="AA51" s="86" t="s">
         <v>185</v>
       </c>
-      <c r="AB51" s="101"/>
-      <c r="AC51" s="104"/>
+      <c r="AB51" s="102"/>
+      <c r="AC51" s="105"/>
       <c r="AD51" s="1"/>
       <c r="AE51" s="1"/>
       <c r="AF51" s="1"/>
@@ -6630,15 +6819,15 @@
       <c r="X52" s="1"/>
       <c r="Y52" s="1"/>
       <c r="Z52" s="75" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="AA52" s="80" t="s">
         <v>188</v>
       </c>
-      <c r="AB52" s="106" t="s">
+      <c r="AB52" s="96" t="s">
         <v>199</v>
       </c>
-      <c r="AC52" s="107" t="s">
+      <c r="AC52" s="98" t="s">
         <v>211</v>
       </c>
       <c r="AD52" s="1"/>
@@ -6718,8 +6907,8 @@
       <c r="AA53" s="78" t="s">
         <v>184</v>
       </c>
-      <c r="AB53" s="92"/>
-      <c r="AC53" s="94"/>
+      <c r="AB53" s="89"/>
+      <c r="AC53" s="91"/>
       <c r="AD53" s="1"/>
       <c r="AE53" s="1"/>
       <c r="AF53" s="1"/>
@@ -6795,8 +6984,8 @@
       <c r="AA54" s="79" t="s">
         <v>185</v>
       </c>
-      <c r="AB54" s="93"/>
-      <c r="AC54" s="95"/>
+      <c r="AB54" s="97"/>
+      <c r="AC54" s="99"/>
       <c r="AD54" s="1"/>
       <c r="AE54" s="1"/>
       <c r="AF54" s="1"/>
@@ -6869,15 +7058,15 @@
       <c r="X55" s="1"/>
       <c r="Y55" s="1"/>
       <c r="Z55" s="83" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="AA55" s="82" t="s">
         <v>189</v>
       </c>
-      <c r="AB55" s="99" t="s">
+      <c r="AB55" s="100" t="s">
         <v>200</v>
       </c>
-      <c r="AC55" s="102" t="s">
+      <c r="AC55" s="103" t="s">
         <v>212</v>
       </c>
       <c r="AD55" s="1"/>
@@ -6957,8 +7146,8 @@
       <c r="AA56" s="84" t="s">
         <v>190</v>
       </c>
-      <c r="AB56" s="100"/>
-      <c r="AC56" s="103"/>
+      <c r="AB56" s="101"/>
+      <c r="AC56" s="104"/>
       <c r="AD56" s="1"/>
       <c r="AE56" s="1"/>
       <c r="AF56" s="1"/>
@@ -7032,8 +7221,8 @@
       <c r="Y57" s="1"/>
       <c r="Z57" s="85"/>
       <c r="AA57" s="86"/>
-      <c r="AB57" s="101"/>
-      <c r="AC57" s="104"/>
+      <c r="AB57" s="102"/>
+      <c r="AC57" s="105"/>
       <c r="AD57" s="1"/>
       <c r="AE57" s="1"/>
       <c r="AF57" s="1"/>
@@ -7106,15 +7295,15 @@
       <c r="X58" s="1"/>
       <c r="Y58" s="1"/>
       <c r="Z58" s="75" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="AA58" s="80" t="s">
         <v>191</v>
       </c>
-      <c r="AB58" s="106" t="s">
+      <c r="AB58" s="96" t="s">
         <v>201</v>
       </c>
-      <c r="AC58" s="107" t="s">
+      <c r="AC58" s="98" t="s">
         <v>213</v>
       </c>
       <c r="AD58" s="1"/>
@@ -7194,8 +7383,8 @@
       <c r="AA59" s="78" t="s">
         <v>190</v>
       </c>
-      <c r="AB59" s="92"/>
-      <c r="AC59" s="94"/>
+      <c r="AB59" s="89"/>
+      <c r="AC59" s="91"/>
       <c r="AD59" s="1"/>
       <c r="AE59" s="1"/>
       <c r="AF59" s="1"/>
@@ -7269,8 +7458,8 @@
       <c r="Y60" s="1"/>
       <c r="Z60" s="77"/>
       <c r="AA60" s="79"/>
-      <c r="AB60" s="93"/>
-      <c r="AC60" s="95"/>
+      <c r="AB60" s="97"/>
+      <c r="AC60" s="99"/>
       <c r="AD60" s="1"/>
       <c r="AE60" s="1"/>
       <c r="AF60" s="1"/>
@@ -7343,15 +7532,15 @@
       <c r="X61" s="1"/>
       <c r="Y61" s="1"/>
       <c r="Z61" s="83" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="AA61" s="82" t="s">
         <v>187</v>
       </c>
-      <c r="AB61" s="99" t="s">
+      <c r="AB61" s="100" t="s">
         <v>202</v>
       </c>
-      <c r="AC61" s="102" t="s">
+      <c r="AC61" s="103" t="s">
         <v>212</v>
       </c>
       <c r="AD61" s="1"/>
@@ -7431,8 +7620,8 @@
       <c r="AA62" s="84" t="s">
         <v>190</v>
       </c>
-      <c r="AB62" s="100"/>
-      <c r="AC62" s="103"/>
+      <c r="AB62" s="101"/>
+      <c r="AC62" s="104"/>
       <c r="AD62" s="1"/>
       <c r="AE62" s="1"/>
       <c r="AF62" s="1"/>
@@ -7506,8 +7695,8 @@
       <c r="Y63" s="1"/>
       <c r="Z63" s="85"/>
       <c r="AA63" s="86"/>
-      <c r="AB63" s="101"/>
-      <c r="AC63" s="104"/>
+      <c r="AB63" s="102"/>
+      <c r="AC63" s="105"/>
       <c r="AD63" s="1"/>
       <c r="AE63" s="1"/>
       <c r="AF63" s="1"/>
@@ -7580,15 +7769,15 @@
       <c r="X64" s="1"/>
       <c r="Y64" s="1"/>
       <c r="Z64" s="75" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="AA64" s="78" t="s">
         <v>188</v>
       </c>
-      <c r="AB64" s="92" t="s">
+      <c r="AB64" s="89" t="s">
         <v>203</v>
       </c>
-      <c r="AC64" s="94" t="s">
+      <c r="AC64" s="91" t="s">
         <v>213</v>
       </c>
       <c r="AD64" s="1"/>
@@ -7668,8 +7857,8 @@
       <c r="AA65" s="78" t="s">
         <v>190</v>
       </c>
-      <c r="AB65" s="92"/>
-      <c r="AC65" s="94"/>
+      <c r="AB65" s="89"/>
+      <c r="AC65" s="91"/>
       <c r="AD65" s="1"/>
       <c r="AE65" s="1"/>
       <c r="AF65" s="1"/>
@@ -7743,8 +7932,8 @@
       <c r="Y66" s="1"/>
       <c r="Z66" s="76"/>
       <c r="AA66" s="81"/>
-      <c r="AB66" s="108"/>
-      <c r="AC66" s="109"/>
+      <c r="AB66" s="90"/>
+      <c r="AC66" s="92"/>
       <c r="AD66" s="1"/>
       <c r="AE66" s="1"/>
       <c r="AF66" s="1"/>
@@ -7969,7 +8158,7 @@
       <c r="X69" s="1"/>
       <c r="Y69" s="1"/>
       <c r="Z69" s="1" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
       <c r="AA69" s="1"/>
       <c r="AB69" s="1"/>
@@ -8046,7 +8235,7 @@
       <c r="X70" s="1"/>
       <c r="Y70" s="1"/>
       <c r="Z70" s="1" t="s">
-        <v>228</v>
+        <v>258</v>
       </c>
       <c r="AA70" s="1"/>
       <c r="AB70" s="1"/>
@@ -38503,6 +38692,35 @@
     </row>
   </sheetData>
   <mergeCells count="45">
+    <mergeCell ref="R3:Y3"/>
+    <mergeCell ref="R4:Y4"/>
+    <mergeCell ref="Z16:Z18"/>
+    <mergeCell ref="AB16:AB18"/>
+    <mergeCell ref="AC16:AC18"/>
+    <mergeCell ref="Z19:Z21"/>
+    <mergeCell ref="AB19:AB21"/>
+    <mergeCell ref="AC19:AC21"/>
+    <mergeCell ref="Z25:Z27"/>
+    <mergeCell ref="AB25:AB27"/>
+    <mergeCell ref="AC25:AC27"/>
+    <mergeCell ref="Z28:Z30"/>
+    <mergeCell ref="AB28:AB30"/>
+    <mergeCell ref="AC28:AC30"/>
+    <mergeCell ref="Z31:Z33"/>
+    <mergeCell ref="AB31:AB33"/>
+    <mergeCell ref="AC31:AC33"/>
+    <mergeCell ref="Z34:Z36"/>
+    <mergeCell ref="AB34:AB36"/>
+    <mergeCell ref="AC34:AC36"/>
+    <mergeCell ref="Z37:Z39"/>
+    <mergeCell ref="AB37:AB39"/>
+    <mergeCell ref="AC37:AC39"/>
+    <mergeCell ref="AC52:AC54"/>
+    <mergeCell ref="Z40:Z42"/>
+    <mergeCell ref="AB40:AB42"/>
+    <mergeCell ref="AC40:AC42"/>
+    <mergeCell ref="AB43:AB45"/>
+    <mergeCell ref="AC43:AC45"/>
     <mergeCell ref="AB64:AB66"/>
     <mergeCell ref="AC64:AC66"/>
     <mergeCell ref="Z22:Z24"/>
@@ -38519,35 +38737,6 @@
     <mergeCell ref="AB49:AB51"/>
     <mergeCell ref="AC49:AC51"/>
     <mergeCell ref="AB52:AB54"/>
-    <mergeCell ref="AC52:AC54"/>
-    <mergeCell ref="Z40:Z42"/>
-    <mergeCell ref="AB40:AB42"/>
-    <mergeCell ref="AC40:AC42"/>
-    <mergeCell ref="AB43:AB45"/>
-    <mergeCell ref="AC43:AC45"/>
-    <mergeCell ref="Z34:Z36"/>
-    <mergeCell ref="AB34:AB36"/>
-    <mergeCell ref="AC34:AC36"/>
-    <mergeCell ref="Z37:Z39"/>
-    <mergeCell ref="AB37:AB39"/>
-    <mergeCell ref="AC37:AC39"/>
-    <mergeCell ref="Z28:Z30"/>
-    <mergeCell ref="AB28:AB30"/>
-    <mergeCell ref="AC28:AC30"/>
-    <mergeCell ref="Z31:Z33"/>
-    <mergeCell ref="AB31:AB33"/>
-    <mergeCell ref="AC31:AC33"/>
-    <mergeCell ref="Z19:Z21"/>
-    <mergeCell ref="AB19:AB21"/>
-    <mergeCell ref="AC19:AC21"/>
-    <mergeCell ref="Z25:Z27"/>
-    <mergeCell ref="AB25:AB27"/>
-    <mergeCell ref="AC25:AC27"/>
-    <mergeCell ref="R3:Y3"/>
-    <mergeCell ref="R4:Y4"/>
-    <mergeCell ref="Z16:Z18"/>
-    <mergeCell ref="AB16:AB18"/>
-    <mergeCell ref="AC16:AC18"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/results.xlsx
+++ b/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utilizador\Desktop\uni\MEI 1ano1sem\DAA\trabalho\DAA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22213A50-5106-428B-8CA5-533593317BCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECBF6386-0897-4F99-B241-8CFD17F79DAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="14020" xr2:uid="{744B1543-7C44-49C5-883E-AA14D96B6E1A}"/>
   </bookViews>
@@ -1612,20 +1612,13 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1633,16 +1626,25 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1663,23 +1665,21 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2169,16 +2169,16 @@
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
-      <c r="R3" s="109" t="s">
+      <c r="R3" s="92" t="s">
         <v>119</v>
       </c>
-      <c r="S3" s="109"/>
-      <c r="T3" s="109"/>
-      <c r="U3" s="109"/>
-      <c r="V3" s="109"/>
-      <c r="W3" s="109"/>
-      <c r="X3" s="109"/>
-      <c r="Y3" s="109"/>
+      <c r="S3" s="92"/>
+      <c r="T3" s="92"/>
+      <c r="U3" s="92"/>
+      <c r="V3" s="92"/>
+      <c r="W3" s="92"/>
+      <c r="X3" s="92"/>
+      <c r="Y3" s="92"/>
       <c r="Z3" s="73" t="s">
         <v>149</v>
       </c>
@@ -2256,16 +2256,16 @@
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
-      <c r="R4" s="109" t="s">
+      <c r="R4" s="92" t="s">
         <v>120</v>
       </c>
-      <c r="S4" s="109"/>
-      <c r="T4" s="109"/>
-      <c r="U4" s="109"/>
-      <c r="V4" s="109"/>
-      <c r="W4" s="109"/>
-      <c r="X4" s="109"/>
-      <c r="Y4" s="109"/>
+      <c r="S4" s="92"/>
+      <c r="T4" s="92"/>
+      <c r="U4" s="92"/>
+      <c r="V4" s="92"/>
+      <c r="W4" s="92"/>
+      <c r="X4" s="92"/>
+      <c r="Y4" s="92"/>
       <c r="Z4" s="73" t="s">
         <v>150</v>
       </c>
@@ -2950,7 +2950,7 @@
       <c r="AL11" s="1"/>
       <c r="AM11" s="1"/>
       <c r="AN11" s="1"/>
-      <c r="AO11" s="110" t="s">
+      <c r="AO11" s="89" t="s">
         <v>278</v>
       </c>
       <c r="AP11" s="11" t="s">
@@ -3508,16 +3508,16 @@
       <c r="W16" s="1"/>
       <c r="X16" s="1"/>
       <c r="Y16" s="1"/>
-      <c r="Z16" s="94" t="s">
+      <c r="Z16" s="93" t="s">
         <v>218</v>
       </c>
       <c r="AA16" s="78" t="s">
         <v>161</v>
       </c>
-      <c r="AB16" s="89" t="s">
+      <c r="AB16" s="95" t="s">
         <v>163</v>
       </c>
-      <c r="AC16" s="91" t="s">
+      <c r="AC16" s="97" t="s">
         <v>103</v>
       </c>
       <c r="AD16" s="1"/>
@@ -3629,12 +3629,12 @@
       <c r="W17" s="1"/>
       <c r="X17" s="1"/>
       <c r="Y17" s="1"/>
-      <c r="Z17" s="94"/>
+      <c r="Z17" s="93"/>
       <c r="AA17" s="78" t="s">
         <v>165</v>
       </c>
-      <c r="AB17" s="89"/>
-      <c r="AC17" s="91"/>
+      <c r="AB17" s="95"/>
+      <c r="AC17" s="97"/>
       <c r="AD17" s="1"/>
       <c r="AE17" s="1"/>
       <c r="AF17" s="1"/>
@@ -3732,12 +3732,12 @@
       <c r="W18" s="1"/>
       <c r="X18" s="1"/>
       <c r="Y18" s="1"/>
-      <c r="Z18" s="95"/>
+      <c r="Z18" s="94"/>
       <c r="AA18" s="79" t="s">
         <v>162</v>
       </c>
-      <c r="AB18" s="97"/>
-      <c r="AC18" s="99"/>
+      <c r="AB18" s="96"/>
+      <c r="AC18" s="98"/>
       <c r="AD18" s="1"/>
       <c r="AE18" s="1"/>
       <c r="AF18" s="1"/>
@@ -3751,7 +3751,7 @@
       <c r="AL18" s="1"/>
       <c r="AM18" s="1"/>
       <c r="AN18" s="1"/>
-      <c r="AO18" s="111"/>
+      <c r="AO18" s="90"/>
       <c r="AP18" s="52"/>
       <c r="AQ18" s="52" t="s">
         <v>236</v>
@@ -3837,16 +3837,16 @@
       <c r="W19" s="1"/>
       <c r="X19" s="1"/>
       <c r="Y19" s="1"/>
-      <c r="Z19" s="106" t="s">
+      <c r="Z19" s="99" t="s">
         <v>219</v>
       </c>
       <c r="AA19" s="82" t="s">
         <v>161</v>
       </c>
-      <c r="AB19" s="100" t="s">
+      <c r="AB19" s="102" t="s">
         <v>117</v>
       </c>
-      <c r="AC19" s="103" t="s">
+      <c r="AC19" s="105" t="s">
         <v>166</v>
       </c>
       <c r="AD19" s="1"/>
@@ -3862,7 +3862,7 @@
       <c r="AL19" s="1"/>
       <c r="AM19" s="1"/>
       <c r="AN19" s="1"/>
-      <c r="AO19" s="111"/>
+      <c r="AO19" s="90"/>
       <c r="AP19" s="52"/>
       <c r="AQ19" s="52" t="s">
         <v>239</v>
@@ -3952,12 +3952,12 @@
       <c r="W20" s="1"/>
       <c r="X20" s="1"/>
       <c r="Y20" s="1"/>
-      <c r="Z20" s="107"/>
+      <c r="Z20" s="100"/>
       <c r="AA20" s="84" t="s">
         <v>164</v>
       </c>
-      <c r="AB20" s="101"/>
-      <c r="AC20" s="104"/>
+      <c r="AB20" s="103"/>
+      <c r="AC20" s="106"/>
       <c r="AD20" s="1"/>
       <c r="AE20" s="1"/>
       <c r="AF20" s="1"/>
@@ -3971,7 +3971,7 @@
       <c r="AL20" s="1"/>
       <c r="AM20" s="1"/>
       <c r="AN20" s="1"/>
-      <c r="AO20" s="112"/>
+      <c r="AO20" s="91"/>
       <c r="AP20" s="58"/>
       <c r="AQ20" s="58" t="s">
         <v>240</v>
@@ -4061,12 +4061,12 @@
       <c r="W21" s="1"/>
       <c r="X21" s="1"/>
       <c r="Y21" s="1"/>
-      <c r="Z21" s="108"/>
+      <c r="Z21" s="101"/>
       <c r="AA21" s="86" t="s">
         <v>162</v>
       </c>
-      <c r="AB21" s="102"/>
-      <c r="AC21" s="105"/>
+      <c r="AB21" s="104"/>
+      <c r="AC21" s="107"/>
       <c r="AD21" s="1"/>
       <c r="AE21" s="1"/>
       <c r="AF21" s="1"/>
@@ -4166,16 +4166,16 @@
       <c r="W22" s="1"/>
       <c r="X22" s="1"/>
       <c r="Y22" s="1"/>
-      <c r="Z22" s="93" t="s">
+      <c r="Z22" s="108" t="s">
         <v>220</v>
       </c>
       <c r="AA22" s="80" t="s">
         <v>215</v>
       </c>
-      <c r="AB22" s="96" t="s">
+      <c r="AB22" s="109" t="s">
         <v>214</v>
       </c>
-      <c r="AC22" s="98" t="s">
+      <c r="AC22" s="110" t="s">
         <v>217</v>
       </c>
       <c r="AD22" s="1"/>
@@ -4277,12 +4277,12 @@
       <c r="W23" s="1"/>
       <c r="X23" s="1"/>
       <c r="Y23" s="1"/>
-      <c r="Z23" s="94"/>
+      <c r="Z23" s="93"/>
       <c r="AA23" s="78" t="s">
         <v>216</v>
       </c>
-      <c r="AB23" s="89"/>
-      <c r="AC23" s="91"/>
+      <c r="AB23" s="95"/>
+      <c r="AC23" s="97"/>
       <c r="AD23" s="1"/>
       <c r="AE23" s="1"/>
       <c r="AF23" s="1"/>
@@ -4376,12 +4376,12 @@
       <c r="W24" s="1"/>
       <c r="X24" s="1"/>
       <c r="Y24" s="1"/>
-      <c r="Z24" s="95"/>
+      <c r="Z24" s="94"/>
       <c r="AA24" s="79" t="s">
         <v>162</v>
       </c>
-      <c r="AB24" s="97"/>
-      <c r="AC24" s="99"/>
+      <c r="AB24" s="96"/>
+      <c r="AC24" s="98"/>
       <c r="AD24" s="1"/>
       <c r="AE24" s="1"/>
       <c r="AF24" s="1"/>
@@ -4471,16 +4471,16 @@
       <c r="W25" s="1"/>
       <c r="X25" s="1"/>
       <c r="Y25" s="1"/>
-      <c r="Z25" s="106" t="s">
+      <c r="Z25" s="99" t="s">
         <v>221</v>
       </c>
       <c r="AA25" s="82" t="s">
         <v>169</v>
       </c>
-      <c r="AB25" s="100" t="s">
+      <c r="AB25" s="102" t="s">
         <v>193</v>
       </c>
-      <c r="AC25" s="103" t="s">
+      <c r="AC25" s="105" t="s">
         <v>204</v>
       </c>
       <c r="AD25" s="1"/>
@@ -4572,12 +4572,12 @@
       <c r="W26" s="1"/>
       <c r="X26" s="1"/>
       <c r="Y26" s="1"/>
-      <c r="Z26" s="107"/>
+      <c r="Z26" s="100"/>
       <c r="AA26" s="84" t="s">
         <v>167</v>
       </c>
-      <c r="AB26" s="101"/>
-      <c r="AC26" s="104"/>
+      <c r="AB26" s="103"/>
+      <c r="AC26" s="106"/>
       <c r="AD26" s="1"/>
       <c r="AE26" s="1"/>
       <c r="AF26" s="1"/>
@@ -4665,12 +4665,12 @@
       <c r="W27" s="1"/>
       <c r="X27" s="1"/>
       <c r="Y27" s="1"/>
-      <c r="Z27" s="108"/>
+      <c r="Z27" s="101"/>
       <c r="AA27" s="86" t="s">
         <v>168</v>
       </c>
-      <c r="AB27" s="102"/>
-      <c r="AC27" s="105"/>
+      <c r="AB27" s="104"/>
+      <c r="AC27" s="107"/>
       <c r="AD27" s="1"/>
       <c r="AE27" s="1"/>
       <c r="AF27" s="1"/>
@@ -4760,16 +4760,16 @@
       <c r="W28" s="1"/>
       <c r="X28" s="1"/>
       <c r="Y28" s="1"/>
-      <c r="Z28" s="93" t="s">
+      <c r="Z28" s="108" t="s">
         <v>222</v>
       </c>
       <c r="AA28" s="80" t="s">
         <v>169</v>
       </c>
-      <c r="AB28" s="96" t="s">
+      <c r="AB28" s="109" t="s">
         <v>194</v>
       </c>
-      <c r="AC28" s="98" t="s">
+      <c r="AC28" s="110" t="s">
         <v>205</v>
       </c>
       <c r="AD28" s="1"/>
@@ -4863,12 +4863,12 @@
       <c r="W29" s="1"/>
       <c r="X29" s="1"/>
       <c r="Y29" s="1"/>
-      <c r="Z29" s="94"/>
+      <c r="Z29" s="93"/>
       <c r="AA29" s="78" t="s">
         <v>170</v>
       </c>
-      <c r="AB29" s="89"/>
-      <c r="AC29" s="91"/>
+      <c r="AB29" s="95"/>
+      <c r="AC29" s="97"/>
       <c r="AD29" s="1"/>
       <c r="AE29" s="1"/>
       <c r="AF29" s="1"/>
@@ -4956,12 +4956,12 @@
       <c r="W30" s="1"/>
       <c r="X30" s="1"/>
       <c r="Y30" s="1"/>
-      <c r="Z30" s="95"/>
+      <c r="Z30" s="94"/>
       <c r="AA30" s="79" t="s">
         <v>168</v>
       </c>
-      <c r="AB30" s="97"/>
-      <c r="AC30" s="99"/>
+      <c r="AB30" s="96"/>
+      <c r="AC30" s="98"/>
       <c r="AD30" s="1"/>
       <c r="AE30" s="1"/>
       <c r="AF30" s="1"/>
@@ -5047,16 +5047,16 @@
       <c r="W31" s="1"/>
       <c r="X31" s="1"/>
       <c r="Y31" s="1"/>
-      <c r="Z31" s="106" t="s">
+      <c r="Z31" s="99" t="s">
         <v>223</v>
       </c>
       <c r="AA31" s="82" t="s">
         <v>174</v>
       </c>
-      <c r="AB31" s="100" t="s">
+      <c r="AB31" s="102" t="s">
         <v>45</v>
       </c>
-      <c r="AC31" s="103" t="s">
+      <c r="AC31" s="105" t="s">
         <v>10</v>
       </c>
       <c r="AD31" s="1"/>
@@ -5140,12 +5140,12 @@
       <c r="W32" s="1"/>
       <c r="X32" s="1"/>
       <c r="Y32" s="1"/>
-      <c r="Z32" s="107"/>
+      <c r="Z32" s="100"/>
       <c r="AA32" s="84" t="s">
         <v>175</v>
       </c>
-      <c r="AB32" s="101"/>
-      <c r="AC32" s="104"/>
+      <c r="AB32" s="103"/>
+      <c r="AC32" s="106"/>
       <c r="AD32" s="1"/>
       <c r="AE32" s="1"/>
       <c r="AF32" s="1"/>
@@ -5227,12 +5227,12 @@
       <c r="W33" s="1"/>
       <c r="X33" s="1"/>
       <c r="Y33" s="1"/>
-      <c r="Z33" s="108"/>
+      <c r="Z33" s="101"/>
       <c r="AA33" s="86" t="s">
         <v>173</v>
       </c>
-      <c r="AB33" s="102"/>
-      <c r="AC33" s="105"/>
+      <c r="AB33" s="104"/>
+      <c r="AC33" s="107"/>
       <c r="AD33" s="1"/>
       <c r="AE33" s="1"/>
       <c r="AF33" s="1"/>
@@ -5312,16 +5312,16 @@
       <c r="W34" s="1"/>
       <c r="X34" s="1"/>
       <c r="Y34" s="1"/>
-      <c r="Z34" s="93" t="s">
+      <c r="Z34" s="108" t="s">
         <v>224</v>
       </c>
       <c r="AA34" s="80" t="s">
         <v>171</v>
       </c>
-      <c r="AB34" s="96" t="s">
+      <c r="AB34" s="109" t="s">
         <v>195</v>
       </c>
-      <c r="AC34" s="98" t="s">
+      <c r="AC34" s="110" t="s">
         <v>102</v>
       </c>
       <c r="AD34" s="1"/>
@@ -5405,12 +5405,12 @@
       <c r="W35" s="1"/>
       <c r="X35" s="1"/>
       <c r="Y35" s="1"/>
-      <c r="Z35" s="94"/>
+      <c r="Z35" s="93"/>
       <c r="AA35" s="78" t="s">
         <v>172</v>
       </c>
-      <c r="AB35" s="89"/>
-      <c r="AC35" s="91"/>
+      <c r="AB35" s="95"/>
+      <c r="AC35" s="97"/>
       <c r="AD35" s="1"/>
       <c r="AE35" s="1"/>
       <c r="AF35" s="1"/>
@@ -5488,12 +5488,12 @@
       <c r="W36" s="1"/>
       <c r="X36" s="1"/>
       <c r="Y36" s="1"/>
-      <c r="Z36" s="95"/>
+      <c r="Z36" s="94"/>
       <c r="AA36" s="79" t="s">
         <v>173</v>
       </c>
-      <c r="AB36" s="97"/>
-      <c r="AC36" s="99"/>
+      <c r="AB36" s="96"/>
+      <c r="AC36" s="98"/>
       <c r="AD36" s="1"/>
       <c r="AE36" s="1"/>
       <c r="AF36" s="1"/>
@@ -5573,16 +5573,16 @@
       <c r="W37" s="1"/>
       <c r="X37" s="1"/>
       <c r="Y37" s="1"/>
-      <c r="Z37" s="106" t="s">
+      <c r="Z37" s="99" t="s">
         <v>225</v>
       </c>
       <c r="AA37" s="82" t="s">
         <v>176</v>
       </c>
-      <c r="AB37" s="100" t="s">
+      <c r="AB37" s="102" t="s">
         <v>196</v>
       </c>
-      <c r="AC37" s="103" t="s">
+      <c r="AC37" s="105" t="s">
         <v>206</v>
       </c>
       <c r="AD37" s="1"/>
@@ -5666,12 +5666,12 @@
       <c r="W38" s="1"/>
       <c r="X38" s="1"/>
       <c r="Y38" s="1"/>
-      <c r="Z38" s="107"/>
+      <c r="Z38" s="100"/>
       <c r="AA38" s="84" t="s">
         <v>177</v>
       </c>
-      <c r="AB38" s="101"/>
-      <c r="AC38" s="104"/>
+      <c r="AB38" s="103"/>
+      <c r="AC38" s="106"/>
       <c r="AD38" s="1"/>
       <c r="AE38" s="1"/>
       <c r="AF38" s="1"/>
@@ -5751,12 +5751,12 @@
       <c r="W39" s="1"/>
       <c r="X39" s="1"/>
       <c r="Y39" s="1"/>
-      <c r="Z39" s="108"/>
+      <c r="Z39" s="101"/>
       <c r="AA39" s="86" t="s">
         <v>178</v>
       </c>
-      <c r="AB39" s="102"/>
-      <c r="AC39" s="105"/>
+      <c r="AB39" s="104"/>
+      <c r="AC39" s="107"/>
       <c r="AD39" s="1"/>
       <c r="AE39" s="1"/>
       <c r="AF39" s="1"/>
@@ -5836,16 +5836,16 @@
       <c r="W40" s="1"/>
       <c r="X40" s="1"/>
       <c r="Y40" s="1"/>
-      <c r="Z40" s="93" t="s">
+      <c r="Z40" s="108" t="s">
         <v>226</v>
       </c>
       <c r="AA40" s="80" t="s">
         <v>179</v>
       </c>
-      <c r="AB40" s="96" t="s">
+      <c r="AB40" s="109" t="s">
         <v>197</v>
       </c>
-      <c r="AC40" s="98" t="s">
+      <c r="AC40" s="110" t="s">
         <v>207</v>
       </c>
       <c r="AD40" s="1"/>
@@ -5929,12 +5929,12 @@
       <c r="W41" s="1"/>
       <c r="X41" s="1"/>
       <c r="Y41" s="1"/>
-      <c r="Z41" s="94"/>
+      <c r="Z41" s="93"/>
       <c r="AA41" s="78" t="s">
         <v>180</v>
       </c>
-      <c r="AB41" s="89"/>
-      <c r="AC41" s="91"/>
+      <c r="AB41" s="95"/>
+      <c r="AC41" s="97"/>
       <c r="AD41" s="1"/>
       <c r="AE41" s="1"/>
       <c r="AF41" s="1"/>
@@ -6014,12 +6014,12 @@
       <c r="W42" s="1"/>
       <c r="X42" s="1"/>
       <c r="Y42" s="1"/>
-      <c r="Z42" s="95"/>
+      <c r="Z42" s="94"/>
       <c r="AA42" s="79" t="s">
         <v>181</v>
       </c>
-      <c r="AB42" s="97"/>
-      <c r="AC42" s="99"/>
+      <c r="AB42" s="96"/>
+      <c r="AC42" s="98"/>
       <c r="AD42" s="1"/>
       <c r="AE42" s="1"/>
       <c r="AF42" s="1"/>
@@ -6097,10 +6097,10 @@
       <c r="AA43" s="82" t="s">
         <v>183</v>
       </c>
-      <c r="AB43" s="100" t="s">
+      <c r="AB43" s="102" t="s">
         <v>198</v>
       </c>
-      <c r="AC43" s="103" t="s">
+      <c r="AC43" s="105" t="s">
         <v>208</v>
       </c>
       <c r="AD43" s="1"/>
@@ -6182,8 +6182,8 @@
       <c r="AA44" s="84" t="s">
         <v>184</v>
       </c>
-      <c r="AB44" s="101"/>
-      <c r="AC44" s="104"/>
+      <c r="AB44" s="103"/>
+      <c r="AC44" s="106"/>
       <c r="AD44" s="1"/>
       <c r="AE44" s="1"/>
       <c r="AF44" s="1"/>
@@ -6261,8 +6261,8 @@
       <c r="AA45" s="86" t="s">
         <v>185</v>
       </c>
-      <c r="AB45" s="102"/>
-      <c r="AC45" s="105"/>
+      <c r="AB45" s="104"/>
+      <c r="AC45" s="107"/>
       <c r="AD45" s="1"/>
       <c r="AE45" s="1"/>
       <c r="AF45" s="1"/>
@@ -6342,10 +6342,10 @@
       <c r="AA46" s="80" t="s">
         <v>186</v>
       </c>
-      <c r="AB46" s="96" t="s">
+      <c r="AB46" s="109" t="s">
         <v>134</v>
       </c>
-      <c r="AC46" s="98" t="s">
+      <c r="AC46" s="110" t="s">
         <v>209</v>
       </c>
       <c r="AD46" s="1"/>
@@ -6427,8 +6427,8 @@
       <c r="AA47" s="78" t="s">
         <v>184</v>
       </c>
-      <c r="AB47" s="89"/>
-      <c r="AC47" s="91"/>
+      <c r="AB47" s="95"/>
+      <c r="AC47" s="97"/>
       <c r="AD47" s="1"/>
       <c r="AE47" s="1"/>
       <c r="AF47" s="1"/>
@@ -6506,8 +6506,8 @@
       <c r="AA48" s="79" t="s">
         <v>185</v>
       </c>
-      <c r="AB48" s="97"/>
-      <c r="AC48" s="99"/>
+      <c r="AB48" s="96"/>
+      <c r="AC48" s="98"/>
       <c r="AD48" s="1"/>
       <c r="AE48" s="1"/>
       <c r="AF48" s="1"/>
@@ -6585,10 +6585,10 @@
       <c r="AA49" s="82" t="s">
         <v>187</v>
       </c>
-      <c r="AB49" s="100" t="s">
+      <c r="AB49" s="102" t="s">
         <v>28</v>
       </c>
-      <c r="AC49" s="103" t="s">
+      <c r="AC49" s="105" t="s">
         <v>210</v>
       </c>
       <c r="AD49" s="1"/>
@@ -6668,8 +6668,8 @@
       <c r="AA50" s="84" t="s">
         <v>184</v>
       </c>
-      <c r="AB50" s="101"/>
-      <c r="AC50" s="104"/>
+      <c r="AB50" s="103"/>
+      <c r="AC50" s="106"/>
       <c r="AD50" s="1"/>
       <c r="AE50" s="1"/>
       <c r="AF50" s="1"/>
@@ -6745,8 +6745,8 @@
       <c r="AA51" s="86" t="s">
         <v>185</v>
       </c>
-      <c r="AB51" s="102"/>
-      <c r="AC51" s="105"/>
+      <c r="AB51" s="104"/>
+      <c r="AC51" s="107"/>
       <c r="AD51" s="1"/>
       <c r="AE51" s="1"/>
       <c r="AF51" s="1"/>
@@ -6824,10 +6824,10 @@
       <c r="AA52" s="80" t="s">
         <v>188</v>
       </c>
-      <c r="AB52" s="96" t="s">
+      <c r="AB52" s="109" t="s">
         <v>199</v>
       </c>
-      <c r="AC52" s="98" t="s">
+      <c r="AC52" s="110" t="s">
         <v>211</v>
       </c>
       <c r="AD52" s="1"/>
@@ -6907,8 +6907,8 @@
       <c r="AA53" s="78" t="s">
         <v>184</v>
       </c>
-      <c r="AB53" s="89"/>
-      <c r="AC53" s="91"/>
+      <c r="AB53" s="95"/>
+      <c r="AC53" s="97"/>
       <c r="AD53" s="1"/>
       <c r="AE53" s="1"/>
       <c r="AF53" s="1"/>
@@ -6984,8 +6984,8 @@
       <c r="AA54" s="79" t="s">
         <v>185</v>
       </c>
-      <c r="AB54" s="97"/>
-      <c r="AC54" s="99"/>
+      <c r="AB54" s="96"/>
+      <c r="AC54" s="98"/>
       <c r="AD54" s="1"/>
       <c r="AE54" s="1"/>
       <c r="AF54" s="1"/>
@@ -7063,10 +7063,10 @@
       <c r="AA55" s="82" t="s">
         <v>189</v>
       </c>
-      <c r="AB55" s="100" t="s">
+      <c r="AB55" s="102" t="s">
         <v>200</v>
       </c>
-      <c r="AC55" s="103" t="s">
+      <c r="AC55" s="105" t="s">
         <v>212</v>
       </c>
       <c r="AD55" s="1"/>
@@ -7146,8 +7146,8 @@
       <c r="AA56" s="84" t="s">
         <v>190</v>
       </c>
-      <c r="AB56" s="101"/>
-      <c r="AC56" s="104"/>
+      <c r="AB56" s="103"/>
+      <c r="AC56" s="106"/>
       <c r="AD56" s="1"/>
       <c r="AE56" s="1"/>
       <c r="AF56" s="1"/>
@@ -7221,8 +7221,8 @@
       <c r="Y57" s="1"/>
       <c r="Z57" s="85"/>
       <c r="AA57" s="86"/>
-      <c r="AB57" s="102"/>
-      <c r="AC57" s="105"/>
+      <c r="AB57" s="104"/>
+      <c r="AC57" s="107"/>
       <c r="AD57" s="1"/>
       <c r="AE57" s="1"/>
       <c r="AF57" s="1"/>
@@ -7300,10 +7300,10 @@
       <c r="AA58" s="80" t="s">
         <v>191</v>
       </c>
-      <c r="AB58" s="96" t="s">
+      <c r="AB58" s="109" t="s">
         <v>201</v>
       </c>
-      <c r="AC58" s="98" t="s">
+      <c r="AC58" s="110" t="s">
         <v>213</v>
       </c>
       <c r="AD58" s="1"/>
@@ -7383,8 +7383,8 @@
       <c r="AA59" s="78" t="s">
         <v>190</v>
       </c>
-      <c r="AB59" s="89"/>
-      <c r="AC59" s="91"/>
+      <c r="AB59" s="95"/>
+      <c r="AC59" s="97"/>
       <c r="AD59" s="1"/>
       <c r="AE59" s="1"/>
       <c r="AF59" s="1"/>
@@ -7458,8 +7458,8 @@
       <c r="Y60" s="1"/>
       <c r="Z60" s="77"/>
       <c r="AA60" s="79"/>
-      <c r="AB60" s="97"/>
-      <c r="AC60" s="99"/>
+      <c r="AB60" s="96"/>
+      <c r="AC60" s="98"/>
       <c r="AD60" s="1"/>
       <c r="AE60" s="1"/>
       <c r="AF60" s="1"/>
@@ -7537,10 +7537,10 @@
       <c r="AA61" s="82" t="s">
         <v>187</v>
       </c>
-      <c r="AB61" s="100" t="s">
+      <c r="AB61" s="102" t="s">
         <v>202</v>
       </c>
-      <c r="AC61" s="103" t="s">
+      <c r="AC61" s="105" t="s">
         <v>212</v>
       </c>
       <c r="AD61" s="1"/>
@@ -7620,8 +7620,8 @@
       <c r="AA62" s="84" t="s">
         <v>190</v>
       </c>
-      <c r="AB62" s="101"/>
-      <c r="AC62" s="104"/>
+      <c r="AB62" s="103"/>
+      <c r="AC62" s="106"/>
       <c r="AD62" s="1"/>
       <c r="AE62" s="1"/>
       <c r="AF62" s="1"/>
@@ -7695,8 +7695,8 @@
       <c r="Y63" s="1"/>
       <c r="Z63" s="85"/>
       <c r="AA63" s="86"/>
-      <c r="AB63" s="102"/>
-      <c r="AC63" s="105"/>
+      <c r="AB63" s="104"/>
+      <c r="AC63" s="107"/>
       <c r="AD63" s="1"/>
       <c r="AE63" s="1"/>
       <c r="AF63" s="1"/>
@@ -7774,10 +7774,10 @@
       <c r="AA64" s="78" t="s">
         <v>188</v>
       </c>
-      <c r="AB64" s="89" t="s">
+      <c r="AB64" s="95" t="s">
         <v>203</v>
       </c>
-      <c r="AC64" s="91" t="s">
+      <c r="AC64" s="97" t="s">
         <v>213</v>
       </c>
       <c r="AD64" s="1"/>
@@ -7857,8 +7857,8 @@
       <c r="AA65" s="78" t="s">
         <v>190</v>
       </c>
-      <c r="AB65" s="89"/>
-      <c r="AC65" s="91"/>
+      <c r="AB65" s="95"/>
+      <c r="AC65" s="97"/>
       <c r="AD65" s="1"/>
       <c r="AE65" s="1"/>
       <c r="AF65" s="1"/>
@@ -7932,8 +7932,8 @@
       <c r="Y66" s="1"/>
       <c r="Z66" s="76"/>
       <c r="AA66" s="81"/>
-      <c r="AB66" s="90"/>
-      <c r="AC66" s="92"/>
+      <c r="AB66" s="111"/>
+      <c r="AC66" s="112"/>
       <c r="AD66" s="1"/>
       <c r="AE66" s="1"/>
       <c r="AF66" s="1"/>
@@ -38692,35 +38692,6 @@
     </row>
   </sheetData>
   <mergeCells count="45">
-    <mergeCell ref="R3:Y3"/>
-    <mergeCell ref="R4:Y4"/>
-    <mergeCell ref="Z16:Z18"/>
-    <mergeCell ref="AB16:AB18"/>
-    <mergeCell ref="AC16:AC18"/>
-    <mergeCell ref="Z19:Z21"/>
-    <mergeCell ref="AB19:AB21"/>
-    <mergeCell ref="AC19:AC21"/>
-    <mergeCell ref="Z25:Z27"/>
-    <mergeCell ref="AB25:AB27"/>
-    <mergeCell ref="AC25:AC27"/>
-    <mergeCell ref="Z28:Z30"/>
-    <mergeCell ref="AB28:AB30"/>
-    <mergeCell ref="AC28:AC30"/>
-    <mergeCell ref="Z31:Z33"/>
-    <mergeCell ref="AB31:AB33"/>
-    <mergeCell ref="AC31:AC33"/>
-    <mergeCell ref="Z34:Z36"/>
-    <mergeCell ref="AB34:AB36"/>
-    <mergeCell ref="AC34:AC36"/>
-    <mergeCell ref="Z37:Z39"/>
-    <mergeCell ref="AB37:AB39"/>
-    <mergeCell ref="AC37:AC39"/>
-    <mergeCell ref="AC52:AC54"/>
-    <mergeCell ref="Z40:Z42"/>
-    <mergeCell ref="AB40:AB42"/>
-    <mergeCell ref="AC40:AC42"/>
-    <mergeCell ref="AB43:AB45"/>
-    <mergeCell ref="AC43:AC45"/>
     <mergeCell ref="AB64:AB66"/>
     <mergeCell ref="AC64:AC66"/>
     <mergeCell ref="Z22:Z24"/>
@@ -38737,6 +38708,35 @@
     <mergeCell ref="AB49:AB51"/>
     <mergeCell ref="AC49:AC51"/>
     <mergeCell ref="AB52:AB54"/>
+    <mergeCell ref="AC52:AC54"/>
+    <mergeCell ref="Z40:Z42"/>
+    <mergeCell ref="AB40:AB42"/>
+    <mergeCell ref="AC40:AC42"/>
+    <mergeCell ref="AB43:AB45"/>
+    <mergeCell ref="AC43:AC45"/>
+    <mergeCell ref="Z34:Z36"/>
+    <mergeCell ref="AB34:AB36"/>
+    <mergeCell ref="AC34:AC36"/>
+    <mergeCell ref="Z37:Z39"/>
+    <mergeCell ref="AB37:AB39"/>
+    <mergeCell ref="AC37:AC39"/>
+    <mergeCell ref="Z28:Z30"/>
+    <mergeCell ref="AB28:AB30"/>
+    <mergeCell ref="AC28:AC30"/>
+    <mergeCell ref="Z31:Z33"/>
+    <mergeCell ref="AB31:AB33"/>
+    <mergeCell ref="AC31:AC33"/>
+    <mergeCell ref="Z19:Z21"/>
+    <mergeCell ref="AB19:AB21"/>
+    <mergeCell ref="AC19:AC21"/>
+    <mergeCell ref="Z25:Z27"/>
+    <mergeCell ref="AB25:AB27"/>
+    <mergeCell ref="AC25:AC27"/>
+    <mergeCell ref="R3:Y3"/>
+    <mergeCell ref="R4:Y4"/>
+    <mergeCell ref="Z16:Z18"/>
+    <mergeCell ref="AB16:AB18"/>
+    <mergeCell ref="AC16:AC18"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/results.xlsx
+++ b/results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utilizador\Desktop\uni\MEI 1ano1sem\DAA\trabalho\DAA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECBF6386-0897-4F99-B241-8CFD17F79DAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FC1C2E3-03F2-4F3E-82C4-F4058E97FF96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="14020" xr2:uid="{744B1543-7C44-49C5-883E-AA14D96B6E1A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{744B1543-7C44-49C5-883E-AA14D96B6E1A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="285">
   <si>
     <t>DAA tests and results</t>
   </si>
@@ -880,6 +880,18 @@
   <si>
     <t>0.380</t>
   </si>
+  <si>
+    <t>0.358</t>
+  </si>
+  <si>
+    <t>ANN1</t>
+  </si>
+  <si>
+    <t>0.376</t>
+  </si>
+  <si>
+    <t>0.374</t>
+  </si>
 </sst>
 </file>
 
@@ -1617,8 +1629,20 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1626,25 +1650,16 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1665,20 +1680,17 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1981,21 +1993,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF73C760-38F4-492B-831A-21BC2182F932}">
   <dimension ref="A1:BU476"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="19.81640625" customWidth="1"/>
-    <col min="10" max="10" width="17.1796875" customWidth="1"/>
-    <col min="18" max="18" width="19.1796875" customWidth="1"/>
-    <col min="25" max="25" width="8.7265625" customWidth="1"/>
-    <col min="26" max="26" width="16.81640625" customWidth="1"/>
-    <col min="27" max="27" width="73.7265625" customWidth="1"/>
-    <col min="33" max="33" width="23.453125" customWidth="1"/>
-    <col min="35" max="35" width="18.1796875" customWidth="1"/>
-    <col min="41" max="41" width="49.54296875" customWidth="1"/>
-    <col min="43" max="43" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.85546875" customWidth="1"/>
+    <col min="10" max="10" width="17.140625" customWidth="1"/>
+    <col min="18" max="18" width="19.140625" customWidth="1"/>
+    <col min="25" max="25" width="8.7109375" customWidth="1"/>
+    <col min="26" max="26" width="16.85546875" customWidth="1"/>
+    <col min="27" max="27" width="73.7109375" customWidth="1"/>
+    <col min="33" max="33" width="23.42578125" customWidth="1"/>
+    <col min="35" max="35" width="18.140625" customWidth="1"/>
+    <col min="41" max="41" width="49.5703125" customWidth="1"/>
+    <col min="43" max="43" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2070,7 +2082,7 @@
       <c r="BT1" s="1"/>
       <c r="BU1" s="1"/>
     </row>
-    <row r="2" spans="1:73" ht="36" x14ac:dyDescent="0.8">
+    <row r="2" spans="1:73" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1"/>
       <c r="B2" s="2" t="s">
         <v>0</v>
@@ -2147,7 +2159,7 @@
       <c r="BT2" s="1"/>
       <c r="BU2" s="1"/>
     </row>
-    <row r="3" spans="1:73" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:73" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="3" t="s">
         <v>46</v>
@@ -2169,16 +2181,16 @@
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
-      <c r="R3" s="92" t="s">
+      <c r="R3" s="112" t="s">
         <v>119</v>
       </c>
-      <c r="S3" s="92"/>
-      <c r="T3" s="92"/>
-      <c r="U3" s="92"/>
-      <c r="V3" s="92"/>
-      <c r="W3" s="92"/>
-      <c r="X3" s="92"/>
-      <c r="Y3" s="92"/>
+      <c r="S3" s="112"/>
+      <c r="T3" s="112"/>
+      <c r="U3" s="112"/>
+      <c r="V3" s="112"/>
+      <c r="W3" s="112"/>
+      <c r="X3" s="112"/>
+      <c r="Y3" s="112"/>
       <c r="Z3" s="73" t="s">
         <v>149</v>
       </c>
@@ -2234,7 +2246,7 @@
       <c r="BT3" s="1"/>
       <c r="BU3" s="1"/>
     </row>
-    <row r="4" spans="1:73" ht="15.65" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:73" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="4" t="s">
         <v>47</v>
@@ -2256,16 +2268,16 @@
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
-      <c r="R4" s="92" t="s">
+      <c r="R4" s="112" t="s">
         <v>120</v>
       </c>
-      <c r="S4" s="92"/>
-      <c r="T4" s="92"/>
-      <c r="U4" s="92"/>
-      <c r="V4" s="92"/>
-      <c r="W4" s="92"/>
-      <c r="X4" s="92"/>
-      <c r="Y4" s="92"/>
+      <c r="S4" s="112"/>
+      <c r="T4" s="112"/>
+      <c r="U4" s="112"/>
+      <c r="V4" s="112"/>
+      <c r="W4" s="112"/>
+      <c r="X4" s="112"/>
+      <c r="Y4" s="112"/>
       <c r="Z4" s="73" t="s">
         <v>150</v>
       </c>
@@ -2321,7 +2333,7 @@
       <c r="BT4" s="1"/>
       <c r="BU4" s="1"/>
     </row>
-    <row r="5" spans="1:73" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:73" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -2406,7 +2418,7 @@
       <c r="BT5" s="1"/>
       <c r="BU5" s="1"/>
     </row>
-    <row r="6" spans="1:73" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:73" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="14" t="s">
         <v>49</v>
@@ -2501,7 +2513,7 @@
       <c r="BT6" s="1"/>
       <c r="BU6" s="1"/>
     </row>
-    <row r="7" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="18"/>
       <c r="C7" s="26"/>
@@ -2592,7 +2604,7 @@
       <c r="BT7" s="1"/>
       <c r="BU7" s="1"/>
     </row>
-    <row r="8" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="19" t="s">
         <v>50</v>
@@ -2687,7 +2699,7 @@
       <c r="BT8" s="1"/>
       <c r="BU8" s="1"/>
     </row>
-    <row r="9" spans="1:73" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="24"/>
       <c r="C9" s="28"/>
@@ -2776,7 +2788,7 @@
       <c r="BT9" s="1"/>
       <c r="BU9" s="1"/>
     </row>
-    <row r="10" spans="1:73" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="21" t="s">
         <v>52</v>
@@ -2871,7 +2883,7 @@
       <c r="BT10" s="1"/>
       <c r="BU10" s="1"/>
     </row>
-    <row r="11" spans="1:73" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="21" t="s">
         <v>51</v>
@@ -2959,7 +2971,7 @@
       <c r="AQ11" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="AR11" s="59" t="s">
+      <c r="AR11" s="11" t="s">
         <v>2</v>
       </c>
       <c r="AS11" s="47" t="s">
@@ -2994,7 +3006,7 @@
       <c r="BT11" s="1"/>
       <c r="BU11" s="1"/>
     </row>
-    <row r="12" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="25" t="s">
         <v>53</v>
@@ -3070,7 +3082,7 @@
       <c r="AQ12" s="57" t="s">
         <v>220</v>
       </c>
-      <c r="AR12" s="60" t="s">
+      <c r="AR12" s="57" t="s">
         <v>270</v>
       </c>
       <c r="AS12" s="20" t="s">
@@ -3105,7 +3117,7 @@
       <c r="BT12" s="1"/>
       <c r="BU12" s="1"/>
     </row>
-    <row r="13" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="19" t="s">
         <v>52</v>
@@ -3183,8 +3195,8 @@
       <c r="AQ13" s="57" t="s">
         <v>222</v>
       </c>
-      <c r="AR13" s="60" t="s">
-        <v>28</v>
+      <c r="AR13" s="57" t="s">
+        <v>281</v>
       </c>
       <c r="AS13" s="20" t="s">
         <v>280</v>
@@ -3218,7 +3230,7 @@
       <c r="BT13" s="1"/>
       <c r="BU13" s="1"/>
     </row>
-    <row r="14" spans="1:73" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="19" t="s">
         <v>51</v>
@@ -3302,7 +3314,7 @@
       <c r="AQ14" s="57" t="s">
         <v>224</v>
       </c>
-      <c r="AR14" s="61" t="s">
+      <c r="AR14" s="88" t="s">
         <v>271</v>
       </c>
       <c r="AS14" s="20"/>
@@ -3335,7 +3347,7 @@
       <c r="BT14" s="1"/>
       <c r="BU14" s="1"/>
     </row>
-    <row r="15" spans="1:73" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="24" t="s">
         <v>54</v>
@@ -3425,7 +3437,7 @@
       <c r="AQ15" s="52" t="s">
         <v>225</v>
       </c>
-      <c r="AR15" s="62" t="s">
+      <c r="AR15" s="52" t="s">
         <v>272</v>
       </c>
       <c r="AS15" s="42"/>
@@ -3458,7 +3470,7 @@
       <c r="BT15" s="1"/>
       <c r="BU15" s="1"/>
     </row>
-    <row r="16" spans="1:73" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="21" t="s">
         <v>55</v>
@@ -3508,16 +3520,16 @@
       <c r="W16" s="1"/>
       <c r="X16" s="1"/>
       <c r="Y16" s="1"/>
-      <c r="Z16" s="93" t="s">
+      <c r="Z16" s="97" t="s">
         <v>218</v>
       </c>
       <c r="AA16" s="78" t="s">
         <v>161</v>
       </c>
-      <c r="AB16" s="95" t="s">
+      <c r="AB16" s="92" t="s">
         <v>163</v>
       </c>
-      <c r="AC16" s="97" t="s">
+      <c r="AC16" s="94" t="s">
         <v>103</v>
       </c>
       <c r="AD16" s="1"/>
@@ -3548,7 +3560,7 @@
       <c r="AQ16" s="52" t="s">
         <v>226</v>
       </c>
-      <c r="AR16" s="62" t="s">
+      <c r="AR16" s="52" t="s">
         <v>273</v>
       </c>
       <c r="AS16" s="42"/>
@@ -3581,7 +3593,7 @@
       <c r="BT16" s="1"/>
       <c r="BU16" s="1"/>
     </row>
-    <row r="17" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="21" t="s">
         <v>56</v>
@@ -3629,12 +3641,12 @@
       <c r="W17" s="1"/>
       <c r="X17" s="1"/>
       <c r="Y17" s="1"/>
-      <c r="Z17" s="93"/>
+      <c r="Z17" s="97"/>
       <c r="AA17" s="78" t="s">
         <v>165</v>
       </c>
-      <c r="AB17" s="95"/>
-      <c r="AC17" s="97"/>
+      <c r="AB17" s="92"/>
+      <c r="AC17" s="94"/>
       <c r="AD17" s="1"/>
       <c r="AE17" s="1"/>
       <c r="AF17" s="1"/>
@@ -3653,7 +3665,7 @@
       <c r="AQ17" s="52" t="s">
         <v>234</v>
       </c>
-      <c r="AR17" s="62" t="s">
+      <c r="AR17" s="52" t="s">
         <v>274</v>
       </c>
       <c r="AS17" s="42"/>
@@ -3686,7 +3698,7 @@
       <c r="BT17" s="1"/>
       <c r="BU17" s="1"/>
     </row>
-    <row r="18" spans="1:73" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:73" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="25" t="s">
         <v>57</v>
@@ -3732,12 +3744,12 @@
       <c r="W18" s="1"/>
       <c r="X18" s="1"/>
       <c r="Y18" s="1"/>
-      <c r="Z18" s="94"/>
+      <c r="Z18" s="98"/>
       <c r="AA18" s="79" t="s">
         <v>162</v>
       </c>
-      <c r="AB18" s="96"/>
-      <c r="AC18" s="98"/>
+      <c r="AB18" s="100"/>
+      <c r="AC18" s="102"/>
       <c r="AD18" s="1"/>
       <c r="AE18" s="1"/>
       <c r="AF18" s="1"/>
@@ -3756,7 +3768,7 @@
       <c r="AQ18" s="52" t="s">
         <v>236</v>
       </c>
-      <c r="AR18" s="62" t="s">
+      <c r="AR18" s="52" t="s">
         <v>275</v>
       </c>
       <c r="AS18" s="42"/>
@@ -3789,7 +3801,7 @@
       <c r="BT18" s="1"/>
       <c r="BU18" s="1"/>
     </row>
-    <row r="19" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="19" t="s">
         <v>55</v>
@@ -3837,16 +3849,16 @@
       <c r="W19" s="1"/>
       <c r="X19" s="1"/>
       <c r="Y19" s="1"/>
-      <c r="Z19" s="99" t="s">
+      <c r="Z19" s="109" t="s">
         <v>219</v>
       </c>
       <c r="AA19" s="82" t="s">
         <v>161</v>
       </c>
-      <c r="AB19" s="102" t="s">
+      <c r="AB19" s="103" t="s">
         <v>117</v>
       </c>
-      <c r="AC19" s="105" t="s">
+      <c r="AC19" s="106" t="s">
         <v>166</v>
       </c>
       <c r="AD19" s="1"/>
@@ -3867,7 +3879,7 @@
       <c r="AQ19" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="AR19" s="62" t="s">
+      <c r="AR19" s="52" t="s">
         <v>276</v>
       </c>
       <c r="AS19" s="42"/>
@@ -3900,7 +3912,7 @@
       <c r="BT19" s="1"/>
       <c r="BU19" s="1"/>
     </row>
-    <row r="20" spans="1:73" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="19" t="s">
         <v>56</v>
@@ -3952,12 +3964,12 @@
       <c r="W20" s="1"/>
       <c r="X20" s="1"/>
       <c r="Y20" s="1"/>
-      <c r="Z20" s="100"/>
+      <c r="Z20" s="110"/>
       <c r="AA20" s="84" t="s">
         <v>164</v>
       </c>
-      <c r="AB20" s="103"/>
-      <c r="AC20" s="106"/>
+      <c r="AB20" s="104"/>
+      <c r="AC20" s="107"/>
       <c r="AD20" s="1"/>
       <c r="AE20" s="1"/>
       <c r="AF20" s="1"/>
@@ -3971,15 +3983,15 @@
       <c r="AL20" s="1"/>
       <c r="AM20" s="1"/>
       <c r="AN20" s="1"/>
-      <c r="AO20" s="91"/>
-      <c r="AP20" s="58"/>
-      <c r="AQ20" s="58" t="s">
+      <c r="AO20" s="90"/>
+      <c r="AP20" s="52"/>
+      <c r="AQ20" s="52" t="s">
         <v>240</v>
       </c>
-      <c r="AR20" s="68" t="s">
+      <c r="AR20" s="52" t="s">
         <v>277</v>
       </c>
-      <c r="AS20" s="44"/>
+      <c r="AS20" s="42"/>
       <c r="AT20" s="1"/>
       <c r="AU20" s="1"/>
       <c r="AV20" s="1"/>
@@ -4009,7 +4021,7 @@
       <c r="BT20" s="1"/>
       <c r="BU20" s="1"/>
     </row>
-    <row r="21" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="24" t="s">
         <v>58</v>
@@ -4061,12 +4073,12 @@
       <c r="W21" s="1"/>
       <c r="X21" s="1"/>
       <c r="Y21" s="1"/>
-      <c r="Z21" s="101"/>
+      <c r="Z21" s="111"/>
       <c r="AA21" s="86" t="s">
         <v>162</v>
       </c>
-      <c r="AB21" s="104"/>
-      <c r="AC21" s="107"/>
+      <c r="AB21" s="105"/>
+      <c r="AC21" s="108"/>
       <c r="AD21" s="1"/>
       <c r="AE21" s="1"/>
       <c r="AF21" s="1"/>
@@ -4080,11 +4092,17 @@
       <c r="AL21" s="1"/>
       <c r="AM21" s="1"/>
       <c r="AN21" s="1"/>
-      <c r="AO21" s="1"/>
-      <c r="AP21" s="1"/>
-      <c r="AQ21" s="1"/>
-      <c r="AR21" s="1"/>
-      <c r="AS21" s="1"/>
+      <c r="AO21" s="91"/>
+      <c r="AP21" s="58"/>
+      <c r="AQ21" s="58" t="s">
+        <v>282</v>
+      </c>
+      <c r="AR21" s="58" t="s">
+        <v>284</v>
+      </c>
+      <c r="AS21" s="44" t="s">
+        <v>283</v>
+      </c>
       <c r="AT21" s="1"/>
       <c r="AU21" s="1"/>
       <c r="AV21" s="1"/>
@@ -4114,7 +4132,7 @@
       <c r="BT21" s="1"/>
       <c r="BU21" s="1"/>
     </row>
-    <row r="22" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="21" t="s">
         <v>71</v>
@@ -4166,16 +4184,16 @@
       <c r="W22" s="1"/>
       <c r="X22" s="1"/>
       <c r="Y22" s="1"/>
-      <c r="Z22" s="108" t="s">
+      <c r="Z22" s="96" t="s">
         <v>220</v>
       </c>
       <c r="AA22" s="80" t="s">
         <v>215</v>
       </c>
-      <c r="AB22" s="109" t="s">
+      <c r="AB22" s="99" t="s">
         <v>214</v>
       </c>
-      <c r="AC22" s="110" t="s">
+      <c r="AC22" s="101" t="s">
         <v>217</v>
       </c>
       <c r="AD22" s="1"/>
@@ -4225,7 +4243,7 @@
       <c r="BT22" s="1"/>
       <c r="BU22" s="1"/>
     </row>
-    <row r="23" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="21" t="s">
         <v>72</v>
@@ -4277,12 +4295,12 @@
       <c r="W23" s="1"/>
       <c r="X23" s="1"/>
       <c r="Y23" s="1"/>
-      <c r="Z23" s="93"/>
+      <c r="Z23" s="97"/>
       <c r="AA23" s="78" t="s">
         <v>216</v>
       </c>
-      <c r="AB23" s="95"/>
-      <c r="AC23" s="97"/>
+      <c r="AB23" s="92"/>
+      <c r="AC23" s="94"/>
       <c r="AD23" s="1"/>
       <c r="AE23" s="1"/>
       <c r="AF23" s="1"/>
@@ -4330,7 +4348,7 @@
       <c r="BT23" s="1"/>
       <c r="BU23" s="1"/>
     </row>
-    <row r="24" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="25"/>
       <c r="C24" s="30"/>
@@ -4376,12 +4394,12 @@
       <c r="W24" s="1"/>
       <c r="X24" s="1"/>
       <c r="Y24" s="1"/>
-      <c r="Z24" s="94"/>
+      <c r="Z24" s="98"/>
       <c r="AA24" s="79" t="s">
         <v>162</v>
       </c>
-      <c r="AB24" s="96"/>
-      <c r="AC24" s="98"/>
+      <c r="AB24" s="100"/>
+      <c r="AC24" s="102"/>
       <c r="AD24" s="1"/>
       <c r="AE24" s="1"/>
       <c r="AF24" s="1"/>
@@ -4427,7 +4445,7 @@
       <c r="BT24" s="1"/>
       <c r="BU24" s="1"/>
     </row>
-    <row r="25" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="19"/>
       <c r="C25" s="27"/>
@@ -4471,16 +4489,16 @@
       <c r="W25" s="1"/>
       <c r="X25" s="1"/>
       <c r="Y25" s="1"/>
-      <c r="Z25" s="99" t="s">
+      <c r="Z25" s="109" t="s">
         <v>221</v>
       </c>
       <c r="AA25" s="82" t="s">
         <v>169</v>
       </c>
-      <c r="AB25" s="102" t="s">
+      <c r="AB25" s="103" t="s">
         <v>193</v>
       </c>
-      <c r="AC25" s="105" t="s">
+      <c r="AC25" s="106" t="s">
         <v>204</v>
       </c>
       <c r="AD25" s="1"/>
@@ -4528,7 +4546,7 @@
       <c r="BT25" s="1"/>
       <c r="BU25" s="1"/>
     </row>
-    <row r="26" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="19" t="s">
         <v>59</v>
@@ -4572,12 +4590,12 @@
       <c r="W26" s="1"/>
       <c r="X26" s="1"/>
       <c r="Y26" s="1"/>
-      <c r="Z26" s="100"/>
+      <c r="Z26" s="110"/>
       <c r="AA26" s="84" t="s">
         <v>167</v>
       </c>
-      <c r="AB26" s="103"/>
-      <c r="AC26" s="106"/>
+      <c r="AB26" s="104"/>
+      <c r="AC26" s="107"/>
       <c r="AD26" s="1"/>
       <c r="AE26" s="1"/>
       <c r="AF26" s="1"/>
@@ -4623,7 +4641,7 @@
       <c r="BT26" s="1"/>
       <c r="BU26" s="1"/>
     </row>
-    <row r="27" spans="1:73" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:73" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="24"/>
       <c r="C27" s="28"/>
@@ -4665,12 +4683,12 @@
       <c r="W27" s="1"/>
       <c r="X27" s="1"/>
       <c r="Y27" s="1"/>
-      <c r="Z27" s="101"/>
+      <c r="Z27" s="111"/>
       <c r="AA27" s="86" t="s">
         <v>168</v>
       </c>
-      <c r="AB27" s="104"/>
-      <c r="AC27" s="107"/>
+      <c r="AB27" s="105"/>
+      <c r="AC27" s="108"/>
       <c r="AD27" s="1"/>
       <c r="AE27" s="1"/>
       <c r="AF27" s="1"/>
@@ -4716,7 +4734,7 @@
       <c r="BT27" s="1"/>
       <c r="BU27" s="1"/>
     </row>
-    <row r="28" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="21"/>
       <c r="C28" s="29"/>
@@ -4760,16 +4778,16 @@
       <c r="W28" s="1"/>
       <c r="X28" s="1"/>
       <c r="Y28" s="1"/>
-      <c r="Z28" s="108" t="s">
+      <c r="Z28" s="96" t="s">
         <v>222</v>
       </c>
       <c r="AA28" s="80" t="s">
         <v>169</v>
       </c>
-      <c r="AB28" s="109" t="s">
+      <c r="AB28" s="99" t="s">
         <v>194</v>
       </c>
-      <c r="AC28" s="110" t="s">
+      <c r="AC28" s="101" t="s">
         <v>205</v>
       </c>
       <c r="AD28" s="1"/>
@@ -4817,7 +4835,7 @@
       <c r="BT28" s="1"/>
       <c r="BU28" s="1"/>
     </row>
-    <row r="29" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="21" t="s">
         <v>60</v>
@@ -4863,12 +4881,12 @@
       <c r="W29" s="1"/>
       <c r="X29" s="1"/>
       <c r="Y29" s="1"/>
-      <c r="Z29" s="93"/>
+      <c r="Z29" s="97"/>
       <c r="AA29" s="78" t="s">
         <v>170</v>
       </c>
-      <c r="AB29" s="95"/>
-      <c r="AC29" s="97"/>
+      <c r="AB29" s="92"/>
+      <c r="AC29" s="94"/>
       <c r="AD29" s="1"/>
       <c r="AE29" s="1"/>
       <c r="AF29" s="1"/>
@@ -4914,7 +4932,7 @@
       <c r="BT29" s="1"/>
       <c r="BU29" s="1"/>
     </row>
-    <row r="30" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="25"/>
       <c r="C30" s="30"/>
@@ -4956,12 +4974,12 @@
       <c r="W30" s="1"/>
       <c r="X30" s="1"/>
       <c r="Y30" s="1"/>
-      <c r="Z30" s="94"/>
+      <c r="Z30" s="98"/>
       <c r="AA30" s="79" t="s">
         <v>168</v>
       </c>
-      <c r="AB30" s="96"/>
-      <c r="AC30" s="98"/>
+      <c r="AB30" s="100"/>
+      <c r="AC30" s="102"/>
       <c r="AD30" s="1"/>
       <c r="AE30" s="1"/>
       <c r="AF30" s="1"/>
@@ -5007,7 +5025,7 @@
       <c r="BT30" s="1"/>
       <c r="BU30" s="1"/>
     </row>
-    <row r="31" spans="1:73" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="19" t="s">
         <v>61</v>
@@ -5047,16 +5065,16 @@
       <c r="W31" s="1"/>
       <c r="X31" s="1"/>
       <c r="Y31" s="1"/>
-      <c r="Z31" s="99" t="s">
+      <c r="Z31" s="109" t="s">
         <v>223</v>
       </c>
       <c r="AA31" s="82" t="s">
         <v>174</v>
       </c>
-      <c r="AB31" s="102" t="s">
+      <c r="AB31" s="103" t="s">
         <v>45</v>
       </c>
-      <c r="AC31" s="105" t="s">
+      <c r="AC31" s="106" t="s">
         <v>10</v>
       </c>
       <c r="AD31" s="1"/>
@@ -5104,7 +5122,7 @@
       <c r="BT31" s="1"/>
       <c r="BU31" s="1"/>
     </row>
-    <row r="32" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="19" t="s">
         <v>62</v>
@@ -5140,12 +5158,12 @@
       <c r="W32" s="1"/>
       <c r="X32" s="1"/>
       <c r="Y32" s="1"/>
-      <c r="Z32" s="100"/>
+      <c r="Z32" s="110"/>
       <c r="AA32" s="84" t="s">
         <v>175</v>
       </c>
-      <c r="AB32" s="103"/>
-      <c r="AC32" s="106"/>
+      <c r="AB32" s="104"/>
+      <c r="AC32" s="107"/>
       <c r="AD32" s="1"/>
       <c r="AE32" s="1"/>
       <c r="AF32" s="1"/>
@@ -5191,7 +5209,7 @@
       <c r="BT32" s="1"/>
       <c r="BU32" s="1"/>
     </row>
-    <row r="33" spans="1:73" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:73" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="B33" s="24" t="s">
         <v>63</v>
@@ -5227,12 +5245,12 @@
       <c r="W33" s="1"/>
       <c r="X33" s="1"/>
       <c r="Y33" s="1"/>
-      <c r="Z33" s="101"/>
+      <c r="Z33" s="111"/>
       <c r="AA33" s="86" t="s">
         <v>173</v>
       </c>
-      <c r="AB33" s="104"/>
-      <c r="AC33" s="107"/>
+      <c r="AB33" s="105"/>
+      <c r="AC33" s="108"/>
       <c r="AD33" s="1"/>
       <c r="AE33" s="1"/>
       <c r="AF33" s="1"/>
@@ -5278,7 +5296,7 @@
       <c r="BT33" s="1"/>
       <c r="BU33" s="1"/>
     </row>
-    <row r="34" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="B34" s="21"/>
       <c r="C34" s="29"/>
@@ -5312,16 +5330,16 @@
       <c r="W34" s="1"/>
       <c r="X34" s="1"/>
       <c r="Y34" s="1"/>
-      <c r="Z34" s="108" t="s">
+      <c r="Z34" s="96" t="s">
         <v>224</v>
       </c>
       <c r="AA34" s="80" t="s">
         <v>171</v>
       </c>
-      <c r="AB34" s="109" t="s">
+      <c r="AB34" s="99" t="s">
         <v>195</v>
       </c>
-      <c r="AC34" s="110" t="s">
+      <c r="AC34" s="101" t="s">
         <v>102</v>
       </c>
       <c r="AD34" s="1"/>
@@ -5369,7 +5387,7 @@
       <c r="BT34" s="1"/>
       <c r="BU34" s="1"/>
     </row>
-    <row r="35" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="B35" s="21" t="s">
         <v>64</v>
@@ -5405,12 +5423,12 @@
       <c r="W35" s="1"/>
       <c r="X35" s="1"/>
       <c r="Y35" s="1"/>
-      <c r="Z35" s="93"/>
+      <c r="Z35" s="97"/>
       <c r="AA35" s="78" t="s">
         <v>172</v>
       </c>
-      <c r="AB35" s="95"/>
-      <c r="AC35" s="97"/>
+      <c r="AB35" s="92"/>
+      <c r="AC35" s="94"/>
       <c r="AD35" s="1"/>
       <c r="AE35" s="1"/>
       <c r="AF35" s="1"/>
@@ -5456,7 +5474,7 @@
       <c r="BT35" s="1"/>
       <c r="BU35" s="1"/>
     </row>
-    <row r="36" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="B36" s="25"/>
       <c r="C36" s="30"/>
@@ -5488,12 +5506,12 @@
       <c r="W36" s="1"/>
       <c r="X36" s="1"/>
       <c r="Y36" s="1"/>
-      <c r="Z36" s="94"/>
+      <c r="Z36" s="98"/>
       <c r="AA36" s="79" t="s">
         <v>173</v>
       </c>
-      <c r="AB36" s="96"/>
-      <c r="AC36" s="98"/>
+      <c r="AB36" s="100"/>
+      <c r="AC36" s="102"/>
       <c r="AD36" s="1"/>
       <c r="AE36" s="1"/>
       <c r="AF36" s="1"/>
@@ -5539,7 +5557,7 @@
       <c r="BT36" s="1"/>
       <c r="BU36" s="1"/>
     </row>
-    <row r="37" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="B37" s="19" t="s">
         <v>65</v>
@@ -5573,16 +5591,16 @@
       <c r="W37" s="1"/>
       <c r="X37" s="1"/>
       <c r="Y37" s="1"/>
-      <c r="Z37" s="99" t="s">
+      <c r="Z37" s="109" t="s">
         <v>225</v>
       </c>
       <c r="AA37" s="82" t="s">
         <v>176</v>
       </c>
-      <c r="AB37" s="102" t="s">
+      <c r="AB37" s="103" t="s">
         <v>196</v>
       </c>
-      <c r="AC37" s="105" t="s">
+      <c r="AC37" s="106" t="s">
         <v>206</v>
       </c>
       <c r="AD37" s="1"/>
@@ -5630,7 +5648,7 @@
       <c r="BT37" s="1"/>
       <c r="BU37" s="1"/>
     </row>
-    <row r="38" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="B38" s="19" t="s">
         <v>66</v>
@@ -5666,12 +5684,12 @@
       <c r="W38" s="1"/>
       <c r="X38" s="1"/>
       <c r="Y38" s="1"/>
-      <c r="Z38" s="100"/>
+      <c r="Z38" s="110"/>
       <c r="AA38" s="84" t="s">
         <v>177</v>
       </c>
-      <c r="AB38" s="103"/>
-      <c r="AC38" s="106"/>
+      <c r="AB38" s="104"/>
+      <c r="AC38" s="107"/>
       <c r="AD38" s="1"/>
       <c r="AE38" s="1"/>
       <c r="AF38" s="1"/>
@@ -5717,7 +5735,7 @@
       <c r="BT38" s="1"/>
       <c r="BU38" s="1"/>
     </row>
-    <row r="39" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="B39" s="24" t="s">
         <v>67</v>
@@ -5751,12 +5769,12 @@
       <c r="W39" s="1"/>
       <c r="X39" s="1"/>
       <c r="Y39" s="1"/>
-      <c r="Z39" s="101"/>
+      <c r="Z39" s="111"/>
       <c r="AA39" s="86" t="s">
         <v>178</v>
       </c>
-      <c r="AB39" s="104"/>
-      <c r="AC39" s="107"/>
+      <c r="AB39" s="105"/>
+      <c r="AC39" s="108"/>
       <c r="AD39" s="1"/>
       <c r="AE39" s="1"/>
       <c r="AF39" s="1"/>
@@ -5802,7 +5820,7 @@
       <c r="BT39" s="1"/>
       <c r="BU39" s="1"/>
     </row>
-    <row r="40" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
       <c r="B40" s="21" t="s">
         <v>68</v>
@@ -5836,16 +5854,16 @@
       <c r="W40" s="1"/>
       <c r="X40" s="1"/>
       <c r="Y40" s="1"/>
-      <c r="Z40" s="108" t="s">
+      <c r="Z40" s="96" t="s">
         <v>226</v>
       </c>
       <c r="AA40" s="80" t="s">
         <v>179</v>
       </c>
-      <c r="AB40" s="109" t="s">
+      <c r="AB40" s="99" t="s">
         <v>197</v>
       </c>
-      <c r="AC40" s="110" t="s">
+      <c r="AC40" s="101" t="s">
         <v>207</v>
       </c>
       <c r="AD40" s="1"/>
@@ -5893,7 +5911,7 @@
       <c r="BT40" s="1"/>
       <c r="BU40" s="1"/>
     </row>
-    <row r="41" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" s="21" t="s">
         <v>69</v>
@@ -5929,12 +5947,12 @@
       <c r="W41" s="1"/>
       <c r="X41" s="1"/>
       <c r="Y41" s="1"/>
-      <c r="Z41" s="93"/>
+      <c r="Z41" s="97"/>
       <c r="AA41" s="78" t="s">
         <v>180</v>
       </c>
-      <c r="AB41" s="95"/>
-      <c r="AC41" s="97"/>
+      <c r="AB41" s="92"/>
+      <c r="AC41" s="94"/>
       <c r="AD41" s="1"/>
       <c r="AE41" s="1"/>
       <c r="AF41" s="1"/>
@@ -5980,7 +5998,7 @@
       <c r="BT41" s="1"/>
       <c r="BU41" s="1"/>
     </row>
-    <row r="42" spans="1:73" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
       <c r="B42" s="23" t="s">
         <v>70</v>
@@ -6014,12 +6032,12 @@
       <c r="W42" s="1"/>
       <c r="X42" s="1"/>
       <c r="Y42" s="1"/>
-      <c r="Z42" s="94"/>
+      <c r="Z42" s="98"/>
       <c r="AA42" s="79" t="s">
         <v>181</v>
       </c>
-      <c r="AB42" s="96"/>
-      <c r="AC42" s="98"/>
+      <c r="AB42" s="100"/>
+      <c r="AC42" s="102"/>
       <c r="AD42" s="1"/>
       <c r="AE42" s="1"/>
       <c r="AF42" s="1"/>
@@ -6065,7 +6083,7 @@
       <c r="BT42" s="1"/>
       <c r="BU42" s="1"/>
     </row>
-    <row r="43" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -6097,10 +6115,10 @@
       <c r="AA43" s="82" t="s">
         <v>183</v>
       </c>
-      <c r="AB43" s="102" t="s">
+      <c r="AB43" s="103" t="s">
         <v>198</v>
       </c>
-      <c r="AC43" s="105" t="s">
+      <c r="AC43" s="106" t="s">
         <v>208</v>
       </c>
       <c r="AD43" s="1"/>
@@ -6148,7 +6166,7 @@
       <c r="BT43" s="1"/>
       <c r="BU43" s="1"/>
     </row>
-    <row r="44" spans="1:73" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:73" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
       <c r="B44" s="13" t="s">
         <v>73</v>
@@ -6182,8 +6200,8 @@
       <c r="AA44" s="84" t="s">
         <v>184</v>
       </c>
-      <c r="AB44" s="103"/>
-      <c r="AC44" s="106"/>
+      <c r="AB44" s="104"/>
+      <c r="AC44" s="107"/>
       <c r="AD44" s="1"/>
       <c r="AE44" s="1"/>
       <c r="AF44" s="1"/>
@@ -6229,7 +6247,7 @@
       <c r="BT44" s="1"/>
       <c r="BU44" s="1"/>
     </row>
-    <row r="45" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
       <c r="B45" s="1" t="s">
         <v>77</v>
@@ -6261,8 +6279,8 @@
       <c r="AA45" s="86" t="s">
         <v>185</v>
       </c>
-      <c r="AB45" s="104"/>
-      <c r="AC45" s="107"/>
+      <c r="AB45" s="105"/>
+      <c r="AC45" s="108"/>
       <c r="AD45" s="1"/>
       <c r="AE45" s="1"/>
       <c r="AF45" s="1"/>
@@ -6308,7 +6326,7 @@
       <c r="BT45" s="1"/>
       <c r="BU45" s="1"/>
     </row>
-    <row r="46" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="B46" s="1" t="s">
         <v>75</v>
@@ -6342,10 +6360,10 @@
       <c r="AA46" s="80" t="s">
         <v>186</v>
       </c>
-      <c r="AB46" s="109" t="s">
+      <c r="AB46" s="99" t="s">
         <v>134</v>
       </c>
-      <c r="AC46" s="110" t="s">
+      <c r="AC46" s="101" t="s">
         <v>209</v>
       </c>
       <c r="AD46" s="1"/>
@@ -6393,7 +6411,7 @@
       <c r="BT46" s="1"/>
       <c r="BU46" s="1"/>
     </row>
-    <row r="47" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="B47" s="1" t="s">
         <v>76</v>
@@ -6427,8 +6445,8 @@
       <c r="AA47" s="78" t="s">
         <v>184</v>
       </c>
-      <c r="AB47" s="95"/>
-      <c r="AC47" s="97"/>
+      <c r="AB47" s="92"/>
+      <c r="AC47" s="94"/>
       <c r="AD47" s="1"/>
       <c r="AE47" s="1"/>
       <c r="AF47" s="1"/>
@@ -6474,7 +6492,7 @@
       <c r="BT47" s="1"/>
       <c r="BU47" s="1"/>
     </row>
-    <row r="48" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
       <c r="B48" s="1" t="s">
         <v>78</v>
@@ -6506,8 +6524,8 @@
       <c r="AA48" s="79" t="s">
         <v>185</v>
       </c>
-      <c r="AB48" s="96"/>
-      <c r="AC48" s="98"/>
+      <c r="AB48" s="100"/>
+      <c r="AC48" s="102"/>
       <c r="AD48" s="1"/>
       <c r="AE48" s="1"/>
       <c r="AF48" s="1"/>
@@ -6553,7 +6571,7 @@
       <c r="BT48" s="1"/>
       <c r="BU48" s="1"/>
     </row>
-    <row r="49" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -6585,10 +6603,10 @@
       <c r="AA49" s="82" t="s">
         <v>187</v>
       </c>
-      <c r="AB49" s="102" t="s">
+      <c r="AB49" s="103" t="s">
         <v>28</v>
       </c>
-      <c r="AC49" s="105" t="s">
+      <c r="AC49" s="106" t="s">
         <v>210</v>
       </c>
       <c r="AD49" s="1"/>
@@ -6636,7 +6654,7 @@
       <c r="BT49" s="1"/>
       <c r="BU49" s="1"/>
     </row>
-    <row r="50" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -6668,8 +6686,8 @@
       <c r="AA50" s="84" t="s">
         <v>184</v>
       </c>
-      <c r="AB50" s="103"/>
-      <c r="AC50" s="106"/>
+      <c r="AB50" s="104"/>
+      <c r="AC50" s="107"/>
       <c r="AD50" s="1"/>
       <c r="AE50" s="1"/>
       <c r="AF50" s="1"/>
@@ -6715,7 +6733,7 @@
       <c r="BT50" s="1"/>
       <c r="BU50" s="1"/>
     </row>
-    <row r="51" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -6745,8 +6763,8 @@
       <c r="AA51" s="86" t="s">
         <v>185</v>
       </c>
-      <c r="AB51" s="104"/>
-      <c r="AC51" s="107"/>
+      <c r="AB51" s="105"/>
+      <c r="AC51" s="108"/>
       <c r="AD51" s="1"/>
       <c r="AE51" s="1"/>
       <c r="AF51" s="1"/>
@@ -6792,7 +6810,7 @@
       <c r="BT51" s="1"/>
       <c r="BU51" s="1"/>
     </row>
-    <row r="52" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -6824,10 +6842,10 @@
       <c r="AA52" s="80" t="s">
         <v>188</v>
       </c>
-      <c r="AB52" s="109" t="s">
+      <c r="AB52" s="99" t="s">
         <v>199</v>
       </c>
-      <c r="AC52" s="110" t="s">
+      <c r="AC52" s="101" t="s">
         <v>211</v>
       </c>
       <c r="AD52" s="1"/>
@@ -6875,7 +6893,7 @@
       <c r="BT52" s="1"/>
       <c r="BU52" s="1"/>
     </row>
-    <row r="53" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -6907,8 +6925,8 @@
       <c r="AA53" s="78" t="s">
         <v>184</v>
       </c>
-      <c r="AB53" s="95"/>
-      <c r="AC53" s="97"/>
+      <c r="AB53" s="92"/>
+      <c r="AC53" s="94"/>
       <c r="AD53" s="1"/>
       <c r="AE53" s="1"/>
       <c r="AF53" s="1"/>
@@ -6954,7 +6972,7 @@
       <c r="BT53" s="1"/>
       <c r="BU53" s="1"/>
     </row>
-    <row r="54" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -6984,8 +7002,8 @@
       <c r="AA54" s="79" t="s">
         <v>185</v>
       </c>
-      <c r="AB54" s="96"/>
-      <c r="AC54" s="98"/>
+      <c r="AB54" s="100"/>
+      <c r="AC54" s="102"/>
       <c r="AD54" s="1"/>
       <c r="AE54" s="1"/>
       <c r="AF54" s="1"/>
@@ -7031,7 +7049,7 @@
       <c r="BT54" s="1"/>
       <c r="BU54" s="1"/>
     </row>
-    <row r="55" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -7063,10 +7081,10 @@
       <c r="AA55" s="82" t="s">
         <v>189</v>
       </c>
-      <c r="AB55" s="102" t="s">
+      <c r="AB55" s="103" t="s">
         <v>200</v>
       </c>
-      <c r="AC55" s="105" t="s">
+      <c r="AC55" s="106" t="s">
         <v>212</v>
       </c>
       <c r="AD55" s="1"/>
@@ -7114,7 +7132,7 @@
       <c r="BT55" s="1"/>
       <c r="BU55" s="1"/>
     </row>
-    <row r="56" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -7146,8 +7164,8 @@
       <c r="AA56" s="84" t="s">
         <v>190</v>
       </c>
-      <c r="AB56" s="103"/>
-      <c r="AC56" s="106"/>
+      <c r="AB56" s="104"/>
+      <c r="AC56" s="107"/>
       <c r="AD56" s="1"/>
       <c r="AE56" s="1"/>
       <c r="AF56" s="1"/>
@@ -7193,7 +7211,7 @@
       <c r="BT56" s="1"/>
       <c r="BU56" s="1"/>
     </row>
-    <row r="57" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -7221,8 +7239,8 @@
       <c r="Y57" s="1"/>
       <c r="Z57" s="85"/>
       <c r="AA57" s="86"/>
-      <c r="AB57" s="104"/>
-      <c r="AC57" s="107"/>
+      <c r="AB57" s="105"/>
+      <c r="AC57" s="108"/>
       <c r="AD57" s="1"/>
       <c r="AE57" s="1"/>
       <c r="AF57" s="1"/>
@@ -7268,7 +7286,7 @@
       <c r="BT57" s="1"/>
       <c r="BU57" s="1"/>
     </row>
-    <row r="58" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -7300,10 +7318,10 @@
       <c r="AA58" s="80" t="s">
         <v>191</v>
       </c>
-      <c r="AB58" s="109" t="s">
+      <c r="AB58" s="99" t="s">
         <v>201</v>
       </c>
-      <c r="AC58" s="110" t="s">
+      <c r="AC58" s="101" t="s">
         <v>213</v>
       </c>
       <c r="AD58" s="1"/>
@@ -7351,7 +7369,7 @@
       <c r="BT58" s="1"/>
       <c r="BU58" s="1"/>
     </row>
-    <row r="59" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -7383,8 +7401,8 @@
       <c r="AA59" s="78" t="s">
         <v>190</v>
       </c>
-      <c r="AB59" s="95"/>
-      <c r="AC59" s="97"/>
+      <c r="AB59" s="92"/>
+      <c r="AC59" s="94"/>
       <c r="AD59" s="1"/>
       <c r="AE59" s="1"/>
       <c r="AF59" s="1"/>
@@ -7430,7 +7448,7 @@
       <c r="BT59" s="1"/>
       <c r="BU59" s="1"/>
     </row>
-    <row r="60" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -7458,8 +7476,8 @@
       <c r="Y60" s="1"/>
       <c r="Z60" s="77"/>
       <c r="AA60" s="79"/>
-      <c r="AB60" s="96"/>
-      <c r="AC60" s="98"/>
+      <c r="AB60" s="100"/>
+      <c r="AC60" s="102"/>
       <c r="AD60" s="1"/>
       <c r="AE60" s="1"/>
       <c r="AF60" s="1"/>
@@ -7505,7 +7523,7 @@
       <c r="BT60" s="1"/>
       <c r="BU60" s="1"/>
     </row>
-    <row r="61" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -7537,10 +7555,10 @@
       <c r="AA61" s="82" t="s">
         <v>187</v>
       </c>
-      <c r="AB61" s="102" t="s">
+      <c r="AB61" s="103" t="s">
         <v>202</v>
       </c>
-      <c r="AC61" s="105" t="s">
+      <c r="AC61" s="106" t="s">
         <v>212</v>
       </c>
       <c r="AD61" s="1"/>
@@ -7588,7 +7606,7 @@
       <c r="BT61" s="1"/>
       <c r="BU61" s="1"/>
     </row>
-    <row r="62" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -7620,8 +7638,8 @@
       <c r="AA62" s="84" t="s">
         <v>190</v>
       </c>
-      <c r="AB62" s="103"/>
-      <c r="AC62" s="106"/>
+      <c r="AB62" s="104"/>
+      <c r="AC62" s="107"/>
       <c r="AD62" s="1"/>
       <c r="AE62" s="1"/>
       <c r="AF62" s="1"/>
@@ -7667,7 +7685,7 @@
       <c r="BT62" s="1"/>
       <c r="BU62" s="1"/>
     </row>
-    <row r="63" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -7695,8 +7713,8 @@
       <c r="Y63" s="1"/>
       <c r="Z63" s="85"/>
       <c r="AA63" s="86"/>
-      <c r="AB63" s="104"/>
-      <c r="AC63" s="107"/>
+      <c r="AB63" s="105"/>
+      <c r="AC63" s="108"/>
       <c r="AD63" s="1"/>
       <c r="AE63" s="1"/>
       <c r="AF63" s="1"/>
@@ -7742,7 +7760,7 @@
       <c r="BT63" s="1"/>
       <c r="BU63" s="1"/>
     </row>
-    <row r="64" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -7774,10 +7792,10 @@
       <c r="AA64" s="78" t="s">
         <v>188</v>
       </c>
-      <c r="AB64" s="95" t="s">
+      <c r="AB64" s="92" t="s">
         <v>203</v>
       </c>
-      <c r="AC64" s="97" t="s">
+      <c r="AC64" s="94" t="s">
         <v>213</v>
       </c>
       <c r="AD64" s="1"/>
@@ -7825,7 +7843,7 @@
       <c r="BT64" s="1"/>
       <c r="BU64" s="1"/>
     </row>
-    <row r="65" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -7857,8 +7875,8 @@
       <c r="AA65" s="78" t="s">
         <v>190</v>
       </c>
-      <c r="AB65" s="95"/>
-      <c r="AC65" s="97"/>
+      <c r="AB65" s="92"/>
+      <c r="AC65" s="94"/>
       <c r="AD65" s="1"/>
       <c r="AE65" s="1"/>
       <c r="AF65" s="1"/>
@@ -7904,7 +7922,7 @@
       <c r="BT65" s="1"/>
       <c r="BU65" s="1"/>
     </row>
-    <row r="66" spans="1:73" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -7932,8 +7950,8 @@
       <c r="Y66" s="1"/>
       <c r="Z66" s="76"/>
       <c r="AA66" s="81"/>
-      <c r="AB66" s="111"/>
-      <c r="AC66" s="112"/>
+      <c r="AB66" s="93"/>
+      <c r="AC66" s="95"/>
       <c r="AD66" s="1"/>
       <c r="AE66" s="1"/>
       <c r="AF66" s="1"/>
@@ -7979,7 +7997,7 @@
       <c r="BT66" s="1"/>
       <c r="BU66" s="1"/>
     </row>
-    <row r="67" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -8054,7 +8072,7 @@
       <c r="BT67" s="1"/>
       <c r="BU67" s="1"/>
     </row>
-    <row r="68" spans="1:73" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:73" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -8131,7 +8149,7 @@
       <c r="BT68" s="1"/>
       <c r="BU68" s="1"/>
     </row>
-    <row r="69" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -8208,7 +8226,7 @@
       <c r="BT69" s="1"/>
       <c r="BU69" s="1"/>
     </row>
-    <row r="70" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -8285,7 +8303,7 @@
       <c r="BT70" s="1"/>
       <c r="BU70" s="1"/>
     </row>
-    <row r="71" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -8360,7 +8378,7 @@
       <c r="BT71" s="1"/>
       <c r="BU71" s="1"/>
     </row>
-    <row r="72" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -8435,7 +8453,7 @@
       <c r="BT72" s="1"/>
       <c r="BU72" s="1"/>
     </row>
-    <row r="73" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -8510,7 +8528,7 @@
       <c r="BT73" s="1"/>
       <c r="BU73" s="1"/>
     </row>
-    <row r="74" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -8585,7 +8603,7 @@
       <c r="BT74" s="1"/>
       <c r="BU74" s="1"/>
     </row>
-    <row r="75" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -8660,7 +8678,7 @@
       <c r="BT75" s="1"/>
       <c r="BU75" s="1"/>
     </row>
-    <row r="76" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -8735,7 +8753,7 @@
       <c r="BT76" s="1"/>
       <c r="BU76" s="1"/>
     </row>
-    <row r="77" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -8810,7 +8828,7 @@
       <c r="BT77" s="1"/>
       <c r="BU77" s="1"/>
     </row>
-    <row r="78" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -8885,7 +8903,7 @@
       <c r="BT78" s="1"/>
       <c r="BU78" s="1"/>
     </row>
-    <row r="79" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -8960,7 +8978,7 @@
       <c r="BT79" s="1"/>
       <c r="BU79" s="1"/>
     </row>
-    <row r="80" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -9035,7 +9053,7 @@
       <c r="BT80" s="1"/>
       <c r="BU80" s="1"/>
     </row>
-    <row r="81" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -9110,7 +9128,7 @@
       <c r="BT81" s="1"/>
       <c r="BU81" s="1"/>
     </row>
-    <row r="82" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -9185,7 +9203,7 @@
       <c r="BT82" s="1"/>
       <c r="BU82" s="1"/>
     </row>
-    <row r="83" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -9260,7 +9278,7 @@
       <c r="BT83" s="1"/>
       <c r="BU83" s="1"/>
     </row>
-    <row r="84" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -9335,7 +9353,7 @@
       <c r="BT84" s="1"/>
       <c r="BU84" s="1"/>
     </row>
-    <row r="85" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -9410,7 +9428,7 @@
       <c r="BT85" s="1"/>
       <c r="BU85" s="1"/>
     </row>
-    <row r="86" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -9485,7 +9503,7 @@
       <c r="BT86" s="1"/>
       <c r="BU86" s="1"/>
     </row>
-    <row r="87" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -9560,7 +9578,7 @@
       <c r="BT87" s="1"/>
       <c r="BU87" s="1"/>
     </row>
-    <row r="88" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -9635,7 +9653,7 @@
       <c r="BT88" s="1"/>
       <c r="BU88" s="1"/>
     </row>
-    <row r="89" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -9710,7 +9728,7 @@
       <c r="BT89" s="1"/>
       <c r="BU89" s="1"/>
     </row>
-    <row r="90" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -9785,7 +9803,7 @@
       <c r="BT90" s="1"/>
       <c r="BU90" s="1"/>
     </row>
-    <row r="91" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -9860,7 +9878,7 @@
       <c r="BT91" s="1"/>
       <c r="BU91" s="1"/>
     </row>
-    <row r="92" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -9935,7 +9953,7 @@
       <c r="BT92" s="1"/>
       <c r="BU92" s="1"/>
     </row>
-    <row r="93" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -10010,7 +10028,7 @@
       <c r="BT93" s="1"/>
       <c r="BU93" s="1"/>
     </row>
-    <row r="94" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -10085,7 +10103,7 @@
       <c r="BT94" s="1"/>
       <c r="BU94" s="1"/>
     </row>
-    <row r="95" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -10160,7 +10178,7 @@
       <c r="BT95" s="1"/>
       <c r="BU95" s="1"/>
     </row>
-    <row r="96" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -10235,7 +10253,7 @@
       <c r="BT96" s="1"/>
       <c r="BU96" s="1"/>
     </row>
-    <row r="97" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -10310,7 +10328,7 @@
       <c r="BT97" s="1"/>
       <c r="BU97" s="1"/>
     </row>
-    <row r="98" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -10385,7 +10403,7 @@
       <c r="BT98" s="1"/>
       <c r="BU98" s="1"/>
     </row>
-    <row r="99" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -10460,7 +10478,7 @@
       <c r="BT99" s="1"/>
       <c r="BU99" s="1"/>
     </row>
-    <row r="100" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -10535,7 +10553,7 @@
       <c r="BT100" s="1"/>
       <c r="BU100" s="1"/>
     </row>
-    <row r="101" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -10610,7 +10628,7 @@
       <c r="BT101" s="1"/>
       <c r="BU101" s="1"/>
     </row>
-    <row r="102" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -10685,7 +10703,7 @@
       <c r="BT102" s="1"/>
       <c r="BU102" s="1"/>
     </row>
-    <row r="103" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -10760,7 +10778,7 @@
       <c r="BT103" s="1"/>
       <c r="BU103" s="1"/>
     </row>
-    <row r="104" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -10835,7 +10853,7 @@
       <c r="BT104" s="1"/>
       <c r="BU104" s="1"/>
     </row>
-    <row r="105" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -10910,7 +10928,7 @@
       <c r="BT105" s="1"/>
       <c r="BU105" s="1"/>
     </row>
-    <row r="106" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -10985,7 +11003,7 @@
       <c r="BT106" s="1"/>
       <c r="BU106" s="1"/>
     </row>
-    <row r="107" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -11060,7 +11078,7 @@
       <c r="BT107" s="1"/>
       <c r="BU107" s="1"/>
     </row>
-    <row r="108" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -11135,7 +11153,7 @@
       <c r="BT108" s="1"/>
       <c r="BU108" s="1"/>
     </row>
-    <row r="109" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -11210,7 +11228,7 @@
       <c r="BT109" s="1"/>
       <c r="BU109" s="1"/>
     </row>
-    <row r="110" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -11285,7 +11303,7 @@
       <c r="BT110" s="1"/>
       <c r="BU110" s="1"/>
     </row>
-    <row r="111" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -11360,7 +11378,7 @@
       <c r="BT111" s="1"/>
       <c r="BU111" s="1"/>
     </row>
-    <row r="112" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -11435,7 +11453,7 @@
       <c r="BT112" s="1"/>
       <c r="BU112" s="1"/>
     </row>
-    <row r="113" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -11510,7 +11528,7 @@
       <c r="BT113" s="1"/>
       <c r="BU113" s="1"/>
     </row>
-    <row r="114" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -11585,7 +11603,7 @@
       <c r="BT114" s="1"/>
       <c r="BU114" s="1"/>
     </row>
-    <row r="115" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -11660,7 +11678,7 @@
       <c r="BT115" s="1"/>
       <c r="BU115" s="1"/>
     </row>
-    <row r="116" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -11735,7 +11753,7 @@
       <c r="BT116" s="1"/>
       <c r="BU116" s="1"/>
     </row>
-    <row r="117" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -11810,7 +11828,7 @@
       <c r="BT117" s="1"/>
       <c r="BU117" s="1"/>
     </row>
-    <row r="118" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -11885,7 +11903,7 @@
       <c r="BT118" s="1"/>
       <c r="BU118" s="1"/>
     </row>
-    <row r="119" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -11960,7 +11978,7 @@
       <c r="BT119" s="1"/>
       <c r="BU119" s="1"/>
     </row>
-    <row r="120" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -12035,7 +12053,7 @@
       <c r="BT120" s="1"/>
       <c r="BU120" s="1"/>
     </row>
-    <row r="121" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -12110,7 +12128,7 @@
       <c r="BT121" s="1"/>
       <c r="BU121" s="1"/>
     </row>
-    <row r="122" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -12185,7 +12203,7 @@
       <c r="BT122" s="1"/>
       <c r="BU122" s="1"/>
     </row>
-    <row r="123" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -12260,7 +12278,7 @@
       <c r="BT123" s="1"/>
       <c r="BU123" s="1"/>
     </row>
-    <row r="124" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -12335,7 +12353,7 @@
       <c r="BT124" s="1"/>
       <c r="BU124" s="1"/>
     </row>
-    <row r="125" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -12410,7 +12428,7 @@
       <c r="BT125" s="1"/>
       <c r="BU125" s="1"/>
     </row>
-    <row r="126" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -12485,7 +12503,7 @@
       <c r="BT126" s="1"/>
       <c r="BU126" s="1"/>
     </row>
-    <row r="127" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -12560,7 +12578,7 @@
       <c r="BT127" s="1"/>
       <c r="BU127" s="1"/>
     </row>
-    <row r="128" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -12635,7 +12653,7 @@
       <c r="BT128" s="1"/>
       <c r="BU128" s="1"/>
     </row>
-    <row r="129" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -12710,7 +12728,7 @@
       <c r="BT129" s="1"/>
       <c r="BU129" s="1"/>
     </row>
-    <row r="130" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -12785,7 +12803,7 @@
       <c r="BT130" s="1"/>
       <c r="BU130" s="1"/>
     </row>
-    <row r="131" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -12860,7 +12878,7 @@
       <c r="BT131" s="1"/>
       <c r="BU131" s="1"/>
     </row>
-    <row r="132" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -12935,7 +12953,7 @@
       <c r="BT132" s="1"/>
       <c r="BU132" s="1"/>
     </row>
-    <row r="133" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -13010,7 +13028,7 @@
       <c r="BT133" s="1"/>
       <c r="BU133" s="1"/>
     </row>
-    <row r="134" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -13085,7 +13103,7 @@
       <c r="BT134" s="1"/>
       <c r="BU134" s="1"/>
     </row>
-    <row r="135" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -13160,7 +13178,7 @@
       <c r="BT135" s="1"/>
       <c r="BU135" s="1"/>
     </row>
-    <row r="136" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -13235,7 +13253,7 @@
       <c r="BT136" s="1"/>
       <c r="BU136" s="1"/>
     </row>
-    <row r="137" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -13310,7 +13328,7 @@
       <c r="BT137" s="1"/>
       <c r="BU137" s="1"/>
     </row>
-    <row r="138" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -13385,7 +13403,7 @@
       <c r="BT138" s="1"/>
       <c r="BU138" s="1"/>
     </row>
-    <row r="139" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -13460,7 +13478,7 @@
       <c r="BT139" s="1"/>
       <c r="BU139" s="1"/>
     </row>
-    <row r="140" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -13535,7 +13553,7 @@
       <c r="BT140" s="1"/>
       <c r="BU140" s="1"/>
     </row>
-    <row r="141" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -13610,7 +13628,7 @@
       <c r="BT141" s="1"/>
       <c r="BU141" s="1"/>
     </row>
-    <row r="142" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -13685,7 +13703,7 @@
       <c r="BT142" s="1"/>
       <c r="BU142" s="1"/>
     </row>
-    <row r="143" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -13760,7 +13778,7 @@
       <c r="BT143" s="1"/>
       <c r="BU143" s="1"/>
     </row>
-    <row r="144" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -13835,7 +13853,7 @@
       <c r="BT144" s="1"/>
       <c r="BU144" s="1"/>
     </row>
-    <row r="145" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -13910,7 +13928,7 @@
       <c r="BT145" s="1"/>
       <c r="BU145" s="1"/>
     </row>
-    <row r="146" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -13985,7 +14003,7 @@
       <c r="BT146" s="1"/>
       <c r="BU146" s="1"/>
     </row>
-    <row r="147" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -14060,7 +14078,7 @@
       <c r="BT147" s="1"/>
       <c r="BU147" s="1"/>
     </row>
-    <row r="148" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -14135,7 +14153,7 @@
       <c r="BT148" s="1"/>
       <c r="BU148" s="1"/>
     </row>
-    <row r="149" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -14210,7 +14228,7 @@
       <c r="BT149" s="1"/>
       <c r="BU149" s="1"/>
     </row>
-    <row r="150" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -14285,7 +14303,7 @@
       <c r="BT150" s="1"/>
       <c r="BU150" s="1"/>
     </row>
-    <row r="151" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -14360,7 +14378,7 @@
       <c r="BT151" s="1"/>
       <c r="BU151" s="1"/>
     </row>
-    <row r="152" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -14435,7 +14453,7 @@
       <c r="BT152" s="1"/>
       <c r="BU152" s="1"/>
     </row>
-    <row r="153" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -14510,7 +14528,7 @@
       <c r="BT153" s="1"/>
       <c r="BU153" s="1"/>
     </row>
-    <row r="154" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -14585,7 +14603,7 @@
       <c r="BT154" s="1"/>
       <c r="BU154" s="1"/>
     </row>
-    <row r="155" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -14660,7 +14678,7 @@
       <c r="BT155" s="1"/>
       <c r="BU155" s="1"/>
     </row>
-    <row r="156" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -14735,7 +14753,7 @@
       <c r="BT156" s="1"/>
       <c r="BU156" s="1"/>
     </row>
-    <row r="157" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -14810,7 +14828,7 @@
       <c r="BT157" s="1"/>
       <c r="BU157" s="1"/>
     </row>
-    <row r="158" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -14885,7 +14903,7 @@
       <c r="BT158" s="1"/>
       <c r="BU158" s="1"/>
     </row>
-    <row r="159" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -14960,7 +14978,7 @@
       <c r="BT159" s="1"/>
       <c r="BU159" s="1"/>
     </row>
-    <row r="160" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -15035,7 +15053,7 @@
       <c r="BT160" s="1"/>
       <c r="BU160" s="1"/>
     </row>
-    <row r="161" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -15110,7 +15128,7 @@
       <c r="BT161" s="1"/>
       <c r="BU161" s="1"/>
     </row>
-    <row r="162" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -15185,7 +15203,7 @@
       <c r="BT162" s="1"/>
       <c r="BU162" s="1"/>
     </row>
-    <row r="163" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -15260,7 +15278,7 @@
       <c r="BT163" s="1"/>
       <c r="BU163" s="1"/>
     </row>
-    <row r="164" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -15335,7 +15353,7 @@
       <c r="BT164" s="1"/>
       <c r="BU164" s="1"/>
     </row>
-    <row r="165" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -15410,7 +15428,7 @@
       <c r="BT165" s="1"/>
       <c r="BU165" s="1"/>
     </row>
-    <row r="166" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -15485,7 +15503,7 @@
       <c r="BT166" s="1"/>
       <c r="BU166" s="1"/>
     </row>
-    <row r="167" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -15560,7 +15578,7 @@
       <c r="BT167" s="1"/>
       <c r="BU167" s="1"/>
     </row>
-    <row r="168" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -15635,7 +15653,7 @@
       <c r="BT168" s="1"/>
       <c r="BU168" s="1"/>
     </row>
-    <row r="169" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -15710,7 +15728,7 @@
       <c r="BT169" s="1"/>
       <c r="BU169" s="1"/>
     </row>
-    <row r="170" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -15785,7 +15803,7 @@
       <c r="BT170" s="1"/>
       <c r="BU170" s="1"/>
     </row>
-    <row r="171" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -15860,7 +15878,7 @@
       <c r="BT171" s="1"/>
       <c r="BU171" s="1"/>
     </row>
-    <row r="172" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -15935,7 +15953,7 @@
       <c r="BT172" s="1"/>
       <c r="BU172" s="1"/>
     </row>
-    <row r="173" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -16010,7 +16028,7 @@
       <c r="BT173" s="1"/>
       <c r="BU173" s="1"/>
     </row>
-    <row r="174" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -16085,7 +16103,7 @@
       <c r="BT174" s="1"/>
       <c r="BU174" s="1"/>
     </row>
-    <row r="175" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -16160,7 +16178,7 @@
       <c r="BT175" s="1"/>
       <c r="BU175" s="1"/>
     </row>
-    <row r="176" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -16235,7 +16253,7 @@
       <c r="BT176" s="1"/>
       <c r="BU176" s="1"/>
     </row>
-    <row r="177" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -16310,7 +16328,7 @@
       <c r="BT177" s="1"/>
       <c r="BU177" s="1"/>
     </row>
-    <row r="178" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -16385,7 +16403,7 @@
       <c r="BT178" s="1"/>
       <c r="BU178" s="1"/>
     </row>
-    <row r="179" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -16460,7 +16478,7 @@
       <c r="BT179" s="1"/>
       <c r="BU179" s="1"/>
     </row>
-    <row r="180" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -16535,7 +16553,7 @@
       <c r="BT180" s="1"/>
       <c r="BU180" s="1"/>
     </row>
-    <row r="181" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -16610,7 +16628,7 @@
       <c r="BT181" s="1"/>
       <c r="BU181" s="1"/>
     </row>
-    <row r="182" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -16685,7 +16703,7 @@
       <c r="BT182" s="1"/>
       <c r="BU182" s="1"/>
     </row>
-    <row r="183" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -16760,7 +16778,7 @@
       <c r="BT183" s="1"/>
       <c r="BU183" s="1"/>
     </row>
-    <row r="184" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -16835,7 +16853,7 @@
       <c r="BT184" s="1"/>
       <c r="BU184" s="1"/>
     </row>
-    <row r="185" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -16910,7 +16928,7 @@
       <c r="BT185" s="1"/>
       <c r="BU185" s="1"/>
     </row>
-    <row r="186" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -16985,7 +17003,7 @@
       <c r="BT186" s="1"/>
       <c r="BU186" s="1"/>
     </row>
-    <row r="187" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -17060,7 +17078,7 @@
       <c r="BT187" s="1"/>
       <c r="BU187" s="1"/>
     </row>
-    <row r="188" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -17135,7 +17153,7 @@
       <c r="BT188" s="1"/>
       <c r="BU188" s="1"/>
     </row>
-    <row r="189" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -17210,7 +17228,7 @@
       <c r="BT189" s="1"/>
       <c r="BU189" s="1"/>
     </row>
-    <row r="190" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -17285,7 +17303,7 @@
       <c r="BT190" s="1"/>
       <c r="BU190" s="1"/>
     </row>
-    <row r="191" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -17360,7 +17378,7 @@
       <c r="BT191" s="1"/>
       <c r="BU191" s="1"/>
     </row>
-    <row r="192" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -17435,7 +17453,7 @@
       <c r="BT192" s="1"/>
       <c r="BU192" s="1"/>
     </row>
-    <row r="193" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -17510,7 +17528,7 @@
       <c r="BT193" s="1"/>
       <c r="BU193" s="1"/>
     </row>
-    <row r="194" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -17585,7 +17603,7 @@
       <c r="BT194" s="1"/>
       <c r="BU194" s="1"/>
     </row>
-    <row r="195" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -17660,7 +17678,7 @@
       <c r="BT195" s="1"/>
       <c r="BU195" s="1"/>
     </row>
-    <row r="196" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
@@ -17735,7 +17753,7 @@
       <c r="BT196" s="1"/>
       <c r="BU196" s="1"/>
     </row>
-    <row r="197" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -17810,7 +17828,7 @@
       <c r="BT197" s="1"/>
       <c r="BU197" s="1"/>
     </row>
-    <row r="198" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
@@ -17885,7 +17903,7 @@
       <c r="BT198" s="1"/>
       <c r="BU198" s="1"/>
     </row>
-    <row r="199" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -17960,7 +17978,7 @@
       <c r="BT199" s="1"/>
       <c r="BU199" s="1"/>
     </row>
-    <row r="200" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -18035,7 +18053,7 @@
       <c r="BT200" s="1"/>
       <c r="BU200" s="1"/>
     </row>
-    <row r="201" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
@@ -18110,7 +18128,7 @@
       <c r="BT201" s="1"/>
       <c r="BU201" s="1"/>
     </row>
-    <row r="202" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
@@ -18185,7 +18203,7 @@
       <c r="BT202" s="1"/>
       <c r="BU202" s="1"/>
     </row>
-    <row r="203" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
@@ -18260,7 +18278,7 @@
       <c r="BT203" s="1"/>
       <c r="BU203" s="1"/>
     </row>
-    <row r="204" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
@@ -18335,7 +18353,7 @@
       <c r="BT204" s="1"/>
       <c r="BU204" s="1"/>
     </row>
-    <row r="205" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
@@ -18410,7 +18428,7 @@
       <c r="BT205" s="1"/>
       <c r="BU205" s="1"/>
     </row>
-    <row r="206" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
@@ -18485,7 +18503,7 @@
       <c r="BT206" s="1"/>
       <c r="BU206" s="1"/>
     </row>
-    <row r="207" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -18560,7 +18578,7 @@
       <c r="BT207" s="1"/>
       <c r="BU207" s="1"/>
     </row>
-    <row r="208" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
@@ -18635,7 +18653,7 @@
       <c r="BT208" s="1"/>
       <c r="BU208" s="1"/>
     </row>
-    <row r="209" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
@@ -18710,7 +18728,7 @@
       <c r="BT209" s="1"/>
       <c r="BU209" s="1"/>
     </row>
-    <row r="210" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
@@ -18785,7 +18803,7 @@
       <c r="BT210" s="1"/>
       <c r="BU210" s="1"/>
     </row>
-    <row r="211" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -18860,7 +18878,7 @@
       <c r="BT211" s="1"/>
       <c r="BU211" s="1"/>
     </row>
-    <row r="212" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
@@ -18935,7 +18953,7 @@
       <c r="BT212" s="1"/>
       <c r="BU212" s="1"/>
     </row>
-    <row r="213" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
@@ -19010,7 +19028,7 @@
       <c r="BT213" s="1"/>
       <c r="BU213" s="1"/>
     </row>
-    <row r="214" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
@@ -19085,7 +19103,7 @@
       <c r="BT214" s="1"/>
       <c r="BU214" s="1"/>
     </row>
-    <row r="215" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
@@ -19160,7 +19178,7 @@
       <c r="BT215" s="1"/>
       <c r="BU215" s="1"/>
     </row>
-    <row r="216" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
@@ -19235,7 +19253,7 @@
       <c r="BT216" s="1"/>
       <c r="BU216" s="1"/>
     </row>
-    <row r="217" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
@@ -19310,7 +19328,7 @@
       <c r="BT217" s="1"/>
       <c r="BU217" s="1"/>
     </row>
-    <row r="218" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
@@ -19385,7 +19403,7 @@
       <c r="BT218" s="1"/>
       <c r="BU218" s="1"/>
     </row>
-    <row r="219" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
@@ -19460,7 +19478,7 @@
       <c r="BT219" s="1"/>
       <c r="BU219" s="1"/>
     </row>
-    <row r="220" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
@@ -19535,7 +19553,7 @@
       <c r="BT220" s="1"/>
       <c r="BU220" s="1"/>
     </row>
-    <row r="221" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
@@ -19610,7 +19628,7 @@
       <c r="BT221" s="1"/>
       <c r="BU221" s="1"/>
     </row>
-    <row r="222" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="1"/>
@@ -19685,7 +19703,7 @@
       <c r="BT222" s="1"/>
       <c r="BU222" s="1"/>
     </row>
-    <row r="223" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
@@ -19760,7 +19778,7 @@
       <c r="BT223" s="1"/>
       <c r="BU223" s="1"/>
     </row>
-    <row r="224" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
@@ -19835,7 +19853,7 @@
       <c r="BT224" s="1"/>
       <c r="BU224" s="1"/>
     </row>
-    <row r="225" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
@@ -19910,7 +19928,7 @@
       <c r="BT225" s="1"/>
       <c r="BU225" s="1"/>
     </row>
-    <row r="226" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
@@ -19985,7 +20003,7 @@
       <c r="BT226" s="1"/>
       <c r="BU226" s="1"/>
     </row>
-    <row r="227" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
@@ -20060,7 +20078,7 @@
       <c r="BT227" s="1"/>
       <c r="BU227" s="1"/>
     </row>
-    <row r="228" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
@@ -20135,7 +20153,7 @@
       <c r="BT228" s="1"/>
       <c r="BU228" s="1"/>
     </row>
-    <row r="229" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
       <c r="C229" s="1"/>
@@ -20210,7 +20228,7 @@
       <c r="BT229" s="1"/>
       <c r="BU229" s="1"/>
     </row>
-    <row r="230" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A230" s="1"/>
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
@@ -20285,7 +20303,7 @@
       <c r="BT230" s="1"/>
       <c r="BU230" s="1"/>
     </row>
-    <row r="231" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A231" s="1"/>
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
@@ -20360,7 +20378,7 @@
       <c r="BT231" s="1"/>
       <c r="BU231" s="1"/>
     </row>
-    <row r="232" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A232" s="1"/>
       <c r="B232" s="1"/>
       <c r="C232" s="1"/>
@@ -20435,7 +20453,7 @@
       <c r="BT232" s="1"/>
       <c r="BU232" s="1"/>
     </row>
-    <row r="233" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A233" s="1"/>
       <c r="B233" s="1"/>
       <c r="C233" s="1"/>
@@ -20510,7 +20528,7 @@
       <c r="BT233" s="1"/>
       <c r="BU233" s="1"/>
     </row>
-    <row r="234" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
@@ -20585,7 +20603,7 @@
       <c r="BT234" s="1"/>
       <c r="BU234" s="1"/>
     </row>
-    <row r="235" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
@@ -20660,7 +20678,7 @@
       <c r="BT235" s="1"/>
       <c r="BU235" s="1"/>
     </row>
-    <row r="236" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -20735,7 +20753,7 @@
       <c r="BT236" s="1"/>
       <c r="BU236" s="1"/>
     </row>
-    <row r="237" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A237" s="1"/>
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
@@ -20810,7 +20828,7 @@
       <c r="BT237" s="1"/>
       <c r="BU237" s="1"/>
     </row>
-    <row r="238" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A238" s="1"/>
       <c r="B238" s="1"/>
       <c r="C238" s="1"/>
@@ -20885,7 +20903,7 @@
       <c r="BT238" s="1"/>
       <c r="BU238" s="1"/>
     </row>
-    <row r="239" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A239" s="1"/>
       <c r="B239" s="1"/>
       <c r="C239" s="1"/>
@@ -20960,7 +20978,7 @@
       <c r="BT239" s="1"/>
       <c r="BU239" s="1"/>
     </row>
-    <row r="240" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -21035,7 +21053,7 @@
       <c r="BT240" s="1"/>
       <c r="BU240" s="1"/>
     </row>
-    <row r="241" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A241" s="1"/>
       <c r="B241" s="1"/>
       <c r="C241" s="1"/>
@@ -21110,7 +21128,7 @@
       <c r="BT241" s="1"/>
       <c r="BU241" s="1"/>
     </row>
-    <row r="242" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A242" s="1"/>
       <c r="B242" s="1"/>
       <c r="C242" s="1"/>
@@ -21185,7 +21203,7 @@
       <c r="BT242" s="1"/>
       <c r="BU242" s="1"/>
     </row>
-    <row r="243" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A243" s="1"/>
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
@@ -21260,7 +21278,7 @@
       <c r="BT243" s="1"/>
       <c r="BU243" s="1"/>
     </row>
-    <row r="244" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A244" s="1"/>
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
@@ -21335,7 +21353,7 @@
       <c r="BT244" s="1"/>
       <c r="BU244" s="1"/>
     </row>
-    <row r="245" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
@@ -21410,7 +21428,7 @@
       <c r="BT245" s="1"/>
       <c r="BU245" s="1"/>
     </row>
-    <row r="246" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A246" s="1"/>
       <c r="B246" s="1"/>
       <c r="C246" s="1"/>
@@ -21485,7 +21503,7 @@
       <c r="BT246" s="1"/>
       <c r="BU246" s="1"/>
     </row>
-    <row r="247" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A247" s="1"/>
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
@@ -21560,7 +21578,7 @@
       <c r="BT247" s="1"/>
       <c r="BU247" s="1"/>
     </row>
-    <row r="248" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A248" s="1"/>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
@@ -21635,7 +21653,7 @@
       <c r="BT248" s="1"/>
       <c r="BU248" s="1"/>
     </row>
-    <row r="249" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A249" s="1"/>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
@@ -21710,7 +21728,7 @@
       <c r="BT249" s="1"/>
       <c r="BU249" s="1"/>
     </row>
-    <row r="250" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A250" s="1"/>
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
@@ -21785,7 +21803,7 @@
       <c r="BT250" s="1"/>
       <c r="BU250" s="1"/>
     </row>
-    <row r="251" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A251" s="1"/>
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
@@ -21860,7 +21878,7 @@
       <c r="BT251" s="1"/>
       <c r="BU251" s="1"/>
     </row>
-    <row r="252" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A252" s="1"/>
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
@@ -21935,7 +21953,7 @@
       <c r="BT252" s="1"/>
       <c r="BU252" s="1"/>
     </row>
-    <row r="253" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
       <c r="C253" s="1"/>
@@ -22010,7 +22028,7 @@
       <c r="BT253" s="1"/>
       <c r="BU253" s="1"/>
     </row>
-    <row r="254" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A254" s="1"/>
       <c r="B254" s="1"/>
       <c r="C254" s="1"/>
@@ -22085,7 +22103,7 @@
       <c r="BT254" s="1"/>
       <c r="BU254" s="1"/>
     </row>
-    <row r="255" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A255" s="1"/>
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
@@ -22160,7 +22178,7 @@
       <c r="BT255" s="1"/>
       <c r="BU255" s="1"/>
     </row>
-    <row r="256" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A256" s="1"/>
       <c r="B256" s="1"/>
       <c r="C256" s="1"/>
@@ -22235,7 +22253,7 @@
       <c r="BT256" s="1"/>
       <c r="BU256" s="1"/>
     </row>
-    <row r="257" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A257" s="1"/>
       <c r="B257" s="1"/>
       <c r="C257" s="1"/>
@@ -22310,7 +22328,7 @@
       <c r="BT257" s="1"/>
       <c r="BU257" s="1"/>
     </row>
-    <row r="258" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
@@ -22385,7 +22403,7 @@
       <c r="BT258" s="1"/>
       <c r="BU258" s="1"/>
     </row>
-    <row r="259" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
@@ -22460,7 +22478,7 @@
       <c r="BT259" s="1"/>
       <c r="BU259" s="1"/>
     </row>
-    <row r="260" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A260" s="1"/>
       <c r="B260" s="1"/>
       <c r="C260" s="1"/>
@@ -22535,7 +22553,7 @@
       <c r="BT260" s="1"/>
       <c r="BU260" s="1"/>
     </row>
-    <row r="261" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A261" s="1"/>
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
@@ -22610,7 +22628,7 @@
       <c r="BT261" s="1"/>
       <c r="BU261" s="1"/>
     </row>
-    <row r="262" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A262" s="1"/>
       <c r="B262" s="1"/>
       <c r="C262" s="1"/>
@@ -22685,7 +22703,7 @@
       <c r="BT262" s="1"/>
       <c r="BU262" s="1"/>
     </row>
-    <row r="263" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="C263" s="1"/>
@@ -22760,7 +22778,7 @@
       <c r="BT263" s="1"/>
       <c r="BU263" s="1"/>
     </row>
-    <row r="264" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A264" s="1"/>
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
@@ -22835,7 +22853,7 @@
       <c r="BT264" s="1"/>
       <c r="BU264" s="1"/>
     </row>
-    <row r="265" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A265" s="1"/>
       <c r="B265" s="1"/>
       <c r="C265" s="1"/>
@@ -22910,7 +22928,7 @@
       <c r="BT265" s="1"/>
       <c r="BU265" s="1"/>
     </row>
-    <row r="266" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A266" s="1"/>
       <c r="B266" s="1"/>
       <c r="C266" s="1"/>
@@ -22985,7 +23003,7 @@
       <c r="BT266" s="1"/>
       <c r="BU266" s="1"/>
     </row>
-    <row r="267" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A267" s="1"/>
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
@@ -23060,7 +23078,7 @@
       <c r="BT267" s="1"/>
       <c r="BU267" s="1"/>
     </row>
-    <row r="268" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A268" s="1"/>
       <c r="B268" s="1"/>
       <c r="C268" s="1"/>
@@ -23135,7 +23153,7 @@
       <c r="BT268" s="1"/>
       <c r="BU268" s="1"/>
     </row>
-    <row r="269" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A269" s="1"/>
       <c r="B269" s="1"/>
       <c r="C269" s="1"/>
@@ -23210,7 +23228,7 @@
       <c r="BT269" s="1"/>
       <c r="BU269" s="1"/>
     </row>
-    <row r="270" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A270" s="1"/>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
@@ -23285,7 +23303,7 @@
       <c r="BT270" s="1"/>
       <c r="BU270" s="1"/>
     </row>
-    <row r="271" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A271" s="1"/>
       <c r="B271" s="1"/>
       <c r="C271" s="1"/>
@@ -23360,7 +23378,7 @@
       <c r="BT271" s="1"/>
       <c r="BU271" s="1"/>
     </row>
-    <row r="272" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
@@ -23435,7 +23453,7 @@
       <c r="BT272" s="1"/>
       <c r="BU272" s="1"/>
     </row>
-    <row r="273" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A273" s="1"/>
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
@@ -23510,7 +23528,7 @@
       <c r="BT273" s="1"/>
       <c r="BU273" s="1"/>
     </row>
-    <row r="274" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A274" s="1"/>
       <c r="B274" s="1"/>
       <c r="C274" s="1"/>
@@ -23585,7 +23603,7 @@
       <c r="BT274" s="1"/>
       <c r="BU274" s="1"/>
     </row>
-    <row r="275" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A275" s="1"/>
       <c r="B275" s="1"/>
       <c r="C275" s="1"/>
@@ -23660,7 +23678,7 @@
       <c r="BT275" s="1"/>
       <c r="BU275" s="1"/>
     </row>
-    <row r="276" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A276" s="1"/>
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
@@ -23735,7 +23753,7 @@
       <c r="BT276" s="1"/>
       <c r="BU276" s="1"/>
     </row>
-    <row r="277" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A277" s="1"/>
       <c r="B277" s="1"/>
       <c r="C277" s="1"/>
@@ -23810,7 +23828,7 @@
       <c r="BT277" s="1"/>
       <c r="BU277" s="1"/>
     </row>
-    <row r="278" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A278" s="1"/>
       <c r="B278" s="1"/>
       <c r="C278" s="1"/>
@@ -23885,7 +23903,7 @@
       <c r="BT278" s="1"/>
       <c r="BU278" s="1"/>
     </row>
-    <row r="279" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A279" s="1"/>
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
@@ -23960,7 +23978,7 @@
       <c r="BT279" s="1"/>
       <c r="BU279" s="1"/>
     </row>
-    <row r="280" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A280" s="1"/>
       <c r="B280" s="1"/>
       <c r="C280" s="1"/>
@@ -24035,7 +24053,7 @@
       <c r="BT280" s="1"/>
       <c r="BU280" s="1"/>
     </row>
-    <row r="281" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A281" s="1"/>
       <c r="B281" s="1"/>
       <c r="C281" s="1"/>
@@ -24110,7 +24128,7 @@
       <c r="BT281" s="1"/>
       <c r="BU281" s="1"/>
     </row>
-    <row r="282" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A282" s="1"/>
       <c r="B282" s="1"/>
       <c r="C282" s="1"/>
@@ -24185,7 +24203,7 @@
       <c r="BT282" s="1"/>
       <c r="BU282" s="1"/>
     </row>
-    <row r="283" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A283" s="1"/>
       <c r="B283" s="1"/>
       <c r="C283" s="1"/>
@@ -24260,7 +24278,7 @@
       <c r="BT283" s="1"/>
       <c r="BU283" s="1"/>
     </row>
-    <row r="284" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A284" s="1"/>
       <c r="B284" s="1"/>
       <c r="C284" s="1"/>
@@ -24335,7 +24353,7 @@
       <c r="BT284" s="1"/>
       <c r="BU284" s="1"/>
     </row>
-    <row r="285" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A285" s="1"/>
       <c r="B285" s="1"/>
       <c r="C285" s="1"/>
@@ -24410,7 +24428,7 @@
       <c r="BT285" s="1"/>
       <c r="BU285" s="1"/>
     </row>
-    <row r="286" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
@@ -24485,7 +24503,7 @@
       <c r="BT286" s="1"/>
       <c r="BU286" s="1"/>
     </row>
-    <row r="287" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
@@ -24560,7 +24578,7 @@
       <c r="BT287" s="1"/>
       <c r="BU287" s="1"/>
     </row>
-    <row r="288" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A288" s="1"/>
       <c r="B288" s="1"/>
       <c r="C288" s="1"/>
@@ -24635,7 +24653,7 @@
       <c r="BT288" s="1"/>
       <c r="BU288" s="1"/>
     </row>
-    <row r="289" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A289" s="1"/>
       <c r="B289" s="1"/>
       <c r="C289" s="1"/>
@@ -24710,7 +24728,7 @@
       <c r="BT289" s="1"/>
       <c r="BU289" s="1"/>
     </row>
-    <row r="290" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A290" s="1"/>
       <c r="B290" s="1"/>
       <c r="C290" s="1"/>
@@ -24785,7 +24803,7 @@
       <c r="BT290" s="1"/>
       <c r="BU290" s="1"/>
     </row>
-    <row r="291" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A291" s="1"/>
       <c r="B291" s="1"/>
       <c r="C291" s="1"/>
@@ -24860,7 +24878,7 @@
       <c r="BT291" s="1"/>
       <c r="BU291" s="1"/>
     </row>
-    <row r="292" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A292" s="1"/>
       <c r="B292" s="1"/>
       <c r="C292" s="1"/>
@@ -24935,7 +24953,7 @@
       <c r="BT292" s="1"/>
       <c r="BU292" s="1"/>
     </row>
-    <row r="293" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A293" s="1"/>
       <c r="B293" s="1"/>
       <c r="C293" s="1"/>
@@ -25010,7 +25028,7 @@
       <c r="BT293" s="1"/>
       <c r="BU293" s="1"/>
     </row>
-    <row r="294" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A294" s="1"/>
       <c r="B294" s="1"/>
       <c r="C294" s="1"/>
@@ -25085,7 +25103,7 @@
       <c r="BT294" s="1"/>
       <c r="BU294" s="1"/>
     </row>
-    <row r="295" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A295" s="1"/>
       <c r="B295" s="1"/>
       <c r="C295" s="1"/>
@@ -25160,7 +25178,7 @@
       <c r="BT295" s="1"/>
       <c r="BU295" s="1"/>
     </row>
-    <row r="296" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A296" s="1"/>
       <c r="B296" s="1"/>
       <c r="C296" s="1"/>
@@ -25235,7 +25253,7 @@
       <c r="BT296" s="1"/>
       <c r="BU296" s="1"/>
     </row>
-    <row r="297" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A297" s="1"/>
       <c r="B297" s="1"/>
       <c r="C297" s="1"/>
@@ -25310,7 +25328,7 @@
       <c r="BT297" s="1"/>
       <c r="BU297" s="1"/>
     </row>
-    <row r="298" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A298" s="1"/>
       <c r="B298" s="1"/>
       <c r="C298" s="1"/>
@@ -25385,7 +25403,7 @@
       <c r="BT298" s="1"/>
       <c r="BU298" s="1"/>
     </row>
-    <row r="299" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A299" s="1"/>
       <c r="B299" s="1"/>
       <c r="C299" s="1"/>
@@ -25460,7 +25478,7 @@
       <c r="BT299" s="1"/>
       <c r="BU299" s="1"/>
     </row>
-    <row r="300" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
       <c r="C300" s="1"/>
@@ -25535,7 +25553,7 @@
       <c r="BT300" s="1"/>
       <c r="BU300" s="1"/>
     </row>
-    <row r="301" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A301" s="1"/>
       <c r="B301" s="1"/>
       <c r="C301" s="1"/>
@@ -25610,7 +25628,7 @@
       <c r="BT301" s="1"/>
       <c r="BU301" s="1"/>
     </row>
-    <row r="302" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A302" s="1"/>
       <c r="B302" s="1"/>
       <c r="C302" s="1"/>
@@ -25685,7 +25703,7 @@
       <c r="BT302" s="1"/>
       <c r="BU302" s="1"/>
     </row>
-    <row r="303" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A303" s="1"/>
       <c r="B303" s="1"/>
       <c r="C303" s="1"/>
@@ -25760,7 +25778,7 @@
       <c r="BT303" s="1"/>
       <c r="BU303" s="1"/>
     </row>
-    <row r="304" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A304" s="1"/>
       <c r="B304" s="1"/>
       <c r="C304" s="1"/>
@@ -25835,7 +25853,7 @@
       <c r="BT304" s="1"/>
       <c r="BU304" s="1"/>
     </row>
-    <row r="305" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A305" s="1"/>
       <c r="B305" s="1"/>
       <c r="C305" s="1"/>
@@ -25910,7 +25928,7 @@
       <c r="BT305" s="1"/>
       <c r="BU305" s="1"/>
     </row>
-    <row r="306" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A306" s="1"/>
       <c r="B306" s="1"/>
       <c r="C306" s="1"/>
@@ -25985,7 +26003,7 @@
       <c r="BT306" s="1"/>
       <c r="BU306" s="1"/>
     </row>
-    <row r="307" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A307" s="1"/>
       <c r="B307" s="1"/>
       <c r="C307" s="1"/>
@@ -26060,7 +26078,7 @@
       <c r="BT307" s="1"/>
       <c r="BU307" s="1"/>
     </row>
-    <row r="308" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A308" s="1"/>
       <c r="B308" s="1"/>
       <c r="C308" s="1"/>
@@ -26135,7 +26153,7 @@
       <c r="BT308" s="1"/>
       <c r="BU308" s="1"/>
     </row>
-    <row r="309" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A309" s="1"/>
       <c r="B309" s="1"/>
       <c r="C309" s="1"/>
@@ -26210,7 +26228,7 @@
       <c r="BT309" s="1"/>
       <c r="BU309" s="1"/>
     </row>
-    <row r="310" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A310" s="1"/>
       <c r="B310" s="1"/>
       <c r="C310" s="1"/>
@@ -26285,7 +26303,7 @@
       <c r="BT310" s="1"/>
       <c r="BU310" s="1"/>
     </row>
-    <row r="311" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A311" s="1"/>
       <c r="B311" s="1"/>
       <c r="C311" s="1"/>
@@ -26360,7 +26378,7 @@
       <c r="BT311" s="1"/>
       <c r="BU311" s="1"/>
     </row>
-    <row r="312" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A312" s="1"/>
       <c r="B312" s="1"/>
       <c r="C312" s="1"/>
@@ -26435,7 +26453,7 @@
       <c r="BT312" s="1"/>
       <c r="BU312" s="1"/>
     </row>
-    <row r="313" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A313" s="1"/>
       <c r="B313" s="1"/>
       <c r="C313" s="1"/>
@@ -26510,7 +26528,7 @@
       <c r="BT313" s="1"/>
       <c r="BU313" s="1"/>
     </row>
-    <row r="314" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A314" s="1"/>
       <c r="B314" s="1"/>
       <c r="C314" s="1"/>
@@ -26585,7 +26603,7 @@
       <c r="BT314" s="1"/>
       <c r="BU314" s="1"/>
     </row>
-    <row r="315" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A315" s="1"/>
       <c r="B315" s="1"/>
       <c r="C315" s="1"/>
@@ -26660,7 +26678,7 @@
       <c r="BT315" s="1"/>
       <c r="BU315" s="1"/>
     </row>
-    <row r="316" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A316" s="1"/>
       <c r="B316" s="1"/>
       <c r="C316" s="1"/>
@@ -26735,7 +26753,7 @@
       <c r="BT316" s="1"/>
       <c r="BU316" s="1"/>
     </row>
-    <row r="317" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A317" s="1"/>
       <c r="B317" s="1"/>
       <c r="C317" s="1"/>
@@ -26810,7 +26828,7 @@
       <c r="BT317" s="1"/>
       <c r="BU317" s="1"/>
     </row>
-    <row r="318" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A318" s="1"/>
       <c r="B318" s="1"/>
       <c r="C318" s="1"/>
@@ -26885,7 +26903,7 @@
       <c r="BT318" s="1"/>
       <c r="BU318" s="1"/>
     </row>
-    <row r="319" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A319" s="1"/>
       <c r="B319" s="1"/>
       <c r="C319" s="1"/>
@@ -26960,7 +26978,7 @@
       <c r="BT319" s="1"/>
       <c r="BU319" s="1"/>
     </row>
-    <row r="320" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A320" s="1"/>
       <c r="B320" s="1"/>
       <c r="C320" s="1"/>
@@ -27035,7 +27053,7 @@
       <c r="BT320" s="1"/>
       <c r="BU320" s="1"/>
     </row>
-    <row r="321" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A321" s="1"/>
       <c r="B321" s="1"/>
       <c r="C321" s="1"/>
@@ -27110,7 +27128,7 @@
       <c r="BT321" s="1"/>
       <c r="BU321" s="1"/>
     </row>
-    <row r="322" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A322" s="1"/>
       <c r="B322" s="1"/>
       <c r="C322" s="1"/>
@@ -27185,7 +27203,7 @@
       <c r="BT322" s="1"/>
       <c r="BU322" s="1"/>
     </row>
-    <row r="323" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A323" s="1"/>
       <c r="B323" s="1"/>
       <c r="C323" s="1"/>
@@ -27260,7 +27278,7 @@
       <c r="BT323" s="1"/>
       <c r="BU323" s="1"/>
     </row>
-    <row r="324" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A324" s="1"/>
       <c r="B324" s="1"/>
       <c r="C324" s="1"/>
@@ -27335,7 +27353,7 @@
       <c r="BT324" s="1"/>
       <c r="BU324" s="1"/>
     </row>
-    <row r="325" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A325" s="1"/>
       <c r="B325" s="1"/>
       <c r="C325" s="1"/>
@@ -27410,7 +27428,7 @@
       <c r="BT325" s="1"/>
       <c r="BU325" s="1"/>
     </row>
-    <row r="326" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A326" s="1"/>
       <c r="B326" s="1"/>
       <c r="C326" s="1"/>
@@ -27485,7 +27503,7 @@
       <c r="BT326" s="1"/>
       <c r="BU326" s="1"/>
     </row>
-    <row r="327" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A327" s="1"/>
       <c r="B327" s="1"/>
       <c r="C327" s="1"/>
@@ -27560,7 +27578,7 @@
       <c r="BT327" s="1"/>
       <c r="BU327" s="1"/>
     </row>
-    <row r="328" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A328" s="1"/>
       <c r="B328" s="1"/>
       <c r="C328" s="1"/>
@@ -27635,7 +27653,7 @@
       <c r="BT328" s="1"/>
       <c r="BU328" s="1"/>
     </row>
-    <row r="329" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A329" s="1"/>
       <c r="B329" s="1"/>
       <c r="C329" s="1"/>
@@ -27710,7 +27728,7 @@
       <c r="BT329" s="1"/>
       <c r="BU329" s="1"/>
     </row>
-    <row r="330" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A330" s="1"/>
       <c r="B330" s="1"/>
       <c r="C330" s="1"/>
@@ -27785,7 +27803,7 @@
       <c r="BT330" s="1"/>
       <c r="BU330" s="1"/>
     </row>
-    <row r="331" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A331" s="1"/>
       <c r="B331" s="1"/>
       <c r="C331" s="1"/>
@@ -27860,7 +27878,7 @@
       <c r="BT331" s="1"/>
       <c r="BU331" s="1"/>
     </row>
-    <row r="332" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A332" s="1"/>
       <c r="B332" s="1"/>
       <c r="C332" s="1"/>
@@ -27935,7 +27953,7 @@
       <c r="BT332" s="1"/>
       <c r="BU332" s="1"/>
     </row>
-    <row r="333" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A333" s="1"/>
       <c r="B333" s="1"/>
       <c r="C333" s="1"/>
@@ -28010,7 +28028,7 @@
       <c r="BT333" s="1"/>
       <c r="BU333" s="1"/>
     </row>
-    <row r="334" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A334" s="1"/>
       <c r="B334" s="1"/>
       <c r="C334" s="1"/>
@@ -28085,7 +28103,7 @@
       <c r="BT334" s="1"/>
       <c r="BU334" s="1"/>
     </row>
-    <row r="335" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A335" s="1"/>
       <c r="B335" s="1"/>
       <c r="C335" s="1"/>
@@ -28160,7 +28178,7 @@
       <c r="BT335" s="1"/>
       <c r="BU335" s="1"/>
     </row>
-    <row r="336" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A336" s="1"/>
       <c r="B336" s="1"/>
       <c r="C336" s="1"/>
@@ -28235,7 +28253,7 @@
       <c r="BT336" s="1"/>
       <c r="BU336" s="1"/>
     </row>
-    <row r="337" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A337" s="1"/>
       <c r="B337" s="1"/>
       <c r="C337" s="1"/>
@@ -28310,7 +28328,7 @@
       <c r="BT337" s="1"/>
       <c r="BU337" s="1"/>
     </row>
-    <row r="338" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A338" s="1"/>
       <c r="B338" s="1"/>
       <c r="C338" s="1"/>
@@ -28385,7 +28403,7 @@
       <c r="BT338" s="1"/>
       <c r="BU338" s="1"/>
     </row>
-    <row r="339" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A339" s="1"/>
       <c r="B339" s="1"/>
       <c r="C339" s="1"/>
@@ -28460,7 +28478,7 @@
       <c r="BT339" s="1"/>
       <c r="BU339" s="1"/>
     </row>
-    <row r="340" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A340" s="1"/>
       <c r="B340" s="1"/>
       <c r="C340" s="1"/>
@@ -28535,7 +28553,7 @@
       <c r="BT340" s="1"/>
       <c r="BU340" s="1"/>
     </row>
-    <row r="341" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A341" s="1"/>
       <c r="B341" s="1"/>
       <c r="C341" s="1"/>
@@ -28610,7 +28628,7 @@
       <c r="BT341" s="1"/>
       <c r="BU341" s="1"/>
     </row>
-    <row r="342" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A342" s="1"/>
       <c r="B342" s="1"/>
       <c r="C342" s="1"/>
@@ -28685,7 +28703,7 @@
       <c r="BT342" s="1"/>
       <c r="BU342" s="1"/>
     </row>
-    <row r="343" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A343" s="1"/>
       <c r="B343" s="1"/>
       <c r="C343" s="1"/>
@@ -28760,7 +28778,7 @@
       <c r="BT343" s="1"/>
       <c r="BU343" s="1"/>
     </row>
-    <row r="344" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A344" s="1"/>
       <c r="B344" s="1"/>
       <c r="C344" s="1"/>
@@ -28835,7 +28853,7 @@
       <c r="BT344" s="1"/>
       <c r="BU344" s="1"/>
     </row>
-    <row r="345" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A345" s="1"/>
       <c r="B345" s="1"/>
       <c r="C345" s="1"/>
@@ -28910,7 +28928,7 @@
       <c r="BT345" s="1"/>
       <c r="BU345" s="1"/>
     </row>
-    <row r="346" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A346" s="1"/>
       <c r="B346" s="1"/>
       <c r="C346" s="1"/>
@@ -28985,7 +29003,7 @@
       <c r="BT346" s="1"/>
       <c r="BU346" s="1"/>
     </row>
-    <row r="347" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A347" s="1"/>
       <c r="B347" s="1"/>
       <c r="C347" s="1"/>
@@ -29060,7 +29078,7 @@
       <c r="BT347" s="1"/>
       <c r="BU347" s="1"/>
     </row>
-    <row r="348" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A348" s="1"/>
       <c r="B348" s="1"/>
       <c r="C348" s="1"/>
@@ -29135,7 +29153,7 @@
       <c r="BT348" s="1"/>
       <c r="BU348" s="1"/>
     </row>
-    <row r="349" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A349" s="1"/>
       <c r="B349" s="1"/>
       <c r="C349" s="1"/>
@@ -29210,7 +29228,7 @@
       <c r="BT349" s="1"/>
       <c r="BU349" s="1"/>
     </row>
-    <row r="350" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A350" s="1"/>
       <c r="B350" s="1"/>
       <c r="C350" s="1"/>
@@ -29285,7 +29303,7 @@
       <c r="BT350" s="1"/>
       <c r="BU350" s="1"/>
     </row>
-    <row r="351" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A351" s="1"/>
       <c r="B351" s="1"/>
       <c r="C351" s="1"/>
@@ -29360,7 +29378,7 @@
       <c r="BT351" s="1"/>
       <c r="BU351" s="1"/>
     </row>
-    <row r="352" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A352" s="1"/>
       <c r="B352" s="1"/>
       <c r="C352" s="1"/>
@@ -29435,7 +29453,7 @@
       <c r="BT352" s="1"/>
       <c r="BU352" s="1"/>
     </row>
-    <row r="353" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A353" s="1"/>
       <c r="B353" s="1"/>
       <c r="C353" s="1"/>
@@ -29510,7 +29528,7 @@
       <c r="BT353" s="1"/>
       <c r="BU353" s="1"/>
     </row>
-    <row r="354" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A354" s="1"/>
       <c r="B354" s="1"/>
       <c r="C354" s="1"/>
@@ -29585,7 +29603,7 @@
       <c r="BT354" s="1"/>
       <c r="BU354" s="1"/>
     </row>
-    <row r="355" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A355" s="1"/>
       <c r="B355" s="1"/>
       <c r="C355" s="1"/>
@@ -29660,7 +29678,7 @@
       <c r="BT355" s="1"/>
       <c r="BU355" s="1"/>
     </row>
-    <row r="356" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A356" s="1"/>
       <c r="B356" s="1"/>
       <c r="C356" s="1"/>
@@ -29735,7 +29753,7 @@
       <c r="BT356" s="1"/>
       <c r="BU356" s="1"/>
     </row>
-    <row r="357" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A357" s="1"/>
       <c r="B357" s="1"/>
       <c r="C357" s="1"/>
@@ -29810,7 +29828,7 @@
       <c r="BT357" s="1"/>
       <c r="BU357" s="1"/>
     </row>
-    <row r="358" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A358" s="1"/>
       <c r="B358" s="1"/>
       <c r="C358" s="1"/>
@@ -29885,7 +29903,7 @@
       <c r="BT358" s="1"/>
       <c r="BU358" s="1"/>
     </row>
-    <row r="359" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A359" s="1"/>
       <c r="B359" s="1"/>
       <c r="C359" s="1"/>
@@ -29960,7 +29978,7 @@
       <c r="BT359" s="1"/>
       <c r="BU359" s="1"/>
     </row>
-    <row r="360" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A360" s="1"/>
       <c r="B360" s="1"/>
       <c r="C360" s="1"/>
@@ -30035,7 +30053,7 @@
       <c r="BT360" s="1"/>
       <c r="BU360" s="1"/>
     </row>
-    <row r="361" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A361" s="1"/>
       <c r="B361" s="1"/>
       <c r="C361" s="1"/>
@@ -30110,7 +30128,7 @@
       <c r="BT361" s="1"/>
       <c r="BU361" s="1"/>
     </row>
-    <row r="362" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A362" s="1"/>
       <c r="B362" s="1"/>
       <c r="C362" s="1"/>
@@ -30185,7 +30203,7 @@
       <c r="BT362" s="1"/>
       <c r="BU362" s="1"/>
     </row>
-    <row r="363" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A363" s="1"/>
       <c r="B363" s="1"/>
       <c r="C363" s="1"/>
@@ -30260,7 +30278,7 @@
       <c r="BT363" s="1"/>
       <c r="BU363" s="1"/>
     </row>
-    <row r="364" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A364" s="1"/>
       <c r="B364" s="1"/>
       <c r="C364" s="1"/>
@@ -30335,7 +30353,7 @@
       <c r="BT364" s="1"/>
       <c r="BU364" s="1"/>
     </row>
-    <row r="365" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A365" s="1"/>
       <c r="B365" s="1"/>
       <c r="C365" s="1"/>
@@ -30410,7 +30428,7 @@
       <c r="BT365" s="1"/>
       <c r="BU365" s="1"/>
     </row>
-    <row r="366" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A366" s="1"/>
       <c r="B366" s="1"/>
       <c r="C366" s="1"/>
@@ -30485,7 +30503,7 @@
       <c r="BT366" s="1"/>
       <c r="BU366" s="1"/>
     </row>
-    <row r="367" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A367" s="1"/>
       <c r="B367" s="1"/>
       <c r="C367" s="1"/>
@@ -30560,7 +30578,7 @@
       <c r="BT367" s="1"/>
       <c r="BU367" s="1"/>
     </row>
-    <row r="368" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A368" s="1"/>
       <c r="B368" s="1"/>
       <c r="C368" s="1"/>
@@ -30635,7 +30653,7 @@
       <c r="BT368" s="1"/>
       <c r="BU368" s="1"/>
     </row>
-    <row r="369" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A369" s="1"/>
       <c r="B369" s="1"/>
       <c r="C369" s="1"/>
@@ -30710,7 +30728,7 @@
       <c r="BT369" s="1"/>
       <c r="BU369" s="1"/>
     </row>
-    <row r="370" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A370" s="1"/>
       <c r="B370" s="1"/>
       <c r="C370" s="1"/>
@@ -30785,7 +30803,7 @@
       <c r="BT370" s="1"/>
       <c r="BU370" s="1"/>
     </row>
-    <row r="371" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A371" s="1"/>
       <c r="B371" s="1"/>
       <c r="C371" s="1"/>
@@ -30860,7 +30878,7 @@
       <c r="BT371" s="1"/>
       <c r="BU371" s="1"/>
     </row>
-    <row r="372" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A372" s="1"/>
       <c r="B372" s="1"/>
       <c r="C372" s="1"/>
@@ -30935,7 +30953,7 @@
       <c r="BT372" s="1"/>
       <c r="BU372" s="1"/>
     </row>
-    <row r="373" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A373" s="1"/>
       <c r="B373" s="1"/>
       <c r="C373" s="1"/>
@@ -31010,7 +31028,7 @@
       <c r="BT373" s="1"/>
       <c r="BU373" s="1"/>
     </row>
-    <row r="374" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A374" s="1"/>
       <c r="B374" s="1"/>
       <c r="C374" s="1"/>
@@ -31085,7 +31103,7 @@
       <c r="BT374" s="1"/>
       <c r="BU374" s="1"/>
     </row>
-    <row r="375" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A375" s="1"/>
       <c r="B375" s="1"/>
       <c r="C375" s="1"/>
@@ -31160,7 +31178,7 @@
       <c r="BT375" s="1"/>
       <c r="BU375" s="1"/>
     </row>
-    <row r="376" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A376" s="1"/>
       <c r="B376" s="1"/>
       <c r="C376" s="1"/>
@@ -31235,7 +31253,7 @@
       <c r="BT376" s="1"/>
       <c r="BU376" s="1"/>
     </row>
-    <row r="377" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A377" s="1"/>
       <c r="B377" s="1"/>
       <c r="C377" s="1"/>
@@ -31310,7 +31328,7 @@
       <c r="BT377" s="1"/>
       <c r="BU377" s="1"/>
     </row>
-    <row r="378" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A378" s="1"/>
       <c r="B378" s="1"/>
       <c r="C378" s="1"/>
@@ -31385,7 +31403,7 @@
       <c r="BT378" s="1"/>
       <c r="BU378" s="1"/>
     </row>
-    <row r="379" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A379" s="1"/>
       <c r="B379" s="1"/>
       <c r="C379" s="1"/>
@@ -31460,7 +31478,7 @@
       <c r="BT379" s="1"/>
       <c r="BU379" s="1"/>
     </row>
-    <row r="380" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A380" s="1"/>
       <c r="B380" s="1"/>
       <c r="C380" s="1"/>
@@ -31535,7 +31553,7 @@
       <c r="BT380" s="1"/>
       <c r="BU380" s="1"/>
     </row>
-    <row r="381" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A381" s="1"/>
       <c r="B381" s="1"/>
       <c r="C381" s="1"/>
@@ -31610,7 +31628,7 @@
       <c r="BT381" s="1"/>
       <c r="BU381" s="1"/>
     </row>
-    <row r="382" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A382" s="1"/>
       <c r="B382" s="1"/>
       <c r="C382" s="1"/>
@@ -31685,7 +31703,7 @@
       <c r="BT382" s="1"/>
       <c r="BU382" s="1"/>
     </row>
-    <row r="383" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A383" s="1"/>
       <c r="B383" s="1"/>
       <c r="C383" s="1"/>
@@ -31760,7 +31778,7 @@
       <c r="BT383" s="1"/>
       <c r="BU383" s="1"/>
     </row>
-    <row r="384" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A384" s="1"/>
       <c r="B384" s="1"/>
       <c r="C384" s="1"/>
@@ -31835,7 +31853,7 @@
       <c r="BT384" s="1"/>
       <c r="BU384" s="1"/>
     </row>
-    <row r="385" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A385" s="1"/>
       <c r="B385" s="1"/>
       <c r="C385" s="1"/>
@@ -31910,7 +31928,7 @@
       <c r="BT385" s="1"/>
       <c r="BU385" s="1"/>
     </row>
-    <row r="386" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A386" s="1"/>
       <c r="B386" s="1"/>
       <c r="C386" s="1"/>
@@ -31985,7 +32003,7 @@
       <c r="BT386" s="1"/>
       <c r="BU386" s="1"/>
     </row>
-    <row r="387" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A387" s="1"/>
       <c r="B387" s="1"/>
       <c r="C387" s="1"/>
@@ -32060,7 +32078,7 @@
       <c r="BT387" s="1"/>
       <c r="BU387" s="1"/>
     </row>
-    <row r="388" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A388" s="1"/>
       <c r="B388" s="1"/>
       <c r="C388" s="1"/>
@@ -32135,7 +32153,7 @@
       <c r="BT388" s="1"/>
       <c r="BU388" s="1"/>
     </row>
-    <row r="389" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A389" s="1"/>
       <c r="B389" s="1"/>
       <c r="C389" s="1"/>
@@ -32210,7 +32228,7 @@
       <c r="BT389" s="1"/>
       <c r="BU389" s="1"/>
     </row>
-    <row r="390" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A390" s="1"/>
       <c r="B390" s="1"/>
       <c r="C390" s="1"/>
@@ -32285,7 +32303,7 @@
       <c r="BT390" s="1"/>
       <c r="BU390" s="1"/>
     </row>
-    <row r="391" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A391" s="1"/>
       <c r="B391" s="1"/>
       <c r="C391" s="1"/>
@@ -32360,7 +32378,7 @@
       <c r="BT391" s="1"/>
       <c r="BU391" s="1"/>
     </row>
-    <row r="392" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A392" s="1"/>
       <c r="B392" s="1"/>
       <c r="C392" s="1"/>
@@ -32435,7 +32453,7 @@
       <c r="BT392" s="1"/>
       <c r="BU392" s="1"/>
     </row>
-    <row r="393" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A393" s="1"/>
       <c r="B393" s="1"/>
       <c r="C393" s="1"/>
@@ -32510,7 +32528,7 @@
       <c r="BT393" s="1"/>
       <c r="BU393" s="1"/>
     </row>
-    <row r="394" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A394" s="1"/>
       <c r="B394" s="1"/>
       <c r="C394" s="1"/>
@@ -32585,7 +32603,7 @@
       <c r="BT394" s="1"/>
       <c r="BU394" s="1"/>
     </row>
-    <row r="395" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A395" s="1"/>
       <c r="B395" s="1"/>
       <c r="C395" s="1"/>
@@ -32660,7 +32678,7 @@
       <c r="BT395" s="1"/>
       <c r="BU395" s="1"/>
     </row>
-    <row r="396" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A396" s="1"/>
       <c r="B396" s="1"/>
       <c r="C396" s="1"/>
@@ -32735,7 +32753,7 @@
       <c r="BT396" s="1"/>
       <c r="BU396" s="1"/>
     </row>
-    <row r="397" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A397" s="1"/>
       <c r="B397" s="1"/>
       <c r="C397" s="1"/>
@@ -32810,7 +32828,7 @@
       <c r="BT397" s="1"/>
       <c r="BU397" s="1"/>
     </row>
-    <row r="398" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A398" s="1"/>
       <c r="B398" s="1"/>
       <c r="C398" s="1"/>
@@ -32885,7 +32903,7 @@
       <c r="BT398" s="1"/>
       <c r="BU398" s="1"/>
     </row>
-    <row r="399" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A399" s="1"/>
       <c r="B399" s="1"/>
       <c r="C399" s="1"/>
@@ -32960,7 +32978,7 @@
       <c r="BT399" s="1"/>
       <c r="BU399" s="1"/>
     </row>
-    <row r="400" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A400" s="1"/>
       <c r="B400" s="1"/>
       <c r="C400" s="1"/>
@@ -33035,7 +33053,7 @@
       <c r="BT400" s="1"/>
       <c r="BU400" s="1"/>
     </row>
-    <row r="401" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A401" s="1"/>
       <c r="B401" s="1"/>
       <c r="C401" s="1"/>
@@ -33110,7 +33128,7 @@
       <c r="BT401" s="1"/>
       <c r="BU401" s="1"/>
     </row>
-    <row r="402" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A402" s="1"/>
       <c r="B402" s="1"/>
       <c r="C402" s="1"/>
@@ -33185,7 +33203,7 @@
       <c r="BT402" s="1"/>
       <c r="BU402" s="1"/>
     </row>
-    <row r="403" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A403" s="1"/>
       <c r="B403" s="1"/>
       <c r="C403" s="1"/>
@@ -33260,7 +33278,7 @@
       <c r="BT403" s="1"/>
       <c r="BU403" s="1"/>
     </row>
-    <row r="404" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A404" s="1"/>
       <c r="B404" s="1"/>
       <c r="C404" s="1"/>
@@ -33335,7 +33353,7 @@
       <c r="BT404" s="1"/>
       <c r="BU404" s="1"/>
     </row>
-    <row r="405" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A405" s="1"/>
       <c r="B405" s="1"/>
       <c r="C405" s="1"/>
@@ -33410,7 +33428,7 @@
       <c r="BT405" s="1"/>
       <c r="BU405" s="1"/>
     </row>
-    <row r="406" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A406" s="1"/>
       <c r="B406" s="1"/>
       <c r="C406" s="1"/>
@@ -33485,7 +33503,7 @@
       <c r="BT406" s="1"/>
       <c r="BU406" s="1"/>
     </row>
-    <row r="407" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A407" s="1"/>
       <c r="B407" s="1"/>
       <c r="C407" s="1"/>
@@ -33560,7 +33578,7 @@
       <c r="BT407" s="1"/>
       <c r="BU407" s="1"/>
     </row>
-    <row r="408" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A408" s="1"/>
       <c r="B408" s="1"/>
       <c r="C408" s="1"/>
@@ -33635,7 +33653,7 @@
       <c r="BT408" s="1"/>
       <c r="BU408" s="1"/>
     </row>
-    <row r="409" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A409" s="1"/>
       <c r="B409" s="1"/>
       <c r="C409" s="1"/>
@@ -33710,7 +33728,7 @@
       <c r="BT409" s="1"/>
       <c r="BU409" s="1"/>
     </row>
-    <row r="410" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A410" s="1"/>
       <c r="B410" s="1"/>
       <c r="C410" s="1"/>
@@ -33785,7 +33803,7 @@
       <c r="BT410" s="1"/>
       <c r="BU410" s="1"/>
     </row>
-    <row r="411" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A411" s="1"/>
       <c r="B411" s="1"/>
       <c r="C411" s="1"/>
@@ -33860,7 +33878,7 @@
       <c r="BT411" s="1"/>
       <c r="BU411" s="1"/>
     </row>
-    <row r="412" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A412" s="1"/>
       <c r="B412" s="1"/>
       <c r="C412" s="1"/>
@@ -33935,7 +33953,7 @@
       <c r="BT412" s="1"/>
       <c r="BU412" s="1"/>
     </row>
-    <row r="413" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A413" s="1"/>
       <c r="B413" s="1"/>
       <c r="C413" s="1"/>
@@ -34010,7 +34028,7 @@
       <c r="BT413" s="1"/>
       <c r="BU413" s="1"/>
     </row>
-    <row r="414" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A414" s="1"/>
       <c r="B414" s="1"/>
       <c r="C414" s="1"/>
@@ -34085,7 +34103,7 @@
       <c r="BT414" s="1"/>
       <c r="BU414" s="1"/>
     </row>
-    <row r="415" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A415" s="1"/>
       <c r="B415" s="1"/>
       <c r="C415" s="1"/>
@@ -34160,7 +34178,7 @@
       <c r="BT415" s="1"/>
       <c r="BU415" s="1"/>
     </row>
-    <row r="416" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A416" s="1"/>
       <c r="B416" s="1"/>
       <c r="C416" s="1"/>
@@ -34235,7 +34253,7 @@
       <c r="BT416" s="1"/>
       <c r="BU416" s="1"/>
     </row>
-    <row r="417" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A417" s="1"/>
       <c r="B417" s="1"/>
       <c r="C417" s="1"/>
@@ -34310,7 +34328,7 @@
       <c r="BT417" s="1"/>
       <c r="BU417" s="1"/>
     </row>
-    <row r="418" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A418" s="1"/>
       <c r="B418" s="1"/>
       <c r="C418" s="1"/>
@@ -34385,7 +34403,7 @@
       <c r="BT418" s="1"/>
       <c r="BU418" s="1"/>
     </row>
-    <row r="419" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A419" s="1"/>
       <c r="B419" s="1"/>
       <c r="C419" s="1"/>
@@ -34460,7 +34478,7 @@
       <c r="BT419" s="1"/>
       <c r="BU419" s="1"/>
     </row>
-    <row r="420" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A420" s="1"/>
       <c r="B420" s="1"/>
       <c r="C420" s="1"/>
@@ -34535,7 +34553,7 @@
       <c r="BT420" s="1"/>
       <c r="BU420" s="1"/>
     </row>
-    <row r="421" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A421" s="1"/>
       <c r="B421" s="1"/>
       <c r="C421" s="1"/>
@@ -34610,7 +34628,7 @@
       <c r="BT421" s="1"/>
       <c r="BU421" s="1"/>
     </row>
-    <row r="422" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A422" s="1"/>
       <c r="B422" s="1"/>
       <c r="C422" s="1"/>
@@ -34685,7 +34703,7 @@
       <c r="BT422" s="1"/>
       <c r="BU422" s="1"/>
     </row>
-    <row r="423" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A423" s="1"/>
       <c r="B423" s="1"/>
       <c r="C423" s="1"/>
@@ -34760,7 +34778,7 @@
       <c r="BT423" s="1"/>
       <c r="BU423" s="1"/>
     </row>
-    <row r="424" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A424" s="1"/>
       <c r="B424" s="1"/>
       <c r="C424" s="1"/>
@@ -34835,7 +34853,7 @@
       <c r="BT424" s="1"/>
       <c r="BU424" s="1"/>
     </row>
-    <row r="425" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A425" s="1"/>
       <c r="B425" s="1"/>
       <c r="C425" s="1"/>
@@ -34910,7 +34928,7 @@
       <c r="BT425" s="1"/>
       <c r="BU425" s="1"/>
     </row>
-    <row r="426" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A426" s="1"/>
       <c r="B426" s="1"/>
       <c r="C426" s="1"/>
@@ -34985,7 +35003,7 @@
       <c r="BT426" s="1"/>
       <c r="BU426" s="1"/>
     </row>
-    <row r="427" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A427" s="1"/>
       <c r="B427" s="1"/>
       <c r="C427" s="1"/>
@@ -35060,7 +35078,7 @@
       <c r="BT427" s="1"/>
       <c r="BU427" s="1"/>
     </row>
-    <row r="428" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A428" s="1"/>
       <c r="B428" s="1"/>
       <c r="C428" s="1"/>
@@ -35135,7 +35153,7 @@
       <c r="BT428" s="1"/>
       <c r="BU428" s="1"/>
     </row>
-    <row r="429" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A429" s="1"/>
       <c r="B429" s="1"/>
       <c r="C429" s="1"/>
@@ -35210,7 +35228,7 @@
       <c r="BT429" s="1"/>
       <c r="BU429" s="1"/>
     </row>
-    <row r="430" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A430" s="1"/>
       <c r="B430" s="1"/>
       <c r="C430" s="1"/>
@@ -35285,7 +35303,7 @@
       <c r="BT430" s="1"/>
       <c r="BU430" s="1"/>
     </row>
-    <row r="431" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A431" s="1"/>
       <c r="B431" s="1"/>
       <c r="C431" s="1"/>
@@ -35360,7 +35378,7 @@
       <c r="BT431" s="1"/>
       <c r="BU431" s="1"/>
     </row>
-    <row r="432" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A432" s="1"/>
       <c r="B432" s="1"/>
       <c r="C432" s="1"/>
@@ -35435,7 +35453,7 @@
       <c r="BT432" s="1"/>
       <c r="BU432" s="1"/>
     </row>
-    <row r="433" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A433" s="1"/>
       <c r="B433" s="1"/>
       <c r="C433" s="1"/>
@@ -35510,7 +35528,7 @@
       <c r="BT433" s="1"/>
       <c r="BU433" s="1"/>
     </row>
-    <row r="434" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A434" s="1"/>
       <c r="B434" s="1"/>
       <c r="C434" s="1"/>
@@ -35585,7 +35603,7 @@
       <c r="BT434" s="1"/>
       <c r="BU434" s="1"/>
     </row>
-    <row r="435" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A435" s="1"/>
       <c r="B435" s="1"/>
       <c r="C435" s="1"/>
@@ -35660,7 +35678,7 @@
       <c r="BT435" s="1"/>
       <c r="BU435" s="1"/>
     </row>
-    <row r="436" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A436" s="1"/>
       <c r="B436" s="1"/>
       <c r="C436" s="1"/>
@@ -35735,7 +35753,7 @@
       <c r="BT436" s="1"/>
       <c r="BU436" s="1"/>
     </row>
-    <row r="437" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A437" s="1"/>
       <c r="B437" s="1"/>
       <c r="C437" s="1"/>
@@ -35810,7 +35828,7 @@
       <c r="BT437" s="1"/>
       <c r="BU437" s="1"/>
     </row>
-    <row r="438" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A438" s="1"/>
       <c r="B438" s="1"/>
       <c r="C438" s="1"/>
@@ -35885,7 +35903,7 @@
       <c r="BT438" s="1"/>
       <c r="BU438" s="1"/>
     </row>
-    <row r="439" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A439" s="1"/>
       <c r="B439" s="1"/>
       <c r="C439" s="1"/>
@@ -35960,7 +35978,7 @@
       <c r="BT439" s="1"/>
       <c r="BU439" s="1"/>
     </row>
-    <row r="440" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A440" s="1"/>
       <c r="B440" s="1"/>
       <c r="C440" s="1"/>
@@ -36035,7 +36053,7 @@
       <c r="BT440" s="1"/>
       <c r="BU440" s="1"/>
     </row>
-    <row r="441" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A441" s="1"/>
       <c r="B441" s="1"/>
       <c r="C441" s="1"/>
@@ -36110,7 +36128,7 @@
       <c r="BT441" s="1"/>
       <c r="BU441" s="1"/>
     </row>
-    <row r="442" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A442" s="1"/>
       <c r="B442" s="1"/>
       <c r="C442" s="1"/>
@@ -36185,7 +36203,7 @@
       <c r="BT442" s="1"/>
       <c r="BU442" s="1"/>
     </row>
-    <row r="443" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A443" s="1"/>
       <c r="B443" s="1"/>
       <c r="C443" s="1"/>
@@ -36260,7 +36278,7 @@
       <c r="BT443" s="1"/>
       <c r="BU443" s="1"/>
     </row>
-    <row r="444" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A444" s="1"/>
       <c r="B444" s="1"/>
       <c r="C444" s="1"/>
@@ -36335,7 +36353,7 @@
       <c r="BT444" s="1"/>
       <c r="BU444" s="1"/>
     </row>
-    <row r="445" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A445" s="1"/>
       <c r="B445" s="1"/>
       <c r="C445" s="1"/>
@@ -36410,7 +36428,7 @@
       <c r="BT445" s="1"/>
       <c r="BU445" s="1"/>
     </row>
-    <row r="446" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A446" s="1"/>
       <c r="B446" s="1"/>
       <c r="C446" s="1"/>
@@ -36485,7 +36503,7 @@
       <c r="BT446" s="1"/>
       <c r="BU446" s="1"/>
     </row>
-    <row r="447" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A447" s="1"/>
       <c r="B447" s="1"/>
       <c r="C447" s="1"/>
@@ -36560,7 +36578,7 @@
       <c r="BT447" s="1"/>
       <c r="BU447" s="1"/>
     </row>
-    <row r="448" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A448" s="1"/>
       <c r="B448" s="1"/>
       <c r="C448" s="1"/>
@@ -36635,7 +36653,7 @@
       <c r="BT448" s="1"/>
       <c r="BU448" s="1"/>
     </row>
-    <row r="449" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A449" s="1"/>
       <c r="B449" s="1"/>
       <c r="C449" s="1"/>
@@ -36710,7 +36728,7 @@
       <c r="BT449" s="1"/>
       <c r="BU449" s="1"/>
     </row>
-    <row r="450" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A450" s="1"/>
       <c r="B450" s="1"/>
       <c r="C450" s="1"/>
@@ -36785,7 +36803,7 @@
       <c r="BT450" s="1"/>
       <c r="BU450" s="1"/>
     </row>
-    <row r="451" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A451" s="1"/>
       <c r="B451" s="1"/>
       <c r="C451" s="1"/>
@@ -36860,7 +36878,7 @@
       <c r="BT451" s="1"/>
       <c r="BU451" s="1"/>
     </row>
-    <row r="452" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A452" s="1"/>
       <c r="B452" s="1"/>
       <c r="C452" s="1"/>
@@ -36935,7 +36953,7 @@
       <c r="BT452" s="1"/>
       <c r="BU452" s="1"/>
     </row>
-    <row r="453" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A453" s="1"/>
       <c r="B453" s="1"/>
       <c r="C453" s="1"/>
@@ -37010,7 +37028,7 @@
       <c r="BT453" s="1"/>
       <c r="BU453" s="1"/>
     </row>
-    <row r="454" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A454" s="1"/>
       <c r="B454" s="1"/>
       <c r="C454" s="1"/>
@@ -37085,7 +37103,7 @@
       <c r="BT454" s="1"/>
       <c r="BU454" s="1"/>
     </row>
-    <row r="455" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A455" s="1"/>
       <c r="B455" s="1"/>
       <c r="C455" s="1"/>
@@ -37160,7 +37178,7 @@
       <c r="BT455" s="1"/>
       <c r="BU455" s="1"/>
     </row>
-    <row r="456" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A456" s="1"/>
       <c r="B456" s="1"/>
       <c r="C456" s="1"/>
@@ -37235,7 +37253,7 @@
       <c r="BT456" s="1"/>
       <c r="BU456" s="1"/>
     </row>
-    <row r="457" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A457" s="1"/>
       <c r="B457" s="1"/>
       <c r="C457" s="1"/>
@@ -37310,7 +37328,7 @@
       <c r="BT457" s="1"/>
       <c r="BU457" s="1"/>
     </row>
-    <row r="458" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A458" s="1"/>
       <c r="B458" s="1"/>
       <c r="C458" s="1"/>
@@ -37385,7 +37403,7 @@
       <c r="BT458" s="1"/>
       <c r="BU458" s="1"/>
     </row>
-    <row r="459" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A459" s="1"/>
       <c r="B459" s="1"/>
       <c r="C459" s="1"/>
@@ -37460,7 +37478,7 @@
       <c r="BT459" s="1"/>
       <c r="BU459" s="1"/>
     </row>
-    <row r="460" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A460" s="1"/>
       <c r="B460" s="1"/>
       <c r="C460" s="1"/>
@@ -37535,7 +37553,7 @@
       <c r="BT460" s="1"/>
       <c r="BU460" s="1"/>
     </row>
-    <row r="461" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A461" s="1"/>
       <c r="B461" s="1"/>
       <c r="C461" s="1"/>
@@ -37610,7 +37628,7 @@
       <c r="BT461" s="1"/>
       <c r="BU461" s="1"/>
     </row>
-    <row r="462" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A462" s="1"/>
       <c r="B462" s="1"/>
       <c r="C462" s="1"/>
@@ -37685,7 +37703,7 @@
       <c r="BT462" s="1"/>
       <c r="BU462" s="1"/>
     </row>
-    <row r="463" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A463" s="1"/>
       <c r="B463" s="1"/>
       <c r="C463" s="1"/>
@@ -37760,7 +37778,7 @@
       <c r="BT463" s="1"/>
       <c r="BU463" s="1"/>
     </row>
-    <row r="464" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A464" s="1"/>
       <c r="B464" s="1"/>
       <c r="C464" s="1"/>
@@ -37835,7 +37853,7 @@
       <c r="BT464" s="1"/>
       <c r="BU464" s="1"/>
     </row>
-    <row r="465" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A465" s="1"/>
       <c r="B465" s="1"/>
       <c r="C465" s="1"/>
@@ -37910,7 +37928,7 @@
       <c r="BT465" s="1"/>
       <c r="BU465" s="1"/>
     </row>
-    <row r="466" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A466" s="1"/>
       <c r="B466" s="1"/>
       <c r="C466" s="1"/>
@@ -37985,7 +38003,7 @@
       <c r="BT466" s="1"/>
       <c r="BU466" s="1"/>
     </row>
-    <row r="467" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A467" s="1"/>
       <c r="B467" s="1"/>
       <c r="C467" s="1"/>
@@ -38060,7 +38078,7 @@
       <c r="BT467" s="1"/>
       <c r="BU467" s="1"/>
     </row>
-    <row r="468" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A468" s="1"/>
       <c r="B468" s="1"/>
       <c r="C468" s="1"/>
@@ -38135,7 +38153,7 @@
       <c r="BT468" s="1"/>
       <c r="BU468" s="1"/>
     </row>
-    <row r="469" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A469" s="1"/>
       <c r="B469" s="1"/>
       <c r="C469" s="1"/>
@@ -38210,7 +38228,7 @@
       <c r="BT469" s="1"/>
       <c r="BU469" s="1"/>
     </row>
-    <row r="470" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A470" s="1"/>
       <c r="B470" s="1"/>
       <c r="C470" s="1"/>
@@ -38285,7 +38303,7 @@
       <c r="BT470" s="1"/>
       <c r="BU470" s="1"/>
     </row>
-    <row r="471" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A471" s="1"/>
       <c r="B471" s="1"/>
       <c r="C471" s="1"/>
@@ -38360,7 +38378,7 @@
       <c r="BT471" s="1"/>
       <c r="BU471" s="1"/>
     </row>
-    <row r="472" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A472" s="1"/>
       <c r="B472" s="1"/>
       <c r="C472" s="1"/>
@@ -38435,7 +38453,7 @@
       <c r="BT472" s="1"/>
       <c r="BU472" s="1"/>
     </row>
-    <row r="473" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A473" s="1"/>
       <c r="B473" s="1"/>
       <c r="C473" s="1"/>
@@ -38510,7 +38528,7 @@
       <c r="BT473" s="1"/>
       <c r="BU473" s="1"/>
     </row>
-    <row r="474" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A474" s="1"/>
       <c r="G474" s="1"/>
       <c r="H474" s="1"/>
@@ -38570,7 +38588,7 @@
       <c r="BT474" s="1"/>
       <c r="BU474" s="1"/>
     </row>
-    <row r="475" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A475" s="1"/>
       <c r="G475" s="1"/>
       <c r="H475" s="1"/>
@@ -38630,7 +38648,7 @@
       <c r="BT475" s="1"/>
       <c r="BU475" s="1"/>
     </row>
-    <row r="476" spans="1:73" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A476" s="1"/>
       <c r="G476" s="1"/>
       <c r="H476" s="1"/>
@@ -38692,6 +38710,35 @@
     </row>
   </sheetData>
   <mergeCells count="45">
+    <mergeCell ref="R3:Y3"/>
+    <mergeCell ref="R4:Y4"/>
+    <mergeCell ref="Z16:Z18"/>
+    <mergeCell ref="AB16:AB18"/>
+    <mergeCell ref="AC16:AC18"/>
+    <mergeCell ref="Z19:Z21"/>
+    <mergeCell ref="AB19:AB21"/>
+    <mergeCell ref="AC19:AC21"/>
+    <mergeCell ref="Z25:Z27"/>
+    <mergeCell ref="AB25:AB27"/>
+    <mergeCell ref="AC25:AC27"/>
+    <mergeCell ref="Z28:Z30"/>
+    <mergeCell ref="AB28:AB30"/>
+    <mergeCell ref="AC28:AC30"/>
+    <mergeCell ref="Z31:Z33"/>
+    <mergeCell ref="AB31:AB33"/>
+    <mergeCell ref="AC31:AC33"/>
+    <mergeCell ref="Z34:Z36"/>
+    <mergeCell ref="AB34:AB36"/>
+    <mergeCell ref="AC34:AC36"/>
+    <mergeCell ref="Z37:Z39"/>
+    <mergeCell ref="AB37:AB39"/>
+    <mergeCell ref="AC37:AC39"/>
+    <mergeCell ref="AC52:AC54"/>
+    <mergeCell ref="Z40:Z42"/>
+    <mergeCell ref="AB40:AB42"/>
+    <mergeCell ref="AC40:AC42"/>
+    <mergeCell ref="AB43:AB45"/>
+    <mergeCell ref="AC43:AC45"/>
     <mergeCell ref="AB64:AB66"/>
     <mergeCell ref="AC64:AC66"/>
     <mergeCell ref="Z22:Z24"/>
@@ -38708,35 +38755,6 @@
     <mergeCell ref="AB49:AB51"/>
     <mergeCell ref="AC49:AC51"/>
     <mergeCell ref="AB52:AB54"/>
-    <mergeCell ref="AC52:AC54"/>
-    <mergeCell ref="Z40:Z42"/>
-    <mergeCell ref="AB40:AB42"/>
-    <mergeCell ref="AC40:AC42"/>
-    <mergeCell ref="AB43:AB45"/>
-    <mergeCell ref="AC43:AC45"/>
-    <mergeCell ref="Z34:Z36"/>
-    <mergeCell ref="AB34:AB36"/>
-    <mergeCell ref="AC34:AC36"/>
-    <mergeCell ref="Z37:Z39"/>
-    <mergeCell ref="AB37:AB39"/>
-    <mergeCell ref="AC37:AC39"/>
-    <mergeCell ref="Z28:Z30"/>
-    <mergeCell ref="AB28:AB30"/>
-    <mergeCell ref="AC28:AC30"/>
-    <mergeCell ref="Z31:Z33"/>
-    <mergeCell ref="AB31:AB33"/>
-    <mergeCell ref="AC31:AC33"/>
-    <mergeCell ref="Z19:Z21"/>
-    <mergeCell ref="AB19:AB21"/>
-    <mergeCell ref="AC19:AC21"/>
-    <mergeCell ref="Z25:Z27"/>
-    <mergeCell ref="AB25:AB27"/>
-    <mergeCell ref="AC25:AC27"/>
-    <mergeCell ref="R3:Y3"/>
-    <mergeCell ref="R4:Y4"/>
-    <mergeCell ref="Z16:Z18"/>
-    <mergeCell ref="AB16:AB18"/>
-    <mergeCell ref="AC16:AC18"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
